--- a/database_penyimpanan_aman/database_transaksi_rincian.xlsx
+++ b/database_penyimpanan_aman/database_transaksi_rincian.xlsx
@@ -692,7 +692,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-08-16 20:23:22</t>
+          <t>2026-08-16 20:36:21</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_transaksi_rincian.xlsx
+++ b/database_penyimpanan_aman/database_transaksi_rincian.xlsx
@@ -692,7 +692,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-08-16 20:36:21</t>
+          <t>2026-08-16 20:39:05</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_transaksi_rincian.xlsx
+++ b/database_penyimpanan_aman/database_transaksi_rincian.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB2"/>
+  <dimension ref="A1:AB3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -559,10 +559,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>7207250142</t>
-        </is>
+      <c r="A2" t="n">
+        <v>7207250142</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -601,10 +599,8 @@
           <t>24 Month</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4500011424</t>
-        </is>
+      <c r="I2" t="n">
+        <v>4500011424</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -693,6 +689,144 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>2026-08-16 20:39:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka
+</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>S250551FLD-R1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>043/BSS-JOB/AB/VII/2026</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>31 Jul 2026</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia
+</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>24 Month</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4500011425</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jasa Sewa Man Lift Untuk support Kegiatan Operation &amp; Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026, Refer CTR No. 7207250142-BSS-CTR-2026-020" (01 - 31 Juli 2026)
+</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>1 Jul 2026</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>MONTHLY BASIS</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg
+</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>100</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>01 Jul 2026</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>31 Jul 2026</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>62818000</v>
+      </c>
+      <c r="U3" t="n">
+        <v>62818000</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Periode Pekerjaan 01 sd 31 Juli 2026</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>2026-08-16 20:58:40</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_transaksi_rincian.xlsx
+++ b/database_penyimpanan_aman/database_transaksi_rincian.xlsx
@@ -575,7 +575,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>042/BSS-JOB/AB/VII/2026</t>
+          <t>043/BSS-JOB/AB/VII/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -600,11 +600,11 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4500011424</v>
+        <v>4500011425</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jasa Sewa Backhoe Loader Untuk support Kegiatan Operation &amp; Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026, Refer CTR No. 7207250142-BSS-CTR-2026-019" (01 - 31 Juli 2026)
+          <t xml:space="preserve">Jasa Sewa Man Lift Untuk support Kegiatan Operation &amp; Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026, Refer CTR No. 7207250142-BSS-CTR-2026-020" (01 - 31 Juli 2026)
 </t>
         </is>
       </c>
@@ -625,7 +625,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP
+          <t xml:space="preserve">Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg
 </t>
         </is>
       </c>
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="T2" t="n">
-        <v>75538000</v>
+        <v>62818000</v>
       </c>
       <c r="U2" t="n">
-        <v>75538000</v>
+        <v>62818000</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -683,12 +683,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Periode Pekerjaan 01 Juli sd 31 Juli 2026</t>
+          <t>Periode Pekerjaan 01 sd 31 Juli 2026</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-08-16 20:39:05</t>
+          <t>2026-08-16 20:58:40</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>043/BSS-JOB/AB/VII/2026</t>
+          <t>042/BSS-JOB/AB/VII/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4500011425</t>
+          <t>4500011424</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jasa Sewa Man Lift Untuk support Kegiatan Operation &amp; Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026, Refer CTR No. 7207250142-BSS-CTR-2026-020" (01 - 31 Juli 2026)
+          <t xml:space="preserve">Jasa Sewa Backhoe Loader Untuk support Kegiatan Operation &amp; Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026, Refer CTR No. 7207250142-BSS-CTR-2026-019" (01 - 31 Juli 2026)
 </t>
         </is>
       </c>
@@ -763,7 +763,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg
+          <t xml:space="preserve">Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP
 </t>
         </is>
       </c>
@@ -789,10 +789,10 @@
         </is>
       </c>
       <c r="T3" t="n">
-        <v>62818000</v>
+        <v>75538000</v>
       </c>
       <c r="U3" t="n">
-        <v>62818000</v>
+        <v>75538000</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -821,12 +821,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Periode Pekerjaan 01 sd 31 Juli 2026</t>
+          <t>Periode Pekerjaan tgl 01 Juli sd 31 Juli 2026</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-08-16 20:58:40</t>
+          <t>2026-08-18 11:46:26</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_transaksi_rincian.xlsx
+++ b/database_penyimpanan_aman/database_transaksi_rincian.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB3"/>
+  <dimension ref="A1:AB2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -575,7 +575,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>043/BSS-JOB/AB/VII/2026</t>
+          <t>042/BSS-JOB/AB/VII/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -600,11 +600,11 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4500011425</v>
+        <v>4500011424</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jasa Sewa Man Lift Untuk support Kegiatan Operation &amp; Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026, Refer CTR No. 7207250142-BSS-CTR-2026-020" (01 - 31 Juli 2026)
+          <t xml:space="preserve">Jasa Sewa Backhoe Loader Untuk support Kegiatan Operation &amp; Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026, Refer CTR No. 7207250142-BSS-CTR-2026-019" (01 - 31 Juli 2026)
 </t>
         </is>
       </c>
@@ -625,7 +625,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg
+          <t xml:space="preserve">Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP
 </t>
         </is>
       </c>
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="T2" t="n">
-        <v>62818000</v>
+        <v>75538000</v>
       </c>
       <c r="U2" t="n">
-        <v>62818000</v>
+        <v>75538000</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -688,145 +688,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-08-16 20:58:40</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>7207250142</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka
-</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>S250551FLD-R1</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>042/BSS-JOB/AB/VII/2026</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>31 Jul 2026</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia
-</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>24 Month</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4500011424</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jasa Sewa Backhoe Loader Untuk support Kegiatan Operation &amp; Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026, Refer CTR No. 7207250142-BSS-CTR-2026-019" (01 - 31 Juli 2026)
-</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>1 Jul 2026</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>IDR</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>MONTHLY BASIS</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP
-</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>1</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>100</v>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>01 Jul 2026</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>31 Jul 2026</t>
-        </is>
-      </c>
-      <c r="T3" t="n">
-        <v>75538000</v>
-      </c>
-      <c r="U3" t="n">
-        <v>75538000</v>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Cabang Luwuk</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0167 0167 8888 303</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>PT. BANGGAI SENTRAL SULAWESI</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Accounts Payable - Finance Department</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Periode Pekerjaan tgl 01 Juli sd 31 Juli 2026</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>2026-08-18 11:46:26</t>
+          <t>2026-08-19 20:38:42</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_transaksi_rincian.xlsx
+++ b/database_penyimpanan_aman/database_transaksi_rincian.xlsx
@@ -559,8 +559,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>7207250142</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -599,8 +601,10 @@
           <t>24 Month</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>4500011424</v>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4500011424</t>
+        </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -688,7 +692,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-08-19 20:38:42</t>
+          <t>2026-08-20 12:48:46</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_transaksi_rincian.xlsx
+++ b/database_penyimpanan_aman/database_transaksi_rincian.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB2"/>
+  <dimension ref="A1:AB3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -559,10 +559,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>7207250142</t>
-        </is>
+      <c r="A2" t="n">
+        <v>7207250142</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -601,10 +599,8 @@
           <t>24 Month</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4500011424</t>
-        </is>
+      <c r="I2" t="n">
+        <v>4500011424</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -692,7 +688,145 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-08-20 12:48:46</t>
+          <t>2026-08-20 16:11:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka
+</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>S250551FLD-R1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>043/BSS-JOB/AB/VII/2026</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>31 Jul 2026</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia
+</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>24 Month</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4500011425</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jasa Sewa Man Lift Untuk support Kegiatan Operation &amp; Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026, Refer CTR No. 7207250142-BSS-CTR-2026-020" (01 - 31 Juli 2026)
+</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>1 Jul 2026</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>MONTHLY BASIS</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg
+</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>100</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>01 Jul 2026</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>31 Jul 2026</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>62818000</v>
+      </c>
+      <c r="U3" t="n">
+        <v>62818000</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Periode Pekerjaan 01 Juli sd 31 Juli 2026</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:11:05</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_transaksi_rincian.xlsx
+++ b/database_penyimpanan_aman/database_transaksi_rincian.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB3"/>
+  <dimension ref="A1:AB4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -688,15 +688,13 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:11:05</t>
+          <t>2026-08-21 16:04:43</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>7207250142</t>
-        </is>
+      <c r="A3" t="n">
+        <v>7207250142</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -735,10 +733,8 @@
           <t>24 Month</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4500011425</t>
-        </is>
+      <c r="I3" t="n">
+        <v>4500011425</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -826,7 +822,145 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-08-20 16:11:05</t>
+          <t>2026-08-21 16:04:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>7203250036</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Penyediaan Jasa Penyewaan Alat Berat Werehouse
+</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>S250009SCM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>010/BSS-JOB/WH/VII/2026</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>31 Jul 2026</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia
+</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>03 Desember 2027</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4500010848</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton
+</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2 Januari 2026</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>MONTHLY BASIS</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Daily Rate
+</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>18</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>100</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>01 Jul 2026</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>31 Jul 2026</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>1197000</v>
+      </c>
+      <c r="U4" t="n">
+        <v>21546000</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Forklift 5 Ton Operasi Tanggal 01 sd 31 Juli 2026 di Senoro 2</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:04:43</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_transaksi_rincian.xlsx
+++ b/database_penyimpanan_aman/database_transaksi_rincian.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB4"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -557,6 +557,41 @@
           <t>Update Terakhir</t>
         </is>
       </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>Nomor_Kontrak</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>Nama_Kontrak</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Nomor_Tender</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>PI_No.</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>Tanggal_PI</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>Ditujukan_Kepada</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>Items</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -688,9 +723,16 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:04:43</t>
-        </is>
-      </c>
+          <t>2026-08-21 22:07:41</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -822,9 +864,16 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-08-21 16:04:43</t>
-        </is>
-      </c>
+          <t>2026-08-21 22:07:41</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -876,8 +925,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton
-</t>
+          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -902,7 +950,7 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -926,7 +974,7 @@
         <v>1197000</v>
       </c>
       <c r="U4" t="n">
-        <v>21546000</v>
+        <v>27531000</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -955,14 +1003,21 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Forklift 5 Ton Operasi Tanggal 01 sd 31 Juli 2026 di Senoro 2</t>
+          <t>Periode 01 sd 31 Juli 2026</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:04:43</t>
-        </is>
-      </c>
+          <t>2026-08-21 22:07:41</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/database_penyimpanan_aman/database_transaksi_rincian.xlsx
+++ b/database_penyimpanan_aman/database_transaksi_rincian.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AI6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>042/BSS-JOB/AB/VII/2026</t>
+          <t>043/BSS-JOB/AB/VII/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -635,11 +635,11 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4500011424</v>
+        <v>4500011425</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jasa Sewa Backhoe Loader Untuk support Kegiatan Operation &amp; Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026, Refer CTR No. 7207250142-BSS-CTR-2026-019" (01 - 31 Juli 2026)
+          <t xml:space="preserve">Jasa Sewa Man Lift Untuk support Kegiatan Operation &amp; Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026, Refer CTR No. 7207250142-BSS-CTR-2026-020" (01 - 31 Juli 2026)
 </t>
         </is>
       </c>
@@ -660,7 +660,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP
+          <t xml:space="preserve">Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg
 </t>
         </is>
       </c>
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="T2" t="n">
-        <v>75538000</v>
+        <v>62818000</v>
       </c>
       <c r="U2" t="n">
-        <v>75538000</v>
+        <v>62818000</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -718,12 +718,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Periode Pekerjaan 01 sd 31 Juli 2026</t>
+          <t>Periode Pekerjaan 01 Juli sd 31 Juli 2026</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-08-21 22:07:41</t>
+          <t>2026-08-22 13:39:12</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -740,8 +740,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka
-</t>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -751,7 +750,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>043/BSS-JOB/AB/VII/2026</t>
+          <t>042/BSS-JOB/AB/VII/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -764,24 +763,14 @@
           <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia
-</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>24 Month</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>4500011425</v>
+        <v>4500011424</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jasa Sewa Man Lift Untuk support Kegiatan Operation &amp; Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026, Refer CTR No. 7207250142-BSS-CTR-2026-020" (01 - 31 Juli 2026)
-</t>
+          <t>Jasa Sewa Alat Berat Untuk support Kegiatan Operation &amp; Maintenance</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -801,8 +790,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg
-</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Truck Mounted Crane (TMC) Capacity 8 T</t>
         </is>
       </c>
       <c r="O3" t="n">
@@ -813,58 +801,36 @@
           <t>Month</t>
         </is>
       </c>
-      <c r="Q3" t="n">
-        <v>100</v>
-      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
-          <t>01 Jul 2026</t>
+          <t>01 Aug 2026</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="T3" t="n">
-        <v>62818000</v>
+        <v>131224000</v>
       </c>
       <c r="U3" t="n">
-        <v>62818000</v>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Cabang Luwuk</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0167 0167 8888 303</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>PT. BANGGAI SENTRAL SULAWESI</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Accounts Payable - Finance Department</t>
-        </is>
-      </c>
+        <v>131224000</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Periode Pekerjaan 01 Juli sd 31 Juli 2026</t>
+          <t>Alat Beroperasi Periode Juli 2026</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-08-21 22:07:41</t>
+          <t>2026-08-22 13:39:12</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -876,10 +842,8 @@
       <c r="AI3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>7203250036</t>
-        </is>
+      <c r="A4" t="n">
+        <v>7203250036</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -918,10 +882,8 @@
           <t>03 Desember 2027</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4500010848</t>
-        </is>
+      <c r="I4" t="n">
+        <v>4500010848</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -950,7 +912,7 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -974,7 +936,7 @@
         <v>1197000</v>
       </c>
       <c r="U4" t="n">
-        <v>27531000</v>
+        <v>21546000</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -1003,12 +965,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Periode 01 sd 31 Juli 2026</t>
+          <t>Forklift 5 ton, Operasi di CPP Senoro Periode 1 sd 31 Juli 2026</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-08-21 22:07:41</t>
+          <t>2026-08-22 13:39:12</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -1019,6 +981,285 @@
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7203250036</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Penyediaan Jasa Penyewaan Alat Berat Werehouse
+</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>S250009SCM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>010/BSS-JOB/WH/VII/2026</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>31 Jul 2026</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia
+</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>03 Desember 2027</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>4500010848</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2 Januari 2026</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>MONTHLY BASIS</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Daily Rate
+</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>18</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>100</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>01 Jul 2026</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>31 Jul 2026</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>1197000</v>
+      </c>
+      <c r="U5" t="n">
+        <v>21546000</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Forklift 5 ton, Operasi di  Werehouse Senoro 2 Periode 1 sd 31 Juli 2026 </t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>2026-08-22 13:39:12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7203250036</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Penyediaan Jasa Penyewaan Alat Berat Werehouse
+</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>S250009SCM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>010/BSS-JOB/WH/VII/2026</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>31 Jul 2026</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia
+</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>03 Desember 2027</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>4500010848</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2 Januari 2026</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>MONTHLY BASIS</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Standby Rate</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>100</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>01 Jul 2026</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>31 Jul 2026</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>598500</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1197000</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2 Unit Forklift Standby di CPP Senoro dan Werehouse Senoro 2 Periode 1 sd 31 Juli 2026 </t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>2026-08-22 13:39:12</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database_penyimpanan_aman/database_transaksi_rincian.xlsx
+++ b/database_penyimpanan_aman/database_transaksi_rincian.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI6"/>
+  <dimension ref="A1:AI17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -723,7 +723,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-08-22 13:39:12</t>
+          <t>2026-08-23 16:07:22</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -830,7 +830,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-08-22 13:39:12</t>
+          <t>2026-08-23 16:07:22</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -970,7 +970,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-08-22 13:39:12</t>
+          <t>2026-08-23 16:07:22</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-08-22 13:39:12</t>
+          <t>2026-08-23 16:07:22</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-08-22 13:39:12</t>
+          <t>2026-08-23 16:07:22</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -1260,6 +1260,1469 @@
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah
+</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>005/BSS-JOB/WS/V/2026</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>20 Juni 2026</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia
+</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>16</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>100</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>15 May 2026</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>18 May 2026</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
+        <v>200000</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Pengiriman Sampel Air Senoro Cluster B ke Jakarta </t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:07:22</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah
+</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>005/BSS-JOB/WS/V/2026</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>20 Juni 2026</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia
+</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Pallet</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>100</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>18 May 2026</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>18 May 2026</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U8" t="n">
+        <v>250000</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Pembuatan Pallet Sample Air</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:07:22</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah
+</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>005/BSS-JOB/WS/V/2026</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>20 Juni 2026</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia
+</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>100</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>18 May 2026</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>20 May 2026</t>
+        </is>
+      </c>
+      <c r="T9" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Pickup material dari Luwuk ke Bandara di Luwuk dan Bandara Jakarta - PT. Halliburton tgl 18 dan 20 Mei 2026</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:07:22</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah
+</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>005/BSS-JOB/WS/V/2026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>20 Juni 2026</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia
+</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Helper Local (Skilled)</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>2</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>100</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>18 May 2026</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>20 May 2026</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
+        <v>350000</v>
+      </c>
+      <c r="U10" t="n">
+        <v>700000</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Pengurusan Cargo di Luwuk - Bandara atas Nama Parman tgl 18 Mei 2026 dan  Pengurusan Cargo di Jakarta, Atas Nama Zaenal Abidin, tgl 20 Mei 2026</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:07:22</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>014/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>20 Juni 2026</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>MOVING SEA FREIGHT TRANSPORT</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Jasa repacking for Seafreight, estimasi ukuran pallet 100x100x100 cm</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Pallet</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>100</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>15 Jul 2026</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>15 Jul 2026</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="U11" t="n">
+        <v>6630000</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 Unit Pallet : dengan Ukuran 170x80x210 cm = 2,9 m3 190x150x75 cm = 2,1 m3 135x135x90 cm = 1,6 m3 </t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:07:22</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>014/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>20 Juni 2026</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>100</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>16 Jul 2026</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>16 Jul 2026</t>
+        </is>
+      </c>
+      <c r="T12" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Pengurusan Pickup Barang dari Senoro 2 ke Jetty Tangkian </t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:07:22</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>014/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>20 Juni 2026</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>LAND TRANSPORTATION</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Tankian Jetty atau sebaliknya c/w BBM &amp; driver</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>100</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>16 Jul 2026</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>16 Jul 2026</t>
+        </is>
+      </c>
+      <c r="T13" t="n">
+        <v>6440000</v>
+      </c>
+      <c r="U13" t="n">
+        <v>6440000</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Trucking Barang X-Mas Tree dari Senoro 2 ke Jetty di Tankian </t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:07:22</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>014/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>20 Juni 2026</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>forklift-loader cap min 5 Ton, call out, (hanya unit)</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>4</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>100</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>16 Jul 2026</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>11 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T14" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="U14" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Forklit di Palabuhan Tangkian, Surabaya,Jakarta, Batam </t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:07:22</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>014/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>20 Juni 2026</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>MOVING SEA FREIGHT TRANSPORT</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Surabaya - Luwuk/ Senoro atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>100</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>20 Jul 2026</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>27 Jul 2026</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>22400000</v>
+      </c>
+      <c r="U15" t="n">
+        <v>22400000</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Pengiriman Barang dengan Kapal Cargo dari Jetty tankian ke Pelabuhan tanjung perak di surabaya </t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:07:22</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>014/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>20 Juni 2026</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>TRANSPORTASI DARI SURABAYA KE JABODETABEK:</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Trailler 20 feet</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>100</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>28 Jul 2026</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>31 Jul 2026</t>
+        </is>
+      </c>
+      <c r="T16" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="U16" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Trucking 3 unit Pallet dari Pelabuhan Surabaya ke Pelabuhan di Jakarta </t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:07:22</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>014/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>20 Juni 2026</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>MOVING SEA FREIGHT TRANSPORT</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Jabodetabek - Batam atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>100</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>31 Jul 2026</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>11 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T17" t="n">
+        <v>22400000</v>
+      </c>
+      <c r="U17" t="n">
+        <v>22400000</v>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Pengiriman Barang dengan Kapal Cargo dari Pelabuhan di Jakarta ke Pelabuhan di Batam, door ke Penerima Barang </t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:07:22</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database_penyimpanan_aman/database_transaksi_rincian.xlsx
+++ b/database_penyimpanan_aman/database_transaksi_rincian.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI17"/>
+  <dimension ref="A1:AI24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -723,7 +723,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-08-23 16:07:22</t>
+          <t>2026-08-24 12:32:14</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -830,7 +830,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-08-23 16:07:22</t>
+          <t>2026-08-24 12:32:14</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -970,7 +970,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-08-23 16:07:22</t>
+          <t>2026-08-24 12:32:14</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-08-23 16:07:22</t>
+          <t>2026-08-24 12:32:14</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-08-23 16:07:22</t>
+          <t>2026-08-24 12:32:14</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-08-23 16:07:22</t>
+          <t>2026-08-24 12:32:14</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-08-23 16:07:22</t>
+          <t>2026-08-24 12:32:14</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-08-23 16:07:22</t>
+          <t>2026-08-24 12:32:14</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-08-23 16:07:22</t>
+          <t>2026-08-24 12:32:14</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
@@ -1793,10 +1793,8 @@
       <c r="AI10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A11" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1914,7 +1912,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-08-23 16:07:22</t>
+          <t>2026-08-24 12:32:14</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
@@ -1926,10 +1924,8 @@
       <c r="AI11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A12" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -2047,7 +2043,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-08-23 16:07:22</t>
+          <t>2026-08-24 12:32:14</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
@@ -2059,10 +2055,8 @@
       <c r="AI12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A13" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -2180,7 +2174,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-08-23 16:07:22</t>
+          <t>2026-08-24 12:32:14</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
@@ -2192,10 +2186,8 @@
       <c r="AI13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A14" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2313,7 +2305,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-08-23 16:07:22</t>
+          <t>2026-08-24 12:32:14</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr"/>
@@ -2325,10 +2317,8 @@
       <c r="AI14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A15" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2446,7 +2436,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-08-23 16:07:22</t>
+          <t>2026-08-24 12:32:14</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr"/>
@@ -2458,10 +2448,8 @@
       <c r="AI15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A16" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2579,7 +2567,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-08-23 16:07:22</t>
+          <t>2026-08-24 12:32:14</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
@@ -2591,10 +2579,8 @@
       <c r="AI16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A17" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2712,7 +2698,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-08-23 16:07:22</t>
+          <t>2026-08-24 12:32:14</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
@@ -2723,6 +2709,933 @@
       <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>008/BSS-JOB/WS/VII/2026</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>09 Juli 2026</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Kendaraan Operasional Support Team JOB Survey Lokasi di Senoro</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>4</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>100</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>06 Jul 2026</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>09 Jul 2026</t>
+        </is>
+      </c>
+      <c r="T18" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="U18" t="n">
+        <v>6400000</v>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Kendaraan Operasional Inova DN 1257 CL Support Team JOB Survey Lokasi di Senoro tgl 7 sd 9 Juli 2026</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>2026-08-24 12:32:14</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>4 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>100</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T19" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Pengambilan Material Pop Joint di Senoro 2 ke Luwuk </t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>2026-08-24 12:32:14</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>4 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Pallet</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>100</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T20" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U20" t="n">
+        <v>250000</v>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Pembuatan Pallet untuk Pop Joint </t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>2026-08-24 12:32:14</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>4 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Helper Local (Skilled)</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>2</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>100</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>04 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T21" t="n">
+        <v>350000</v>
+      </c>
+      <c r="U21" t="n">
+        <v>700000</v>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Personel Handling di Luwuk-Bandara 1 orang dan Jakarta-Bogor 1 orang </t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>2026-08-24 12:32:14</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>4 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>105</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>100</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>04 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T22" t="n">
+        <v>200000</v>
+      </c>
+      <c r="U22" t="n">
+        <v>21000000</v>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cargo Barang   Air Freight Material Pop Joint yang dikirim </t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>2026-08-24 12:32:14</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>4 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>JASA TRANSPORTASI DARI DAN KE BANDARA</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>100</v>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>04 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>04 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T23" t="n">
+        <v>3250000</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3250000</v>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>Pengiriman barang Pop Joint dari Bandara Cengkareng ke Bogor alamat  Lamda Multi Dinamika yard</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>2026-08-24 12:32:14</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>012/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>5 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4500011586</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Provisional Sum (At Cost + 15% Fee)</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>1</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>100</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>05 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>05 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T24" t="n">
+        <v>21000000</v>
+      </c>
+      <c r="U24" t="n">
+        <v>24150000</v>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>Pembayaran Biaya Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>2026-08-24 12:32:14</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database_penyimpanan_aman/database_transaksi_rincian.xlsx
+++ b/database_penyimpanan_aman/database_transaksi_rincian.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI24"/>
+  <dimension ref="A1:AI21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -594,13 +594,14 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>7207250142</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka
-</t>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -625,8 +626,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia
-</t>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -634,13 +634,14 @@
           <t>24 Month</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>4500011425</v>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4500011425</t>
+        </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jasa Sewa Man Lift Untuk support Kegiatan Operation &amp; Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026, Refer CTR No. 7207250142-BSS-CTR-2026-020" (01 - 31 Juli 2026)
-</t>
+          <t>Jasa Sewa Man Lift Untuk support Kegiatan Operation &amp; Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026, Refer CTR No. 7207250142-BSS-CTR-2026-020" (01 - 31 Juli 2026)</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -660,8 +661,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg
-</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -723,7 +723,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-08-24 12:32:14</t>
+          <t>2026-08-24 21:34:41</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -735,8 +735,10 @@
       <c r="AI2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>7207250142</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -765,8 +767,10 @@
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="n">
-        <v>4500011424</v>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4500011424</t>
+        </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -830,7 +834,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-08-24 12:32:14</t>
+          <t>2026-08-24 21:34:41</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -842,13 +846,14 @@
       <c r="AI3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>7203250036</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>7203250036</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Penyediaan Jasa Penyewaan Alat Berat Werehouse
-</t>
+          <t>Penyediaan Jasa Penyewaan Alat Berat Werehouse</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -873,8 +878,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia
-</t>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -882,8 +886,10 @@
           <t>03 Desember 2027</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>4500010848</v>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4500010848</t>
+        </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -907,8 +913,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Daily Rate
-</t>
+          <t>Daily Rate</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -970,7 +975,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-08-24 12:32:14</t>
+          <t>2026-08-24 21:34:41</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -982,13 +987,14 @@
       <c r="AI4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>7203250036</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>7203250036</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Penyediaan Jasa Penyewaan Alat Berat Werehouse
-</t>
+          <t>Penyediaan Jasa Penyewaan Alat Berat Werehouse</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1013,8 +1019,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia
-</t>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1022,8 +1027,10 @@
           <t>03 Desember 2027</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>4500010848</v>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4500010848</t>
+        </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -1047,8 +1054,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Daily Rate
-</t>
+          <t>Daily Rate</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -1105,12 +1111,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Forklift 5 ton, Operasi di  Werehouse Senoro 2 Periode 1 sd 31 Juli 2026 </t>
+          <t>Forklift 5 ton, Operasi di  Werehouse Senoro 2 Periode 1 sd 31 Juli 2026</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-08-24 12:32:14</t>
+          <t>2026-08-24 21:34:41</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -1122,13 +1128,14 @@
       <c r="AI5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>7203250036</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>7203250036</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Penyediaan Jasa Penyewaan Alat Berat Werehouse
-</t>
+          <t>Penyediaan Jasa Penyewaan Alat Berat Werehouse</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1153,8 +1160,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia
-</t>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1162,8 +1168,10 @@
           <t>03 Desember 2027</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>4500010848</v>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4500010848</t>
+        </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1244,12 +1252,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 2 Unit Forklift Standby di CPP Senoro dan Werehouse Senoro 2 Periode 1 sd 31 Juli 2026 </t>
+          <t>2 Unit Forklift Standby di CPP Senoro dan Werehouse Senoro 2 Periode 1 sd 31 Juli 2026</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-08-24 12:32:14</t>
+          <t>2026-08-24 21:34:41</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -1261,13 +1269,14 @@
       <c r="AI6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>7201250141</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah
-</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1277,7 +1286,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/WS/V/2026</t>
+          <t>014/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1292,8 +1301,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia
-</t>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1304,7 +1312,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
+          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1315,20 +1323,20 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>MOVING AIR FREIGHT TRANSPORT</t>
+          <t>MOVING SEA FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
+          <t>Jasa repacking for Seafreight, estimasi ukuran pallet 100x100x100 cm</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>16</v>
+        <v>6.63</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Pallet</t>
         </is>
       </c>
       <c r="Q7" t="n">
@@ -1336,19 +1344,19 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>15 May 2026</t>
+          <t>15 Jul 2026</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>18 May 2026</t>
+          <t>15 Jul 2026</t>
         </is>
       </c>
       <c r="T7" t="n">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="U7" t="n">
-        <v>3200000</v>
+        <v>6630000</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -1377,12 +1385,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Pengiriman Sampel Air Senoro Cluster B ke Jakarta </t>
+          <t>3 Unit Pallet : dengan Ukuran 170x80x210 cm = 2,9 m3 190x150x75 cm = 2,1 m3 135x135x90 cm = 1,6 m3</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-08-24 12:32:14</t>
+          <t>2026-08-24 21:34:41</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
@@ -1394,13 +1402,14 @@
       <c r="AI7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>7201250141</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah
-</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1410,7 +1419,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/WS/V/2026</t>
+          <t>014/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1425,8 +1434,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia
-</t>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1437,7 +1445,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
+          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1448,12 +1456,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>MOVING AIR FREIGHT TRANSPORT</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O8" t="n">
@@ -1461,7 +1469,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Pallet</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q8" t="n">
@@ -1469,19 +1477,19 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>18 May 2026</t>
+          <t>16 Jul 2026</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>18 May 2026</t>
+          <t>16 Jul 2026</t>
         </is>
       </c>
       <c r="T8" t="n">
-        <v>250000</v>
+        <v>1600000</v>
       </c>
       <c r="U8" t="n">
-        <v>250000</v>
+        <v>1600000</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -1510,12 +1518,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Pembuatan Pallet Sample Air</t>
+          <t>Pengurusan Pickup Barang dari Senoro 2 ke Jetty Tangkian</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-08-24 12:32:14</t>
+          <t>2026-08-24 21:34:41</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
@@ -1527,13 +1535,14 @@
       <c r="AI8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>7201250141</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah
-</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1543,7 +1552,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/WS/V/2026</t>
+          <t>014/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1558,8 +1567,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia
-</t>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1570,7 +1578,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
+          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1581,12 +1589,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Tankian Jetty atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="O9" t="n">
@@ -1594,7 +1602,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -1602,19 +1610,19 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>18 May 2026</t>
+          <t>16 Jul 2026</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>16 Jul 2026</t>
         </is>
       </c>
       <c r="T9" t="n">
-        <v>1600000</v>
+        <v>6440000</v>
       </c>
       <c r="U9" t="n">
-        <v>1600000</v>
+        <v>6440000</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1643,12 +1651,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Pickup material dari Luwuk ke Bandara di Luwuk dan Bandara Jakarta - PT. Halliburton tgl 18 dan 20 Mei 2026</t>
+          <t>Trucking Barang X-Mas Tree dari Senoro 2 ke Jetty di Tankian</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-08-24 12:32:14</t>
+          <t>2026-08-24 21:34:41</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -1660,13 +1668,14 @@
       <c r="AI9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>7201250141</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah
-</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1676,7 +1685,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/WS/V/2026</t>
+          <t>014/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1691,8 +1700,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia
-</t>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1703,7 +1711,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
+          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1714,20 +1722,20 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Helper Local (Skilled)</t>
+          <t>forklift-loader cap min 5 Ton, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -1735,19 +1743,19 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>18 May 2026</t>
+          <t>16 Jul 2026</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="T10" t="n">
-        <v>350000</v>
+        <v>3500000</v>
       </c>
       <c r="U10" t="n">
-        <v>700000</v>
+        <v>14000000</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1776,12 +1784,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Pengurusan Cargo di Luwuk - Bandara atas Nama Parman tgl 18 Mei 2026 dan  Pengurusan Cargo di Jakarta, Atas Nama Zaenal Abidin, tgl 20 Mei 2026</t>
+          <t>Forklit di Palabuhan Tangkian, Surabaya,Jakarta, Batam</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-08-24 12:32:14</t>
+          <t>2026-08-24 21:34:41</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
@@ -1793,8 +1801,10 @@
       <c r="AI10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>7201250141</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1850,15 +1860,15 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Jasa repacking for Seafreight, estimasi ukuran pallet 100x100x100 cm</t>
+          <t>Surabaya - Luwuk/ Senoro atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>6.63</v>
+        <v>1</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Pallet</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q11" t="n">
@@ -1866,19 +1876,19 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>15 Jul 2026</t>
+          <t>20 Jul 2026</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>15 Jul 2026</t>
+          <t>27 Jul 2026</t>
         </is>
       </c>
       <c r="T11" t="n">
-        <v>1000000</v>
+        <v>22400000</v>
       </c>
       <c r="U11" t="n">
-        <v>6630000</v>
+        <v>22400000</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -1907,12 +1917,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 Unit Pallet : dengan Ukuran 170x80x210 cm = 2,9 m3 190x150x75 cm = 2,1 m3 135x135x90 cm = 1,6 m3 </t>
+          <t>Pengiriman Barang dengan Kapal Cargo dari Jetty tankian ke Pelabuhan tanjung perak di surabaya</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-08-24 12:32:14</t>
+          <t>2026-08-24 21:34:41</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
@@ -1924,8 +1934,10 @@
       <c r="AI11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>7201250141</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1976,12 +1988,12 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>TRANSPORTASI DARI SURABAYA KE JABODETABEK:</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Trailler 20 feet</t>
         </is>
       </c>
       <c r="O12" t="n">
@@ -1989,7 +2001,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="Q12" t="n">
@@ -1997,19 +2009,19 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>16 Jul 2026</t>
+          <t>28 Jul 2026</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>16 Jul 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="T12" t="n">
-        <v>1600000</v>
+        <v>14000000</v>
       </c>
       <c r="U12" t="n">
-        <v>1600000</v>
+        <v>14000000</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -2038,12 +2050,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Pengurusan Pickup Barang dari Senoro 2 ke Jetty Tangkian </t>
+          <t>Trucking 3 unit Pallet dari Pelabuhan Surabaya ke Pelabuhan di Jakarta</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-08-24 12:32:14</t>
+          <t>2026-08-24 21:34:41</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
@@ -2055,8 +2067,10 @@
       <c r="AI12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>7201250141</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -2107,12 +2121,12 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>MOVING SEA FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Tankian Jetty atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Jabodetabek - Batam atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
         </is>
       </c>
       <c r="O13" t="n">
@@ -2128,19 +2142,19 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>16 Jul 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>16 Jul 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="T13" t="n">
-        <v>6440000</v>
+        <v>22400000</v>
       </c>
       <c r="U13" t="n">
-        <v>6440000</v>
+        <v>22400000</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -2169,12 +2183,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Trucking Barang X-Mas Tree dari Senoro 2 ke Jetty di Tankian </t>
+          <t>Pengiriman Barang dengan Kapal Cargo dari Pelabuhan di Jakarta ke Pelabuhan di Batam, door ke Penerima Barang</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-08-24 12:32:14</t>
+          <t>2026-08-24 21:34:41</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
@@ -2186,8 +2200,10 @@
       <c r="AI13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>7201250141</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2201,12 +2217,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>014/BSS-JOB/WS/VIII/2026</t>
+          <t>008/BSS-JOB/WS/VII/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>20 Juni 2026</t>
+          <t>09 Juli 2026</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2227,7 +2243,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+          <t>Kendaraan Operasional Support Team JOB Survey Lokasi di Senoro</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -2238,12 +2254,12 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>forklift-loader cap min 5 Ton, call out, (hanya unit)</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O14" t="n">
@@ -2259,19 +2275,19 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>16 Jul 2026</t>
+          <t>06 Jul 2026</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>11 Aug 2026</t>
+          <t>09 Jul 2026</t>
         </is>
       </c>
       <c r="T14" t="n">
-        <v>3500000</v>
+        <v>1600000</v>
       </c>
       <c r="U14" t="n">
-        <v>14000000</v>
+        <v>6400000</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -2300,12 +2316,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Forklit di Palabuhan Tangkian, Surabaya,Jakarta, Batam </t>
+          <t>Kendaraan Operasional Inova DN 1257 CL Support Team JOB Survey Lokasi di Senoro tgl 7 sd 9 Juli 2026</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-08-24 12:32:14</t>
+          <t>2026-08-24 21:34:41</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr"/>
@@ -2317,8 +2333,10 @@
       <c r="AI14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>7201250141</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2332,12 +2350,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>014/BSS-JOB/WS/VIII/2026</t>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>20 Juni 2026</t>
+          <t>4 Agustus 2026</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2358,7 +2376,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -2369,12 +2387,12 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>MOVING SEA FREIGHT TRANSPORT</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Surabaya - Luwuk/ Senoro atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O15" t="n">
@@ -2382,7 +2400,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q15" t="n">
@@ -2390,19 +2408,19 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>20 Jul 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>27 Jul 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="T15" t="n">
-        <v>22400000</v>
+        <v>1600000</v>
       </c>
       <c r="U15" t="n">
-        <v>22400000</v>
+        <v>1600000</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -2431,12 +2449,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Pengiriman Barang dengan Kapal Cargo dari Jetty tankian ke Pelabuhan tanjung perak di surabaya </t>
+          <t>Pengambilan Material Pop Joint di Senoro 2 ke Luwuk</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-08-24 12:32:14</t>
+          <t>2026-08-24 21:34:41</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr"/>
@@ -2448,8 +2466,10 @@
       <c r="AI15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>7201250141</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2463,12 +2483,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>014/BSS-JOB/WS/VIII/2026</t>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>20 Juni 2026</t>
+          <t>4 Agustus 2026</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2489,7 +2509,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -2500,12 +2520,12 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>TRANSPORTASI DARI SURABAYA KE JABODETABEK:</t>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Trailler 20 feet</t>
+          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
         </is>
       </c>
       <c r="O16" t="n">
@@ -2513,7 +2533,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Pallet</t>
         </is>
       </c>
       <c r="Q16" t="n">
@@ -2521,19 +2541,19 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>28 Jul 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="T16" t="n">
-        <v>14000000</v>
+        <v>250000</v>
       </c>
       <c r="U16" t="n">
-        <v>14000000</v>
+        <v>250000</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -2562,12 +2582,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Trucking 3 unit Pallet dari Pelabuhan Surabaya ke Pelabuhan di Jakarta </t>
+          <t>Pembuatan Pallet untuk Pop Joint</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-08-24 12:32:14</t>
+          <t>2026-08-24 21:34:41</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
@@ -2579,8 +2599,10 @@
       <c r="AI16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>7201250141</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2594,12 +2616,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>014/BSS-JOB/WS/VIII/2026</t>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20 Juni 2026</t>
+          <t>4 Agustus 2026</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2620,7 +2642,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -2631,20 +2653,20 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>MOVING SEA FREIGHT TRANSPORT</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Jabodetabek - Batam atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
+          <t>Helper Local (Skilled)</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="Q17" t="n">
@@ -2652,19 +2674,19 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>11 Aug 2026</t>
+          <t>04 Aug 2026</t>
         </is>
       </c>
       <c r="T17" t="n">
-        <v>22400000</v>
+        <v>350000</v>
       </c>
       <c r="U17" t="n">
-        <v>22400000</v>
+        <v>700000</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -2693,12 +2715,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Pengiriman Barang dengan Kapal Cargo dari Pelabuhan di Jakarta ke Pelabuhan di Batam, door ke Penerima Barang </t>
+          <t>Personel Handling di Luwuk-Bandara 1 orang dan Jakarta-Bogor 1 orang</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-08-24 12:32:14</t>
+          <t>2026-08-24 21:34:41</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
@@ -2710,8 +2732,10 @@
       <c r="AI17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>7201250141</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2725,12 +2749,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>008/BSS-JOB/WS/VII/2026</t>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>09 Juli 2026</t>
+          <t>4 Agustus 2026</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2751,7 +2775,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Kendaraan Operasional Support Team JOB Survey Lokasi di Senoro</t>
+          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -2762,20 +2786,20 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>4</v>
+        <v>105</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q18" t="n">
@@ -2783,19 +2807,19 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>06 Jul 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>09 Jul 2026</t>
+          <t>04 Aug 2026</t>
         </is>
       </c>
       <c r="T18" t="n">
-        <v>1600000</v>
+        <v>200000</v>
       </c>
       <c r="U18" t="n">
-        <v>6400000</v>
+        <v>21000000</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -2824,12 +2848,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Kendaraan Operasional Inova DN 1257 CL Support Team JOB Survey Lokasi di Senoro tgl 7 sd 9 Juli 2026</t>
+          <t>Cargo Barang   Air Freight Material Pop Joint yang dikirim</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-08-24 12:32:14</t>
+          <t>2026-08-24 21:34:41</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
@@ -2841,8 +2865,10 @@
       <c r="AI18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>7201250141</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2893,12 +2919,12 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>JASA TRANSPORTASI DARI DAN KE BANDARA</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
         </is>
       </c>
       <c r="O19" t="n">
@@ -2906,7 +2932,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="Q19" t="n">
@@ -2914,19 +2940,19 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>04 Aug 2026</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>04 Aug 2026</t>
         </is>
       </c>
       <c r="T19" t="n">
-        <v>1600000</v>
+        <v>3250000</v>
       </c>
       <c r="U19" t="n">
-        <v>1600000</v>
+        <v>3250000</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -2955,12 +2981,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Pengambilan Material Pop Joint di Senoro 2 ke Luwuk </t>
+          <t>Pengiriman barang Pop Joint dari Bandara Cengkareng ke Bogor alamat  Lamda Multi Dinamika yard</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-08-24 12:32:14</t>
+          <t>2026-08-24 21:34:41</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
@@ -2972,8 +2998,10 @@
       <c r="AI19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>7201250141</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2987,12 +3015,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
+          <t>012/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4 Agustus 2026</t>
+          <t>5 Agustus 2026</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -3010,13 +3038,21 @@
           <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>4500011586</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>IDR</t>
@@ -3024,12 +3060,12 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>MOVING AIR FREIGHT TRANSPORT</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
+          <t>Provisional Sum (At Cost + 15% Fee)</t>
         </is>
       </c>
       <c r="O20" t="n">
@@ -3037,7 +3073,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Pallet</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q20" t="n">
@@ -3045,19 +3081,19 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="T20" t="n">
-        <v>250000</v>
+        <v>21000000</v>
       </c>
       <c r="U20" t="n">
-        <v>250000</v>
+        <v>24150000</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -3086,12 +3122,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Pembuatan Pallet untuk Pop Joint </t>
+          <t>Pembayaran Biaya Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-08-24 12:32:14</t>
+          <t>2026-08-24 21:34:41</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
@@ -3103,8 +3139,10 @@
       <c r="AI20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>7201250141</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -3118,12 +3156,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
+          <t>005/BSS-JOB/WS/V/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>4 Agustus 2026</t>
+          <t>20 Juni 2026</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3144,7 +3182,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
+          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -3155,20 +3193,20 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Helper Local (Skilled)</t>
+          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q21" t="n">
@@ -3176,19 +3214,19 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>18 May 2026</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>04 Aug 2026</t>
+          <t>18 May 2026</t>
         </is>
       </c>
       <c r="T21" t="n">
-        <v>350000</v>
+        <v>200000</v>
       </c>
       <c r="U21" t="n">
-        <v>700000</v>
+        <v>3200000</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -3217,12 +3255,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Personel Handling di Luwuk-Bandara 1 orang dan Jakarta-Bogor 1 orang </t>
+          <t>Pengiriman Sample air dari Lokasi Cluster B ke Jakarta</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-08-24 12:32:14</t>
+          <t>2026-08-24 21:34:41</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
@@ -3233,409 +3271,6 @@
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="inlineStr"/>
     </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>7201250141</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>S25048TPD</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>4 Agustus 2026</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>IDR</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>MOVING AIR FREIGHT TRANSPORT</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
-        </is>
-      </c>
-      <c r="O22" t="n">
-        <v>105</v>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>100</v>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>03 Aug 2026</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>04 Aug 2026</t>
-        </is>
-      </c>
-      <c r="T22" t="n">
-        <v>200000</v>
-      </c>
-      <c r="U22" t="n">
-        <v>21000000</v>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Cabang Luwuk</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>0167 0167 8888 303</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>PT. BANGGAI SENTRAL SULAWESI</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>Accounts Payable - Finance Department</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cargo Barang   Air Freight Material Pop Joint yang dikirim </t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>2026-08-24 12:32:14</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr"/>
-      <c r="AD22" t="inlineStr"/>
-      <c r="AE22" t="inlineStr"/>
-      <c r="AF22" t="inlineStr"/>
-      <c r="AG22" t="inlineStr"/>
-      <c r="AH22" t="inlineStr"/>
-      <c r="AI22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>7201250141</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>S25048TPD</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>4 Agustus 2026</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>IDR</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>JASA TRANSPORTASI DARI DAN KE BANDARA</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
-        </is>
-      </c>
-      <c r="O23" t="n">
-        <v>1</v>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Trip</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>100</v>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>04 Aug 2026</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>04 Aug 2026</t>
-        </is>
-      </c>
-      <c r="T23" t="n">
-        <v>3250000</v>
-      </c>
-      <c r="U23" t="n">
-        <v>3250000</v>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Cabang Luwuk</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>0167 0167 8888 303</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>PT. BANGGAI SENTRAL SULAWESI</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>Accounts Payable - Finance Department</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>Pengiriman barang Pop Joint dari Bandara Cengkareng ke Bogor alamat  Lamda Multi Dinamika yard</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>2026-08-24 12:32:14</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr"/>
-      <c r="AD23" t="inlineStr"/>
-      <c r="AE23" t="inlineStr"/>
-      <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="inlineStr"/>
-      <c r="AH23" t="inlineStr"/>
-      <c r="AI23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>S25048TPD</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>012/BSS-JOB/WS/VIII/2026</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>5 Agustus 2026</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>4500011586</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>03 Aug 2026</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>IDR</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>PROVISIONAL SUM</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Provisional Sum (At Cost + 15% Fee)</t>
-        </is>
-      </c>
-      <c r="O24" t="n">
-        <v>1</v>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>100</v>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>05 Aug 2026</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>05 Aug 2026</t>
-        </is>
-      </c>
-      <c r="T24" t="n">
-        <v>21000000</v>
-      </c>
-      <c r="U24" t="n">
-        <v>24150000</v>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Cabang Luwuk</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>0167 0167 8888 303</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>PT. BANGGAI SENTRAL SULAWESI</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>Accounts Payable - Finance Department</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>Pembayaran Biaya Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>2026-08-24 12:32:14</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr"/>
-      <c r="AD24" t="inlineStr"/>
-      <c r="AE24" t="inlineStr"/>
-      <c r="AF24" t="inlineStr"/>
-      <c r="AG24" t="inlineStr"/>
-      <c r="AH24" t="inlineStr"/>
-      <c r="AI24" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database_penyimpanan_aman/database_transaksi_rincian.xlsx
+++ b/database_penyimpanan_aman/database_transaksi_rincian.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI21"/>
+  <dimension ref="A1:AI26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -594,10 +594,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>7207250142</t>
-        </is>
+      <c r="A2" t="n">
+        <v>7207250142</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -634,10 +632,8 @@
           <t>24 Month</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4500011425</t>
-        </is>
+      <c r="I2" t="n">
+        <v>4500011425</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -723,7 +719,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-08-24 21:34:41</t>
+          <t>2026-08-25 14:09:56</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -735,24 +731,22 @@
       <c r="AI2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>7207250142</t>
-        </is>
+      <c r="A3" t="n">
+        <v>7203250036</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+          <t>Penyediaan Jasa Penyewaan Alat Berat Werehouse</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>S250551FLD-R1</t>
+          <t>S250009SCM</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>042/BSS-JOB/AB/VII/2026</t>
+          <t>010/BSS-JOB/WH/VII/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -765,21 +759,27 @@
           <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4500011424</t>
-        </is>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>03 Desember 2027</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>4500010848</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Untuk support Kegiatan Operation &amp; Maintenance</t>
+          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1 Jul 2026</t>
+          <t>2 Januari 2026</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -794,47 +794,69 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Truck Mounted Crane (TMC) Capacity 8 T</t>
+          <t>Daily Rate</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr"/>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>100</v>
+      </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>01 Aug 2026</t>
+          <t>01 Jul 2026</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>31 Aug 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="T3" t="n">
-        <v>131224000</v>
+        <v>1197000</v>
       </c>
       <c r="U3" t="n">
-        <v>131224000</v>
-      </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
+        <v>21546000</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Alat Beroperasi Periode Juli 2026</t>
+          <t>Forklift 5 ton, Operasi di CPP Senoro Periode 1 sd 31 Juli 2026</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-08-24 21:34:41</t>
+          <t>2026-08-25 14:09:56</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -846,10 +868,8 @@
       <c r="AI3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>7203250036</t>
-        </is>
+      <c r="A4" t="n">
+        <v>7203250036</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -886,10 +906,8 @@
           <t>03 Desember 2027</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4500010848</t>
-        </is>
+      <c r="I4" t="n">
+        <v>4500010848</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -970,12 +988,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Forklift 5 ton, Operasi di CPP Senoro Periode 1 sd 31 Juli 2026</t>
+          <t>Forklift 5 ton, Operasi di  Werehouse Senoro 2 Periode 1 sd 31 Juli 2026</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-08-24 21:34:41</t>
+          <t>2026-08-25 14:09:56</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -987,10 +1005,8 @@
       <c r="AI4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>7203250036</t>
-        </is>
+      <c r="A5" t="n">
+        <v>7203250036</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1027,10 +1043,8 @@
           <t>03 Desember 2027</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4500010848</t>
-        </is>
+      <c r="I5" t="n">
+        <v>4500010848</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -1054,15 +1068,15 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Daily Rate</t>
+          <t>Standby Rate</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ls</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -1079,11 +1093,11 @@
         </is>
       </c>
       <c r="T5" t="n">
+        <v>598500</v>
+      </c>
+      <c r="U5" t="n">
         <v>1197000</v>
       </c>
-      <c r="U5" t="n">
-        <v>21546000</v>
-      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
@@ -1111,12 +1125,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Forklift 5 ton, Operasi di  Werehouse Senoro 2 Periode 1 sd 31 Juli 2026</t>
+          <t>2 Unit Forklift Standby di CPP Senoro dan Werehouse Senoro 2 Periode 1 sd 31 Juli 2026</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-08-24 21:34:41</t>
+          <t>2026-08-25 14:09:56</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -1128,29 +1142,27 @@
       <c r="AI5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>7203250036</t>
-        </is>
+      <c r="A6" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Penyediaan Jasa Penyewaan Alat Berat Werehouse</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>S250009SCM</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>010/BSS-JOB/WH/VII/2026</t>
+          <t>014/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>20 Juni 2026</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1165,24 +1177,16 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>03 Desember 2027</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4500010848</t>
-        </is>
-      </c>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2 Januari 2026</t>
-        </is>
-      </c>
+          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>IDR</t>
@@ -1190,20 +1194,20 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>MOVING SEA FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Standby Rate</t>
+          <t>Jasa repacking for Seafreight, estimasi ukuran pallet 100x100x100 cm</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>6.63</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ls</t>
+          <t>Pallet</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -1211,19 +1215,19 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>01 Jul 2026</t>
+          <t>15 Jul 2026</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>15 Jul 2026</t>
         </is>
       </c>
       <c r="T6" t="n">
-        <v>598500</v>
+        <v>1000000</v>
       </c>
       <c r="U6" t="n">
-        <v>1197000</v>
+        <v>6630000</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1252,12 +1256,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2 Unit Forklift Standby di CPP Senoro dan Werehouse Senoro 2 Periode 1 sd 31 Juli 2026</t>
+          <t>3 Unit Pallet : dengan Ukuran 170x80x210 cm = 2,9 m3 190x150x75 cm = 2,1 m3 135x135x90 cm = 1,6 m3</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-08-24 21:34:41</t>
+          <t>2026-08-25 14:09:56</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -1269,10 +1273,8 @@
       <c r="AI6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A7" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1323,20 +1325,20 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>MOVING SEA FREIGHT TRANSPORT</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Jasa repacking for Seafreight, estimasi ukuran pallet 100x100x100 cm</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>6.63</v>
+        <v>1</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Pallet</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q7" t="n">
@@ -1344,19 +1346,19 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>15 Jul 2026</t>
+          <t>16 Jul 2026</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>15 Jul 2026</t>
+          <t>16 Jul 2026</t>
         </is>
       </c>
       <c r="T7" t="n">
-        <v>1000000</v>
+        <v>1600000</v>
       </c>
       <c r="U7" t="n">
-        <v>6630000</v>
+        <v>1600000</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -1385,12 +1387,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3 Unit Pallet : dengan Ukuran 170x80x210 cm = 2,9 m3 190x150x75 cm = 2,1 m3 135x135x90 cm = 1,6 m3</t>
+          <t>Pengurusan Pickup Barang dari Senoro 2 ke Jetty Tangkian</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-08-24 21:34:41</t>
+          <t>2026-08-25 14:09:56</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
@@ -1402,10 +1404,8 @@
       <c r="AI7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A8" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1456,12 +1456,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Tankian Jetty atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="O8" t="n">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q8" t="n">
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="T8" t="n">
-        <v>1600000</v>
+        <v>6440000</v>
       </c>
       <c r="U8" t="n">
-        <v>1600000</v>
+        <v>6440000</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -1518,12 +1518,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Pengurusan Pickup Barang dari Senoro 2 ke Jetty Tangkian</t>
+          <t>Trucking Barang X-Mas Tree dari Senoro 2 ke Jetty di Tankian</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-08-24 21:34:41</t>
+          <t>2026-08-25 14:09:56</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
@@ -1535,10 +1535,8 @@
       <c r="AI8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A9" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1589,20 +1587,20 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Tankian Jetty atau sebaliknya c/w BBM &amp; driver</t>
+          <t>forklift-loader cap min 5 Ton, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -1615,14 +1613,14 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>16 Jul 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="T9" t="n">
-        <v>6440000</v>
+        <v>3500000</v>
       </c>
       <c r="U9" t="n">
-        <v>6440000</v>
+        <v>14000000</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1651,12 +1649,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Trucking Barang X-Mas Tree dari Senoro 2 ke Jetty di Tankian</t>
+          <t>Forklit di Palabuhan Tangkian, Surabaya,Jakarta, Batam</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-08-24 21:34:41</t>
+          <t>2026-08-25 14:09:56</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -1668,10 +1666,8 @@
       <c r="AI9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A10" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1722,20 +1718,20 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>MOVING SEA FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>forklift-loader cap min 5 Ton, call out, (hanya unit)</t>
+          <t>Surabaya - Luwuk/ Senoro atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -1743,19 +1739,19 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>16 Jul 2026</t>
+          <t>20 Jul 2026</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>11 Aug 2026</t>
+          <t>27 Jul 2026</t>
         </is>
       </c>
       <c r="T10" t="n">
-        <v>3500000</v>
+        <v>22400000</v>
       </c>
       <c r="U10" t="n">
-        <v>14000000</v>
+        <v>22400000</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1784,12 +1780,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Forklit di Palabuhan Tangkian, Surabaya,Jakarta, Batam</t>
+          <t>Pengiriman Barang dengan Kapal Cargo dari Jetty tankian ke Pelabuhan tanjung perak di surabaya</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-08-24 21:34:41</t>
+          <t>2026-08-25 14:09:56</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
@@ -1801,10 +1797,8 @@
       <c r="AI10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A11" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1855,12 +1849,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>MOVING SEA FREIGHT TRANSPORT</t>
+          <t>TRANSPORTASI DARI SURABAYA KE JABODETABEK:</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Surabaya - Luwuk/ Senoro atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
+          <t>Trailler 20 feet</t>
         </is>
       </c>
       <c r="O11" t="n">
@@ -1868,7 +1862,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="Q11" t="n">
@@ -1876,19 +1870,19 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>20 Jul 2026</t>
+          <t>28 Jul 2026</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>27 Jul 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="T11" t="n">
-        <v>22400000</v>
+        <v>14000000</v>
       </c>
       <c r="U11" t="n">
-        <v>22400000</v>
+        <v>14000000</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -1917,12 +1911,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Pengiriman Barang dengan Kapal Cargo dari Jetty tankian ke Pelabuhan tanjung perak di surabaya</t>
+          <t>Trucking 3 unit Pallet dari Pelabuhan Surabaya ke Pelabuhan di Jakarta</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-08-24 21:34:41</t>
+          <t>2026-08-25 14:09:56</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
@@ -1934,10 +1928,8 @@
       <c r="AI11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A12" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1988,12 +1980,12 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>TRANSPORTASI DARI SURABAYA KE JABODETABEK:</t>
+          <t>MOVING SEA FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Trailler 20 feet</t>
+          <t>Jabodetabek - Batam atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
         </is>
       </c>
       <c r="O12" t="n">
@@ -2001,7 +1993,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q12" t="n">
@@ -2009,19 +2001,19 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>28 Jul 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="T12" t="n">
-        <v>14000000</v>
+        <v>22400000</v>
       </c>
       <c r="U12" t="n">
-        <v>14000000</v>
+        <v>22400000</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -2050,12 +2042,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Trucking 3 unit Pallet dari Pelabuhan Surabaya ke Pelabuhan di Jakarta</t>
+          <t>Pengiriman Barang dengan Kapal Cargo dari Pelabuhan di Jakarta ke Pelabuhan di Batam, door ke Penerima Barang</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-08-24 21:34:41</t>
+          <t>2026-08-25 14:09:56</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
@@ -2067,10 +2059,8 @@
       <c r="AI12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A13" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -2084,12 +2074,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>014/BSS-JOB/WS/VIII/2026</t>
+          <t>012/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>20 Juni 2026</t>
+          <t>5 Agustus 2026</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2107,13 +2097,19 @@
           <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>4500011586</v>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>IDR</t>
@@ -2121,12 +2117,12 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>MOVING SEA FREIGHT TRANSPORT</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Jabodetabek - Batam atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
+          <t>Provisional Sum (At Cost + 15% Fee)</t>
         </is>
       </c>
       <c r="O13" t="n">
@@ -2142,19 +2138,19 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>11 Aug 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="T13" t="n">
-        <v>22400000</v>
+        <v>21000000</v>
       </c>
       <c r="U13" t="n">
-        <v>22400000</v>
+        <v>24150000</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -2183,12 +2179,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Pengiriman Barang dengan Kapal Cargo dari Pelabuhan di Jakarta ke Pelabuhan di Batam, door ke Penerima Barang</t>
+          <t>Pembayaran Biaya Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-08-24 21:34:41</t>
+          <t>2026-08-25 14:09:56</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
@@ -2200,10 +2196,8 @@
       <c r="AI13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A14" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2217,12 +2211,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>008/BSS-JOB/WS/VII/2026</t>
+          <t>005/BSS-JOB/WS/V/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>09 Juli 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2243,7 +2237,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Kendaraan Operasional Support Team JOB Survey Lokasi di Senoro</t>
+          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -2254,20 +2248,20 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q14" t="n">
@@ -2275,19 +2269,19 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>06 Jul 2026</t>
+          <t>18 May 2026</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>09 Jul 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="T14" t="n">
-        <v>1600000</v>
+        <v>200000</v>
       </c>
       <c r="U14" t="n">
-        <v>6400000</v>
+        <v>3200000</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -2316,12 +2310,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Kendaraan Operasional Inova DN 1257 CL Support Team JOB Survey Lokasi di Senoro tgl 7 sd 9 Juli 2026</t>
+          <t>Pengiriman Sample air dari Lokasi Cluster B ke Jakarta</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-08-24 21:34:41</t>
+          <t>2026-08-25 14:09:56</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr"/>
@@ -2333,10 +2327,8 @@
       <c r="AI14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A15" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2350,12 +2342,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
+          <t>005/BSS-JOB/WS/V/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4 Agustus 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2376,7 +2368,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
+          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -2387,12 +2379,12 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
         </is>
       </c>
       <c r="O15" t="n">
@@ -2400,7 +2392,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Pallet</t>
         </is>
       </c>
       <c r="Q15" t="n">
@@ -2408,19 +2400,19 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>18 May 2026</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>18 May 2026</t>
         </is>
       </c>
       <c r="T15" t="n">
-        <v>1600000</v>
+        <v>250000</v>
       </c>
       <c r="U15" t="n">
-        <v>1600000</v>
+        <v>250000</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -2449,12 +2441,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Pengambilan Material Pop Joint di Senoro 2 ke Luwuk</t>
+          <t>Pembuatan Pallet Sample Air (packing Barang)</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-08-24 21:34:41</t>
+          <t>2026-08-25 14:09:56</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr"/>
@@ -2466,10 +2458,8 @@
       <c r="AI15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A16" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2483,12 +2473,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
+          <t>005/BSS-JOB/WS/V/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4 Agustus 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2509,7 +2499,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
+          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -2520,12 +2510,12 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>MOVING AIR FREIGHT TRANSPORT</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O16" t="n">
@@ -2533,7 +2523,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Pallet</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q16" t="n">
@@ -2541,19 +2531,19 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>18 May 2026</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>18 May 2026</t>
         </is>
       </c>
       <c r="T16" t="n">
-        <v>250000</v>
+        <v>1600000</v>
       </c>
       <c r="U16" t="n">
-        <v>250000</v>
+        <v>1600000</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -2582,12 +2572,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Pembuatan Pallet untuk Pop Joint</t>
+          <t>Pickup Material di Luwuk tgl 18 Mei 2026 dari Lokasi ke Bandara</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-08-24 21:34:41</t>
+          <t>2026-08-25 14:09:56</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
@@ -2599,10 +2589,8 @@
       <c r="AI16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A17" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2616,12 +2604,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
+          <t>005/BSS-JOB/WS/V/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4 Agustus 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2642,7 +2630,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
+          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -2674,12 +2662,12 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>18 May 2026</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>04 Aug 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="T17" t="n">
@@ -2715,12 +2703,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Personel Handling di Luwuk-Bandara 1 orang dan Jakarta-Bogor 1 orang</t>
+          <t>Personel untuk pengurusan Barang di Luwuk dan Personel untuk pengurusan barang di Jakarta</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-08-24 21:34:41</t>
+          <t>2026-08-25 14:09:56</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
@@ -2732,10 +2720,8 @@
       <c r="AI17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A18" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2749,12 +2735,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
+          <t>005/BSS-JOB/WS/V/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4 Agustus 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2775,7 +2761,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
+          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -2786,20 +2772,20 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>MOVING AIR FREIGHT TRANSPORT</t>
+          <t>JASA TRANSPORTASI DARI DAN KE BANDARA</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
+          <t>Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>105</v>
+        <v>1</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="Q18" t="n">
@@ -2807,19 +2793,19 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>04 Aug 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="T18" t="n">
-        <v>200000</v>
+        <v>3250000</v>
       </c>
       <c r="U18" t="n">
-        <v>21000000</v>
+        <v>3250000</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -2848,12 +2834,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Cargo Barang   Air Freight Material Pop Joint yang dikirim</t>
+          <t>Land transportasi dari bandara Cengkareng ke alamat penerima sample air PT.Haliburton</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-08-24 21:34:41</t>
+          <t>2026-08-25 14:09:56</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
@@ -2865,10 +2851,8 @@
       <c r="AI18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A19" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2882,12 +2866,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
+          <t>008/BSS-JOB/WS/VII/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>4 Agustus 2026</t>
+          <t>09 Jul 2026</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2908,7 +2892,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
+          <t>Kendaraan Operasional Support Team JOB Survey Lokasi di Senoro</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -2919,20 +2903,20 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>JASA TRANSPORTASI DARI DAN KE BANDARA</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q19" t="n">
@@ -2940,19 +2924,19 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>04 Aug 2026</t>
+          <t>06 Jul 2026</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>04 Aug 2026</t>
+          <t>09 Jul 2026</t>
         </is>
       </c>
       <c r="T19" t="n">
-        <v>3250000</v>
+        <v>1600000</v>
       </c>
       <c r="U19" t="n">
-        <v>3250000</v>
+        <v>6400000</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -2981,12 +2965,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Pengiriman barang Pop Joint dari Bandara Cengkareng ke Bogor alamat  Lamda Multi Dinamika yard</t>
+          <t>Kendaraan Operasional Inova DN 1257 CL Support Team JOB Survey Lokasi di Senoro tgl 6 sd 9 Juli 2026</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-08-24 21:34:41</t>
+          <t>2026-08-25 14:09:56</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
@@ -2998,10 +2982,8 @@
       <c r="AI19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A20" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -3015,12 +2997,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>012/BSS-JOB/WS/VIII/2026</t>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>5 Agustus 2026</t>
+          <t>4 Agustus 2026</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -3038,21 +3020,13 @@
           <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>4500011586</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>03 Aug 2026</t>
-        </is>
-      </c>
+          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>IDR</t>
@@ -3060,12 +3034,12 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Provisional Sum (At Cost + 15% Fee)</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O20" t="n">
@@ -3073,7 +3047,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q20" t="n">
@@ -3081,19 +3055,19 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="T20" t="n">
-        <v>21000000</v>
+        <v>1600000</v>
       </c>
       <c r="U20" t="n">
-        <v>24150000</v>
+        <v>1600000</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -3122,12 +3096,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>Pembayaran Biaya Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
+          <t>Pengambilan Material Pop Joint di Senoro 2 ke Luwuk</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-08-24 21:34:41</t>
+          <t>2026-08-25 14:09:56</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
@@ -3139,10 +3113,8 @@
       <c r="AI20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A21" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -3156,12 +3128,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/WS/V/2026</t>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>20 Juni 2026</t>
+          <t>4 Agustus 2026</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3182,7 +3154,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
+          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -3198,15 +3170,15 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
+          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Pallet</t>
         </is>
       </c>
       <c r="Q21" t="n">
@@ -3214,19 +3186,19 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>18 May 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>18 May 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="T21" t="n">
-        <v>200000</v>
+        <v>250000</v>
       </c>
       <c r="U21" t="n">
-        <v>3200000</v>
+        <v>250000</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -3255,12 +3227,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>Pengiriman Sample air dari Lokasi Cluster B ke Jakarta</t>
+          <t>Pembuatan Pallet untuk Pop Joint</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-08-24 21:34:41</t>
+          <t>2026-08-25 14:09:56</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
@@ -3271,6 +3243,681 @@
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>4 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Helper Local (Skilled)</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>2</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>100</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>04 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T22" t="n">
+        <v>350000</v>
+      </c>
+      <c r="U22" t="n">
+        <v>700000</v>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>Personel Handling di Luwuk-Bandara 1 orang dan Jakarta-Bogor 1 orang</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>2026-08-25 14:09:56</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>4 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>105</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>100</v>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>04 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T23" t="n">
+        <v>200000</v>
+      </c>
+      <c r="U23" t="n">
+        <v>21000000</v>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>Cargo Barang   Air Freight Material Pop Joint yang dikirim</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>2026-08-25 14:09:56</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>4 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>JASA TRANSPORTASI DARI DAN KE BANDARA</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>1</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>100</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>04 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>04 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T24" t="n">
+        <v>3250000</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3250000</v>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>Pengiriman barang Pop Joint dari Bandara Cengkareng ke Bogor alamat  Lamda Multi Dinamika yard</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>2026-08-25 14:09:56</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>015/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>5 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>4500011587</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Data Uji Coba</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Provisional Sum (At Cost + 15% Fee)</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>1</v>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>100</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>25 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>25 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T25" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="U25" t="n">
+        <v>11500000</v>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Harga 1 buah Pompa Air </t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>2026-08-25 14:09:56</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>015/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>5 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>4500011587</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Data Uji Coba</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Provisional Sum (At Cost + 15% Fee)</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>100</v>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>25 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>25 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T26" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>Kabel Ukuran 2x2.5 mm panjang 50 Meter untuk Proyek</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>2026-08-25 14:09:56</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database_penyimpanan_aman/database_transaksi_rincian.xlsx
+++ b/database_penyimpanan_aman/database_transaksi_rincian.xlsx
@@ -594,8 +594,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>7207250142</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -632,8 +634,10 @@
           <t>24 Month</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>4500011425</v>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4500011425</t>
+        </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -719,7 +723,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-08-25 14:09:56</t>
+          <t>2026-08-25 21:59:34</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -731,8 +735,10 @@
       <c r="AI2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>7203250036</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>7203250036</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -769,8 +775,10 @@
           <t>03 Desember 2027</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>4500010848</v>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4500010848</t>
+        </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -856,7 +864,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-08-25 14:09:56</t>
+          <t>2026-08-25 21:59:34</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -868,8 +876,10 @@
       <c r="AI3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>7203250036</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>7203250036</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -906,8 +916,10 @@
           <t>03 Desember 2027</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>4500010848</v>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4500010848</t>
+        </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -993,7 +1005,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-08-25 14:09:56</t>
+          <t>2026-08-25 21:59:34</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -1005,8 +1017,10 @@
       <c r="AI4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>7203250036</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>7203250036</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1043,8 +1057,10 @@
           <t>03 Desember 2027</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>4500010848</v>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4500010848</t>
+        </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -1130,7 +1146,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-08-25 14:09:56</t>
+          <t>2026-08-25 21:59:34</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -1142,8 +1158,10 @@
       <c r="AI5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>7201250141</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1157,12 +1175,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>014/BSS-JOB/WS/VIII/2026</t>
+          <t>012/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20 Juni 2026</t>
+          <t>5 Agustus 2026</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1180,13 +1198,21 @@
           <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4500011586</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>IDR</t>
@@ -1194,20 +1220,20 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>MOVING SEA FREIGHT TRANSPORT</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Jasa repacking for Seafreight, estimasi ukuran pallet 100x100x100 cm</t>
+          <t>Provisional Sum (At Cost + 15% Fee)</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>6.63</v>
+        <v>1</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Pallet</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -1215,19 +1241,19 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>15 Jul 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>15 Jul 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="T6" t="n">
-        <v>1000000</v>
+        <v>21000000</v>
       </c>
       <c r="U6" t="n">
-        <v>6630000</v>
+        <v>24150000</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1256,12 +1282,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3 Unit Pallet : dengan Ukuran 170x80x210 cm = 2,9 m3 190x150x75 cm = 2,1 m3 135x135x90 cm = 1,6 m3</t>
+          <t>Pembayaran Biaya Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-08-25 14:09:56</t>
+          <t>2026-08-25 21:59:34</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -1273,8 +1299,10 @@
       <c r="AI6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>7201250141</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1288,12 +1316,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>014/BSS-JOB/WS/VIII/2026</t>
+          <t>005/BSS-JOB/WS/V/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20 Juni 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1314,7 +1342,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1325,20 +1353,20 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q7" t="n">
@@ -1346,19 +1374,19 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>16 Jul 2026</t>
+          <t>18 May 2026</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>16 Jul 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="T7" t="n">
-        <v>1600000</v>
+        <v>200000</v>
       </c>
       <c r="U7" t="n">
-        <v>1600000</v>
+        <v>3200000</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -1387,12 +1415,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Pengurusan Pickup Barang dari Senoro 2 ke Jetty Tangkian</t>
+          <t>Pengiriman Sample air dari Lokasi Cluster B ke Jakarta</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-08-25 14:09:56</t>
+          <t>2026-08-25 21:59:34</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
@@ -1404,8 +1432,10 @@
       <c r="AI7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>7201250141</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1419,12 +1449,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>014/BSS-JOB/WS/VIII/2026</t>
+          <t>005/BSS-JOB/WS/V/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20 Juni 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1445,7 +1475,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1456,12 +1486,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Tankian Jetty atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
         </is>
       </c>
       <c r="O8" t="n">
@@ -1469,7 +1499,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Pallet</t>
         </is>
       </c>
       <c r="Q8" t="n">
@@ -1477,19 +1507,19 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>16 Jul 2026</t>
+          <t>18 May 2026</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>16 Jul 2026</t>
+          <t>18 May 2026</t>
         </is>
       </c>
       <c r="T8" t="n">
-        <v>6440000</v>
+        <v>250000</v>
       </c>
       <c r="U8" t="n">
-        <v>6440000</v>
+        <v>250000</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -1518,12 +1548,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Trucking Barang X-Mas Tree dari Senoro 2 ke Jetty di Tankian</t>
+          <t>Pembuatan Pallet Sample Air (packing Barang)</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-08-25 14:09:56</t>
+          <t>2026-08-25 21:59:34</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
@@ -1535,8 +1565,10 @@
       <c r="AI8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>7201250141</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1550,12 +1582,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>014/BSS-JOB/WS/VIII/2026</t>
+          <t>005/BSS-JOB/WS/V/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20 Juni 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1576,7 +1608,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1587,16 +1619,16 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>forklift-loader cap min 5 Ton, call out, (hanya unit)</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -1608,19 +1640,19 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>16 Jul 2026</t>
+          <t>18 May 2026</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>11 Aug 2026</t>
+          <t>18 May 2026</t>
         </is>
       </c>
       <c r="T9" t="n">
-        <v>3500000</v>
+        <v>1600000</v>
       </c>
       <c r="U9" t="n">
-        <v>14000000</v>
+        <v>1600000</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1649,12 +1681,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Forklit di Palabuhan Tangkian, Surabaya,Jakarta, Batam</t>
+          <t>Pickup Material di Luwuk tgl 18 Mei 2026 dari Lokasi ke Bandara</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-08-25 14:09:56</t>
+          <t>2026-08-25 21:59:34</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -1666,8 +1698,10 @@
       <c r="AI9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>7201250141</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1681,12 +1715,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>014/BSS-JOB/WS/VIII/2026</t>
+          <t>005/BSS-JOB/WS/V/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>20 Juni 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1707,7 +1741,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1718,20 +1752,20 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>MOVING SEA FREIGHT TRANSPORT</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Surabaya - Luwuk/ Senoro atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
+          <t>Helper Local (Skilled)</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -1739,19 +1773,19 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>20 Jul 2026</t>
+          <t>18 May 2026</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>27 Jul 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="T10" t="n">
-        <v>22400000</v>
+        <v>350000</v>
       </c>
       <c r="U10" t="n">
-        <v>22400000</v>
+        <v>700000</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1780,12 +1814,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Pengiriman Barang dengan Kapal Cargo dari Jetty tankian ke Pelabuhan tanjung perak di surabaya</t>
+          <t>Personel untuk pengurusan Barang di Luwuk dan Personel untuk pengurusan barang di Jakarta</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-08-25 14:09:56</t>
+          <t>2026-08-25 21:59:34</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
@@ -1797,8 +1831,10 @@
       <c r="AI10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>7201250141</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1812,12 +1848,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>014/BSS-JOB/WS/VIII/2026</t>
+          <t>005/BSS-JOB/WS/V/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20 Juni 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1838,7 +1874,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1849,12 +1885,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>TRANSPORTASI DARI SURABAYA KE JABODETABEK:</t>
+          <t>JASA TRANSPORTASI DARI DAN KE BANDARA</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Trailler 20 feet</t>
+          <t>Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
         </is>
       </c>
       <c r="O11" t="n">
@@ -1870,19 +1906,19 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>28 Jul 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="T11" t="n">
-        <v>14000000</v>
+        <v>3250000</v>
       </c>
       <c r="U11" t="n">
-        <v>14000000</v>
+        <v>3250000</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -1911,12 +1947,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Trucking 3 unit Pallet dari Pelabuhan Surabaya ke Pelabuhan di Jakarta</t>
+          <t>Land transportasi dari bandara Cengkareng ke alamat penerima sample air PT.Haliburton</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-08-25 14:09:56</t>
+          <t>2026-08-25 21:59:34</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
@@ -1928,8 +1964,10 @@
       <c r="AI11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>7201250141</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1943,12 +1981,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>014/BSS-JOB/WS/VIII/2026</t>
+          <t>008/BSS-JOB/WS/VII/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20 Juni 2026</t>
+          <t>09 Jul 2026</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1969,7 +2007,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+          <t>Kendaraan Operasional Support Team JOB Survey Lokasi di Senoro</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1980,20 +2018,20 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>MOVING SEA FREIGHT TRANSPORT</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Jabodetabek - Batam atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q12" t="n">
@@ -2001,19 +2039,19 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>06 Jul 2026</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>11 Aug 2026</t>
+          <t>09 Jul 2026</t>
         </is>
       </c>
       <c r="T12" t="n">
-        <v>22400000</v>
+        <v>1600000</v>
       </c>
       <c r="U12" t="n">
-        <v>22400000</v>
+        <v>6400000</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -2042,12 +2080,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Pengiriman Barang dengan Kapal Cargo dari Pelabuhan di Jakarta ke Pelabuhan di Batam, door ke Penerima Barang</t>
+          <t>Kendaraan Operasional Inova DN 1257 CL Support Team JOB Survey Lokasi di Senoro tgl 6 sd 9 Juli 2026</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-08-25 14:09:56</t>
+          <t>2026-08-25 21:59:34</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
@@ -2059,8 +2097,10 @@
       <c r="AI12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>7201250141</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -2074,12 +2114,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>012/BSS-JOB/WS/VIII/2026</t>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>5 Agustus 2026</t>
+          <t>4 Agustus 2026</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2097,19 +2137,13 @@
           <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>4500011586</v>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>03 Aug 2026</t>
-        </is>
-      </c>
+          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>IDR</t>
@@ -2117,12 +2151,12 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Provisional Sum (At Cost + 15% Fee)</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O13" t="n">
@@ -2130,7 +2164,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q13" t="n">
@@ -2138,19 +2172,19 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="T13" t="n">
-        <v>21000000</v>
+        <v>1600000</v>
       </c>
       <c r="U13" t="n">
-        <v>24150000</v>
+        <v>1600000</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -2179,12 +2213,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Pembayaran Biaya Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
+          <t>Pengambilan Material Pop Joint di Senoro 2 ke Luwuk</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-08-25 14:09:56</t>
+          <t>2026-08-25 21:59:34</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
@@ -2196,8 +2230,10 @@
       <c r="AI13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>7201250141</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2211,12 +2247,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/WS/V/2026</t>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>4 Agustus 2026</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2237,7 +2273,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
+          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -2253,15 +2289,15 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
+          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Pallet</t>
         </is>
       </c>
       <c r="Q14" t="n">
@@ -2269,19 +2305,19 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>18 May 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="T14" t="n">
-        <v>200000</v>
+        <v>250000</v>
       </c>
       <c r="U14" t="n">
-        <v>3200000</v>
+        <v>250000</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -2310,12 +2346,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Pengiriman Sample air dari Lokasi Cluster B ke Jakarta</t>
+          <t>Pembuatan Pallet untuk Pop Joint</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-08-25 14:09:56</t>
+          <t>2026-08-25 21:59:34</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr"/>
@@ -2327,8 +2363,10 @@
       <c r="AI14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>7201250141</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2342,12 +2380,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/WS/V/2026</t>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>4 Agustus 2026</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2368,7 +2406,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
+          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -2379,20 +2417,20 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>MOVING AIR FREIGHT TRANSPORT</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
+          <t>Helper Local (Skilled)</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Pallet</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="Q15" t="n">
@@ -2400,19 +2438,19 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>18 May 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>18 May 2026</t>
+          <t>04 Aug 2026</t>
         </is>
       </c>
       <c r="T15" t="n">
-        <v>250000</v>
+        <v>350000</v>
       </c>
       <c r="U15" t="n">
-        <v>250000</v>
+        <v>700000</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -2441,12 +2479,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Pembuatan Pallet Sample Air (packing Barang)</t>
+          <t>Personel Handling di Luwuk-Bandara 1 orang dan Jakarta-Bogor 1 orang</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-08-25 14:09:56</t>
+          <t>2026-08-25 21:59:34</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr"/>
@@ -2458,8 +2496,10 @@
       <c r="AI15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>7201250141</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2473,12 +2513,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/WS/V/2026</t>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>4 Agustus 2026</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2499,7 +2539,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
+          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -2510,20 +2550,20 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>1</v>
+        <v>105</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q16" t="n">
@@ -2531,19 +2571,19 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>18 May 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>18 May 2026</t>
+          <t>04 Aug 2026</t>
         </is>
       </c>
       <c r="T16" t="n">
-        <v>1600000</v>
+        <v>200000</v>
       </c>
       <c r="U16" t="n">
-        <v>1600000</v>
+        <v>21000000</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -2572,12 +2612,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Pickup Material di Luwuk tgl 18 Mei 2026 dari Lokasi ke Bandara</t>
+          <t>Cargo Barang   Air Freight Material Pop Joint yang dikirim</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-08-25 14:09:56</t>
+          <t>2026-08-25 21:59:34</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
@@ -2589,8 +2629,10 @@
       <c r="AI16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>7201250141</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2604,12 +2646,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/WS/V/2026</t>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>4 Agustus 2026</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2630,7 +2672,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
+          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -2641,20 +2683,20 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>JASA TRANSPORTASI DARI DAN KE BANDARA</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Helper Local (Skilled)</t>
+          <t>Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="Q17" t="n">
@@ -2662,19 +2704,19 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>18 May 2026</t>
+          <t>04 Aug 2026</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>04 Aug 2026</t>
         </is>
       </c>
       <c r="T17" t="n">
-        <v>350000</v>
+        <v>3250000</v>
       </c>
       <c r="U17" t="n">
-        <v>700000</v>
+        <v>3250000</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -2703,12 +2745,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Personel untuk pengurusan Barang di Luwuk dan Personel untuk pengurusan barang di Jakarta</t>
+          <t>Pengiriman barang Pop Joint dari Bandara Cengkareng ke Bogor alamat  Lamda Multi Dinamika yard</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-08-25 14:09:56</t>
+          <t>2026-08-25 21:59:34</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
@@ -2720,8 +2762,10 @@
       <c r="AI17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>7201250141</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2735,12 +2779,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/WS/V/2026</t>
+          <t>015/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>5 Agustus 2026</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2758,13 +2802,21 @@
           <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>4500011587</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>Data Uji Coba</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>IDR</t>
@@ -2772,12 +2824,12 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>JASA TRANSPORTASI DARI DAN KE BANDARA</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
+          <t>Provisional Sum (At Cost + 15% Fee)</t>
         </is>
       </c>
       <c r="O18" t="n">
@@ -2785,7 +2837,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q18" t="n">
@@ -2793,19 +2845,19 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>25 Aug 2026</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>25 Aug 2026</t>
         </is>
       </c>
       <c r="T18" t="n">
-        <v>3250000</v>
+        <v>7500000</v>
       </c>
       <c r="U18" t="n">
-        <v>3250000</v>
+        <v>11500000</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -2834,12 +2886,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Land transportasi dari bandara Cengkareng ke alamat penerima sample air PT.Haliburton</t>
+          <t>Harga 1 buah Pompa Air</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-08-25 14:09:56</t>
+          <t>2026-08-25 21:59:34</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
@@ -2851,8 +2903,10 @@
       <c r="AI18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>7201250141</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2866,12 +2920,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>008/BSS-JOB/WS/VII/2026</t>
+          <t>015/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>09 Jul 2026</t>
+          <t>5 Agustus 2026</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2889,13 +2943,21 @@
           <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>4500011587</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Kendaraan Operasional Support Team JOB Survey Lokasi di Senoro</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>Data Uji Coba</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>IDR</t>
@@ -2903,20 +2965,20 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Provisional Sum (At Cost + 15% Fee)</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q19" t="n">
@@ -2924,19 +2986,19 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>06 Jul 2026</t>
+          <t>25 Aug 2026</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>09 Jul 2026</t>
+          <t>25 Aug 2026</t>
         </is>
       </c>
       <c r="T19" t="n">
-        <v>1600000</v>
+        <v>2500000</v>
       </c>
       <c r="U19" t="n">
-        <v>6400000</v>
+        <v>0</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -2965,12 +3027,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Kendaraan Operasional Inova DN 1257 CL Support Team JOB Survey Lokasi di Senoro tgl 6 sd 9 Juli 2026</t>
+          <t>Kabel Ukuran 2x2.5 mm panjang 50 Meter untuk Proyek</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-08-25 14:09:56</t>
+          <t>2026-08-25 21:59:34</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
@@ -2982,8 +3044,10 @@
       <c r="AI19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>7201250141</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2997,12 +3061,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
+          <t>014/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4 Agustus 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -3020,13 +3084,21 @@
           <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>IDR</t>
@@ -3034,20 +3106,20 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>MOVING SEA FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Jasa repacking for Seafreight, estimasi ukuran pallet 100x100x100 cm</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>1</v>
+        <v>6.63</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Pallet</t>
         </is>
       </c>
       <c r="Q20" t="n">
@@ -3055,19 +3127,19 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>15 Jul 2026</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>15 Jul 2026</t>
         </is>
       </c>
       <c r="T20" t="n">
-        <v>1600000</v>
+        <v>1000000</v>
       </c>
       <c r="U20" t="n">
-        <v>1600000</v>
+        <v>6630000</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -3096,12 +3168,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>Pengambilan Material Pop Joint di Senoro 2 ke Luwuk</t>
+          <t>3 Unit Pallet : dengan Ukuran 170x80x210 cm = 2,9 m3 190x150x75 cm = 2,1 m3 135x135x90 cm = 1,6 m3</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-08-25 14:09:56</t>
+          <t>2026-08-25 21:59:34</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
@@ -3113,8 +3185,10 @@
       <c r="AI20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>7201250141</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -3128,12 +3202,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
+          <t>014/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>4 Agustus 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3151,13 +3225,21 @@
           <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>IDR</t>
@@ -3165,12 +3247,12 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>MOVING AIR FREIGHT TRANSPORT</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O21" t="n">
@@ -3178,7 +3260,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Pallet</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q21" t="n">
@@ -3186,19 +3268,19 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>16 Jul 2026</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>16 Jul 2026</t>
         </is>
       </c>
       <c r="T21" t="n">
-        <v>250000</v>
+        <v>1600000</v>
       </c>
       <c r="U21" t="n">
-        <v>250000</v>
+        <v>1600000</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -3227,12 +3309,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>Pembuatan Pallet untuk Pop Joint</t>
+          <t>Pengurusan Pickup Barang dari Senoro 2 ke Jetty Tangkian</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-08-25 14:09:56</t>
+          <t>2026-08-25 21:59:34</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
@@ -3244,8 +3326,10 @@
       <c r="AI21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>7201250141</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -3259,12 +3343,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
+          <t>014/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>4 Agustus 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -3282,13 +3366,21 @@
           <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>IDR</t>
@@ -3296,20 +3388,20 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Helper Local (Skilled)</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Tankian Jetty atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q22" t="n">
@@ -3317,19 +3409,19 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>16 Jul 2026</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>04 Aug 2026</t>
+          <t>16 Jul 2026</t>
         </is>
       </c>
       <c r="T22" t="n">
-        <v>350000</v>
+        <v>6440000</v>
       </c>
       <c r="U22" t="n">
-        <v>700000</v>
+        <v>6440000</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -3358,12 +3450,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Personel Handling di Luwuk-Bandara 1 orang dan Jakarta-Bogor 1 orang</t>
+          <t>Trucking Barang X-Mas Tree dari Senoro 2 ke Jetty di Tankian</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-08-25 14:09:56</t>
+          <t>2026-08-25 21:59:34</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
@@ -3375,8 +3467,10 @@
       <c r="AI22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>7201250141</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -3390,12 +3484,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
+          <t>014/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>4 Agustus 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3413,13 +3507,21 @@
           <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>IDR</t>
@@ -3427,20 +3529,20 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>MOVING AIR FREIGHT TRANSPORT</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
+          <t>forklift-loader cap min 5 Ton, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="O23" t="n">
-        <v>105</v>
+        <v>4</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q23" t="n">
@@ -3448,19 +3550,19 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>16 Jul 2026</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>04 Aug 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="T23" t="n">
-        <v>200000</v>
+        <v>3500000</v>
       </c>
       <c r="U23" t="n">
-        <v>21000000</v>
+        <v>14000000</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -3489,12 +3591,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>Cargo Barang   Air Freight Material Pop Joint yang dikirim</t>
+          <t>Forklit di Palabuhan Tangkian, Surabaya,Jakarta, Batam</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-08-25 14:09:56</t>
+          <t>2026-08-25 21:59:34</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
@@ -3506,8 +3608,10 @@
       <c r="AI23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>7201250141</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -3521,12 +3625,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
+          <t>014/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>4 Agustus 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3544,13 +3648,21 @@
           <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>IDR</t>
@@ -3558,12 +3670,12 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>JASA TRANSPORTASI DARI DAN KE BANDARA</t>
+          <t>MOVING SEA FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
+          <t>Surabaya - Luwuk/ Senoro atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
         </is>
       </c>
       <c r="O24" t="n">
@@ -3571,7 +3683,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q24" t="n">
@@ -3579,19 +3691,19 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>04 Aug 2026</t>
+          <t>20 Jul 2026</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>04 Aug 2026</t>
+          <t>27 Jul 2026</t>
         </is>
       </c>
       <c r="T24" t="n">
-        <v>3250000</v>
+        <v>22400000</v>
       </c>
       <c r="U24" t="n">
-        <v>3250000</v>
+        <v>22400000</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -3620,12 +3732,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>Pengiriman barang Pop Joint dari Bandara Cengkareng ke Bogor alamat  Lamda Multi Dinamika yard</t>
+          <t>Pengiriman Barang dengan Kapal Cargo dari Jetty tankian ke Pelabuhan tanjung perak di surabaya</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-08-25 14:09:56</t>
+          <t>2026-08-25 21:59:34</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr"/>
@@ -3654,12 +3766,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>015/BSS-JOB/WS/VIII/2026</t>
+          <t>014/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>5 Agustus 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3679,17 +3791,17 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4500011587</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Data Uji Coba</t>
+          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -3699,12 +3811,12 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>TRANSPORTASI DARI SURABAYA KE JABODETABEK:</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Provisional Sum (At Cost + 15% Fee)</t>
+          <t>Trailler 20 feet</t>
         </is>
       </c>
       <c r="O25" t="n">
@@ -3712,7 +3824,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="Q25" t="n">
@@ -3720,19 +3832,19 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>25 Aug 2026</t>
+          <t>28 Jul 2026</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>25 Aug 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="T25" t="n">
-        <v>7500000</v>
+        <v>14000000</v>
       </c>
       <c r="U25" t="n">
-        <v>11500000</v>
+        <v>14000000</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -3761,12 +3873,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Harga 1 buah Pompa Air </t>
+          <t>Trucking 3 unit Pallet dari Pelabuhan Surabaya ke Pelabuhan di Jakarta</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-08-25 14:09:56</t>
+          <t>2026-08-25 21:59:34</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr"/>
@@ -3795,12 +3907,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>015/BSS-JOB/WS/VIII/2026</t>
+          <t>014/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>5 Agustus 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3820,17 +3932,17 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4500011587</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Data Uji Coba</t>
+          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3840,12 +3952,12 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>MOVING SEA FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Provisional Sum (At Cost + 15% Fee)</t>
+          <t>Jabodetabek - Batam atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
         </is>
       </c>
       <c r="O26" t="n">
@@ -3861,19 +3973,19 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>25 Aug 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>25 Aug 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="T26" t="n">
-        <v>2500000</v>
+        <v>22400000</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>22400000</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -3902,12 +4014,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>Kabel Ukuran 2x2.5 mm panjang 50 Meter untuk Proyek</t>
+          <t>Pengiriman Barang dengan Kapal Cargo dari Pelabuhan di Jakarta ke Pelabuhan di Batam, door ke Penerima Barang</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-08-25 14:09:56</t>
+          <t>2026-08-25 21:59:34</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr"/>

--- a/database_penyimpanan_aman/database_transaksi_rincian.xlsx
+++ b/database_penyimpanan_aman/database_transaksi_rincian.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI26"/>
+  <dimension ref="A1:AJ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -592,6 +592,11 @@
           <t>Items</t>
         </is>
       </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>Jenis BASTP</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -723,7 +728,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-08-25 21:59:34</t>
+          <t>2026-08-26 15:19:36</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -733,6 +738,7 @@
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -864,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-08-25 21:59:34</t>
+          <t>2026-08-26 15:19:36</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -874,6 +880,7 @@
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1005,7 +1012,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-08-25 21:59:34</t>
+          <t>2026-08-26 15:19:36</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -1015,6 +1022,7 @@
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1146,7 +1154,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-08-25 21:59:34</t>
+          <t>2026-08-26 15:19:36</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -1156,6 +1164,7 @@
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1175,12 +1184,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>012/BSS-JOB/WS/VIII/2026</t>
+          <t>005/BSS-JOB/WS/V/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5 Agustus 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1198,21 +1207,13 @@
           <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4500011586</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>03 Aug 2026</t>
-        </is>
-      </c>
+          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>IDR</t>
@@ -1220,20 +1221,20 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Provisional Sum (At Cost + 15% Fee)</t>
+          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -1241,19 +1242,19 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>18 May 2026</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="T6" t="n">
-        <v>21000000</v>
+        <v>200000</v>
       </c>
       <c r="U6" t="n">
-        <v>24150000</v>
+        <v>3200000</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1282,12 +1283,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Pembayaran Biaya Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
+          <t>Pengiriman Sample air dari Lokasi Cluster B ke Jakarta</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-08-25 21:59:34</t>
+          <t>2026-08-26 15:19:36</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -1297,6 +1298,7 @@
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1358,15 +1360,15 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
+          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Pallet</t>
         </is>
       </c>
       <c r="Q7" t="n">
@@ -1379,14 +1381,14 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>18 May 2026</t>
         </is>
       </c>
       <c r="T7" t="n">
-        <v>200000</v>
+        <v>250000</v>
       </c>
       <c r="U7" t="n">
-        <v>3200000</v>
+        <v>250000</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -1415,12 +1417,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Pengiriman Sample air dari Lokasi Cluster B ke Jakarta</t>
+          <t>Pembuatan Pallet Sample Air (packing Barang)</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-08-25 21:59:34</t>
+          <t>2026-08-26 15:19:36</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
@@ -1430,6 +1432,7 @@
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1486,12 +1489,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>MOVING AIR FREIGHT TRANSPORT</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O8" t="n">
@@ -1499,7 +1502,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Pallet</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q8" t="n">
@@ -1516,10 +1519,10 @@
         </is>
       </c>
       <c r="T8" t="n">
-        <v>250000</v>
+        <v>1600000</v>
       </c>
       <c r="U8" t="n">
-        <v>250000</v>
+        <v>1600000</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -1548,12 +1551,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Pembuatan Pallet Sample Air (packing Barang)</t>
+          <t>Pickup Material di Luwuk tgl 18 Mei 2026 dari Lokasi ke Bandara</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-08-25 21:59:34</t>
+          <t>2026-08-26 15:19:36</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
@@ -1563,6 +1566,7 @@
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1619,20 +1623,20 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Helper Local (Skilled)</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -1645,14 +1649,14 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>18 May 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="T9" t="n">
-        <v>1600000</v>
+        <v>350000</v>
       </c>
       <c r="U9" t="n">
-        <v>1600000</v>
+        <v>700000</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1681,12 +1685,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Pickup Material di Luwuk tgl 18 Mei 2026 dari Lokasi ke Bandara</t>
+          <t>Personel untuk pengurusan Barang di Luwuk dan Personel untuk pengurusan barang di Jakarta</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-08-25 21:59:34</t>
+          <t>2026-08-26 15:19:36</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -1696,6 +1700,7 @@
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1752,20 +1757,20 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>JASA TRANSPORTASI DARI DAN KE BANDARA</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Helper Local (Skilled)</t>
+          <t>Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -1773,7 +1778,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>18 May 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1782,10 +1787,10 @@
         </is>
       </c>
       <c r="T10" t="n">
-        <v>350000</v>
+        <v>3250000</v>
       </c>
       <c r="U10" t="n">
-        <v>700000</v>
+        <v>3250000</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1814,12 +1819,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Personel untuk pengurusan Barang di Luwuk dan Personel untuk pengurusan barang di Jakarta</t>
+          <t>Land transportasi dari bandara Cengkareng ke alamat penerima sample air PT.Haliburton</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-08-25 21:59:34</t>
+          <t>2026-08-26 15:19:36</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
@@ -1829,6 +1834,7 @@
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1848,12 +1854,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/WS/V/2026</t>
+          <t>008/BSS-JOB/WS/VII/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>09 Jul 2026</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1874,7 +1880,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
+          <t>Kendaraan Operasional Support Team JOB Survey Lokasi di Senoro</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1885,20 +1891,20 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>JASA TRANSPORTASI DARI DAN KE BANDARA</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q11" t="n">
@@ -1906,19 +1912,19 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>06 Jul 2026</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>09 Jul 2026</t>
         </is>
       </c>
       <c r="T11" t="n">
-        <v>3250000</v>
+        <v>1600000</v>
       </c>
       <c r="U11" t="n">
-        <v>3250000</v>
+        <v>6400000</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -1947,12 +1953,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Land transportasi dari bandara Cengkareng ke alamat penerima sample air PT.Haliburton</t>
+          <t>Kendaraan Operasional Inova DN 1257 CL Support Team JOB Survey Lokasi di Senoro tgl 6 sd 9 Juli 2026</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-08-25 21:59:34</t>
+          <t>2026-08-26 15:19:36</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
@@ -1962,6 +1968,7 @@
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1981,12 +1988,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>008/BSS-JOB/WS/VII/2026</t>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>09 Jul 2026</t>
+          <t>4 Agustus 2026</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2007,7 +2014,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Kendaraan Operasional Support Team JOB Survey Lokasi di Senoro</t>
+          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -2023,11 +2030,11 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -2039,19 +2046,19 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>06 Jul 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>09 Jul 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="T12" t="n">
         <v>1600000</v>
       </c>
       <c r="U12" t="n">
-        <v>6400000</v>
+        <v>1600000</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -2080,12 +2087,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Kendaraan Operasional Inova DN 1257 CL Support Team JOB Survey Lokasi di Senoro tgl 6 sd 9 Juli 2026</t>
+          <t>Pengambilan Material Pop Joint di Senoro 2 ke Luwuk</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-08-25 21:59:34</t>
+          <t>2026-08-26 15:19:36</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
@@ -2095,6 +2102,7 @@
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2151,12 +2159,12 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
         </is>
       </c>
       <c r="O13" t="n">
@@ -2164,7 +2172,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Pallet</t>
         </is>
       </c>
       <c r="Q13" t="n">
@@ -2181,10 +2189,10 @@
         </is>
       </c>
       <c r="T13" t="n">
-        <v>1600000</v>
+        <v>250000</v>
       </c>
       <c r="U13" t="n">
-        <v>1600000</v>
+        <v>250000</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -2213,12 +2221,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Pengambilan Material Pop Joint di Senoro 2 ke Luwuk</t>
+          <t>Pembuatan Pallet untuk Pop Joint</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-08-25 21:59:34</t>
+          <t>2026-08-26 15:19:36</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
@@ -2228,6 +2236,7 @@
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2284,20 +2293,20 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>MOVING AIR FREIGHT TRANSPORT</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
+          <t>Helper Local (Skilled)</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Pallet</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="Q14" t="n">
@@ -2310,14 +2319,14 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>04 Aug 2026</t>
         </is>
       </c>
       <c r="T14" t="n">
-        <v>250000</v>
+        <v>350000</v>
       </c>
       <c r="U14" t="n">
-        <v>250000</v>
+        <v>700000</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -2346,12 +2355,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Pembuatan Pallet untuk Pop Joint</t>
+          <t>Personel Handling di Luwuk-Bandara 1 orang dan Jakarta-Bogor 1 orang</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-08-25 21:59:34</t>
+          <t>2026-08-26 15:19:36</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr"/>
@@ -2361,6 +2370,7 @@
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2417,20 +2427,20 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Helper Local (Skilled)</t>
+          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q15" t="n">
@@ -2447,10 +2457,10 @@
         </is>
       </c>
       <c r="T15" t="n">
-        <v>350000</v>
+        <v>200000</v>
       </c>
       <c r="U15" t="n">
-        <v>700000</v>
+        <v>21000000</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -2479,12 +2489,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Personel Handling di Luwuk-Bandara 1 orang dan Jakarta-Bogor 1 orang</t>
+          <t>Cargo Barang   Air Freight Material Pop Joint yang dikirim</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-08-25 21:59:34</t>
+          <t>2026-08-26 15:19:36</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr"/>
@@ -2494,6 +2504,7 @@
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr"/>
       <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2550,20 +2561,20 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>MOVING AIR FREIGHT TRANSPORT</t>
+          <t>JASA TRANSPORTASI DARI DAN KE BANDARA</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
+          <t>Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>105</v>
+        <v>1</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="Q16" t="n">
@@ -2571,7 +2582,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>04 Aug 2026</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2580,10 +2591,10 @@
         </is>
       </c>
       <c r="T16" t="n">
-        <v>200000</v>
+        <v>3250000</v>
       </c>
       <c r="U16" t="n">
-        <v>21000000</v>
+        <v>3250000</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -2612,12 +2623,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Cargo Barang   Air Freight Material Pop Joint yang dikirim</t>
+          <t>Pengiriman barang Pop Joint dari Bandara Cengkareng ke Bogor alamat  Lamda Multi Dinamika yard</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-08-25 21:59:34</t>
+          <t>2026-08-26 15:19:36</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
@@ -2627,6 +2638,7 @@
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr"/>
       <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2646,12 +2658,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
+          <t>015/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4 Agustus 2026</t>
+          <t>5 Agustus 2026</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2669,13 +2681,21 @@
           <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4500011587</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>Data Uji Coba</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>IDR</t>
@@ -2683,12 +2703,12 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>JASA TRANSPORTASI DARI DAN KE BANDARA</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
+          <t>Provisional Sum (At Cost + 15% Fee)</t>
         </is>
       </c>
       <c r="O17" t="n">
@@ -2696,7 +2716,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q17" t="n">
@@ -2704,19 +2724,19 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>04 Aug 2026</t>
+          <t>25 Aug 2026</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>04 Aug 2026</t>
+          <t>25 Aug 2026</t>
         </is>
       </c>
       <c r="T17" t="n">
-        <v>3250000</v>
+        <v>7500000</v>
       </c>
       <c r="U17" t="n">
-        <v>3250000</v>
+        <v>11500000</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -2745,12 +2765,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Pengiriman barang Pop Joint dari Bandara Cengkareng ke Bogor alamat  Lamda Multi Dinamika yard</t>
+          <t>Harga 1 buah Pompa Air</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-08-25 21:59:34</t>
+          <t>2026-08-26 15:19:36</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
@@ -2760,6 +2780,7 @@
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2854,10 +2875,10 @@
         </is>
       </c>
       <c r="T18" t="n">
-        <v>7500000</v>
+        <v>2500000</v>
       </c>
       <c r="U18" t="n">
-        <v>11500000</v>
+        <v>0</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -2886,12 +2907,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Harga 1 buah Pompa Air</t>
+          <t>Kabel Ukuran 2x2.5 mm panjang 50 Meter untuk Proyek</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-08-25 21:59:34</t>
+          <t>2026-08-26 15:19:36</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
@@ -2901,6 +2922,7 @@
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2920,12 +2942,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>015/BSS-JOB/WS/VIII/2026</t>
+          <t>014/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>5 Agustus 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2945,17 +2967,17 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4500011587</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Data Uji Coba</t>
+          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2965,20 +2987,20 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>MOVING SEA FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Provisional Sum (At Cost + 15% Fee)</t>
+          <t>Jasa repacking for Seafreight, estimasi ukuran pallet 100x100x100 cm</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>1</v>
+        <v>6.63</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Pallet</t>
         </is>
       </c>
       <c r="Q19" t="n">
@@ -2986,19 +3008,19 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>25 Aug 2026</t>
+          <t>15 Jul 2026</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>25 Aug 2026</t>
+          <t>15 Jul 2026</t>
         </is>
       </c>
       <c r="T19" t="n">
-        <v>2500000</v>
+        <v>1000000</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>6630000</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -3027,12 +3049,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Kabel Ukuran 2x2.5 mm panjang 50 Meter untuk Proyek</t>
+          <t>3 Unit Pallet : dengan Ukuran 170x80x210 cm = 2,9 m3 190x150x75 cm = 2,1 m3 135x135x90 cm = 1,6 m3</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-08-25 21:59:34</t>
+          <t>2026-08-26 15:19:36</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
@@ -3042,6 +3064,7 @@
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr"/>
       <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3106,20 +3129,20 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>MOVING SEA FREIGHT TRANSPORT</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Jasa repacking for Seafreight, estimasi ukuran pallet 100x100x100 cm</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>6.63</v>
+        <v>1</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Pallet</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q20" t="n">
@@ -3127,19 +3150,19 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>15 Jul 2026</t>
+          <t>16 Jul 2026</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>15 Jul 2026</t>
+          <t>16 Jul 2026</t>
         </is>
       </c>
       <c r="T20" t="n">
-        <v>1000000</v>
+        <v>1600000</v>
       </c>
       <c r="U20" t="n">
-        <v>6630000</v>
+        <v>1600000</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -3168,12 +3191,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>3 Unit Pallet : dengan Ukuran 170x80x210 cm = 2,9 m3 190x150x75 cm = 2,1 m3 135x135x90 cm = 1,6 m3</t>
+          <t>Pengurusan Pickup Barang dari Senoro 2 ke Jetty Tangkian</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-08-25 21:59:34</t>
+          <t>2026-08-26 15:19:36</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
@@ -3183,6 +3206,7 @@
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3247,12 +3271,12 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Tankian Jetty atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="O21" t="n">
@@ -3260,7 +3284,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q21" t="n">
@@ -3277,10 +3301,10 @@
         </is>
       </c>
       <c r="T21" t="n">
-        <v>1600000</v>
+        <v>6440000</v>
       </c>
       <c r="U21" t="n">
-        <v>1600000</v>
+        <v>6440000</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -3309,12 +3333,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>Pengurusan Pickup Barang dari Senoro 2 ke Jetty Tangkian</t>
+          <t>Trucking Barang X-Mas Tree dari Senoro 2 ke Jetty di Tankian</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-08-25 21:59:34</t>
+          <t>2026-08-26 15:19:36</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
@@ -3324,6 +3348,7 @@
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3388,20 +3413,20 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Tankian Jetty atau sebaliknya c/w BBM &amp; driver</t>
+          <t>forklift-loader cap min 5 Ton, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q22" t="n">
@@ -3414,14 +3439,14 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>16 Jul 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="T22" t="n">
-        <v>6440000</v>
+        <v>3500000</v>
       </c>
       <c r="U22" t="n">
-        <v>6440000</v>
+        <v>14000000</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -3450,12 +3475,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Trucking Barang X-Mas Tree dari Senoro 2 ke Jetty di Tankian</t>
+          <t>Forklit di Palabuhan Tangkian, Surabaya,Jakarta, Batam</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-08-25 21:59:34</t>
+          <t>2026-08-26 15:19:36</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
@@ -3465,6 +3490,7 @@
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3529,20 +3555,20 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>MOVING SEA FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>forklift-loader cap min 5 Ton, call out, (hanya unit)</t>
+          <t>Surabaya - Luwuk/ Senoro atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
         </is>
       </c>
       <c r="O23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q23" t="n">
@@ -3550,19 +3576,19 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>16 Jul 2026</t>
+          <t>20 Jul 2026</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>11 Aug 2026</t>
+          <t>27 Jul 2026</t>
         </is>
       </c>
       <c r="T23" t="n">
-        <v>3500000</v>
+        <v>22400000</v>
       </c>
       <c r="U23" t="n">
-        <v>14000000</v>
+        <v>22400000</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -3591,12 +3617,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>Forklit di Palabuhan Tangkian, Surabaya,Jakarta, Batam</t>
+          <t>Pengiriman Barang dengan Kapal Cargo dari Jetty tankian ke Pelabuhan tanjung perak di surabaya</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-08-25 21:59:34</t>
+          <t>2026-08-26 15:19:36</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
@@ -3606,6 +3632,7 @@
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="inlineStr"/>
       <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3670,12 +3697,12 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>MOVING SEA FREIGHT TRANSPORT</t>
+          <t>TRANSPORTASI DARI SURABAYA KE JABODETABEK:</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Surabaya - Luwuk/ Senoro atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
+          <t>Trailler 20 feet</t>
         </is>
       </c>
       <c r="O24" t="n">
@@ -3683,7 +3710,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="Q24" t="n">
@@ -3691,19 +3718,19 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>20 Jul 2026</t>
+          <t>28 Jul 2026</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>27 Jul 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="T24" t="n">
-        <v>22400000</v>
+        <v>14000000</v>
       </c>
       <c r="U24" t="n">
-        <v>22400000</v>
+        <v>14000000</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -3732,12 +3759,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>Pengiriman Barang dengan Kapal Cargo dari Jetty tankian ke Pelabuhan tanjung perak di surabaya</t>
+          <t>Trucking 3 unit Pallet dari Pelabuhan Surabaya ke Pelabuhan di Jakarta</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-08-25 21:59:34</t>
+          <t>2026-08-26 15:19:36</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr"/>
@@ -3747,6 +3774,7 @@
       <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3811,12 +3839,12 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>TRANSPORTASI DARI SURABAYA KE JABODETABEK:</t>
+          <t>MOVING SEA FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Trailler 20 feet</t>
+          <t>Jabodetabek - Batam atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
         </is>
       </c>
       <c r="O25" t="n">
@@ -3824,7 +3852,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q25" t="n">
@@ -3832,19 +3860,19 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>28 Jul 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="T25" t="n">
-        <v>14000000</v>
+        <v>22400000</v>
       </c>
       <c r="U25" t="n">
-        <v>14000000</v>
+        <v>22400000</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -3873,12 +3901,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>Trucking 3 unit Pallet dari Pelabuhan Surabaya ke Pelabuhan di Jakarta</t>
+          <t>Pengiriman Barang dengan Kapal Cargo dari Pelabuhan di Jakarta ke Pelabuhan di Batam, door ke Penerima Barang</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-08-25 21:59:34</t>
+          <t>2026-08-26 15:19:36</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr"/>
@@ -3888,6 +3916,7 @@
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="inlineStr"/>
       <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3907,12 +3936,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>014/BSS-JOB/WS/VIII/2026</t>
+          <t>012/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>11 Aug 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3927,22 +3956,22 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011586</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3952,12 +3981,12 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>MOVING SEA FREIGHT TRANSPORT</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Jabodetabek - Batam atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
+          <t>Provisional Sum (At Cost + 15% Fee)</t>
         </is>
       </c>
       <c r="O26" t="n">
@@ -3973,19 +4002,19 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>11 Aug 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="T26" t="n">
-        <v>22400000</v>
+        <v>21000000</v>
       </c>
       <c r="U26" t="n">
-        <v>22400000</v>
+        <v>24150000</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -4014,12 +4043,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>Pengiriman Barang dengan Kapal Cargo dari Pelabuhan di Jakarta ke Pelabuhan di Batam, door ke Penerima Barang</t>
+          <t>Pembayaran Biaya Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-08-25 21:59:34</t>
+          <t>2026-08-26 15:19:36</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr"/>
@@ -4029,6 +4058,445 @@
       <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>05 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>4500011587</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Pembelian Material Kabel dan Kayu untuk senoro</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Aqua 600 ml</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>24</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>100</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>05 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>05 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T27" t="n">
+        <v>7500</v>
+      </c>
+      <c r="U27" t="n">
+        <v>180000</v>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>Untuk crew lokasi senoro</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>2026-08-26 15:19:36</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>05 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>4500011587</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Pembelian Material Kabel dan Kayu untuk senoro</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Aqua Galon Segel</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>10</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>100</v>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>26 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>26 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T28" t="n">
+        <v>53300</v>
+      </c>
+      <c r="U28" t="n">
+        <v>533000</v>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>Untuk konsumsi crew di senoro</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>2026-08-26 15:19:36</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>05 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>4500011587</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Pembelian Material Kabel dan Kayu untuk senoro</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Batu Agregate A</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>5</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>100</v>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>26 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>26 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T29" t="n">
+        <v>400000</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>Untuk timbunan jalan di senoro</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>2026-08-26 15:19:36</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/database_penyimpanan_aman/database_transaksi_rincian.xlsx
+++ b/database_penyimpanan_aman/database_transaksi_rincian.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ29"/>
+  <dimension ref="A1:AJ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -601,27 +601,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>7207250142</t>
+          <t>7201250141</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>S250551FLD-R1</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>043/BSS-JOB/AB/VII/2026</t>
+          <t>005/BSS-JOB/WS/V/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -636,22 +636,22 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>24 Month</t>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4500011425</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift Untuk support Kegiatan Operation &amp; Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026, Refer CTR No. 7207250142-BSS-CTR-2026-020" (01 - 31 Juli 2026)</t>
+          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1 Jul 2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -661,20 +661,20 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
+          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -682,19 +682,19 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>01 Jul 2026</t>
+          <t>18 May 2026</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="T2" t="n">
-        <v>62818000</v>
+        <v>200000</v>
       </c>
       <c r="U2" t="n">
-        <v>62818000</v>
+        <v>3200000</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -723,12 +723,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Periode Pekerjaan 01 Juli sd 31 Juli 2026</t>
+          <t>Pengiriman Sample air dari Lokasi Cluster B ke Jakarta</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-08-26 15:19:36</t>
+          <t>2026-08-26 18:30:06</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -738,32 +738,36 @@
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>7203250036</t>
+          <t>7201250141</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Penyediaan Jasa Penyewaan Alat Berat Werehouse</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>S250009SCM</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>010/BSS-JOB/WH/VII/2026</t>
+          <t>005/BSS-JOB/WS/V/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -778,22 +782,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>03 Desember 2027</t>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4500010848</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton</t>
+          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2 Januari 2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -803,20 +807,20 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Daily Rate</t>
+          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Pallet</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -824,19 +828,19 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>01 Jul 2026</t>
+          <t>18 May 2026</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>18 May 2026</t>
         </is>
       </c>
       <c r="T3" t="n">
-        <v>1197000</v>
+        <v>250000</v>
       </c>
       <c r="U3" t="n">
-        <v>21546000</v>
+        <v>250000</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -865,12 +869,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Forklift 5 ton, Operasi di CPP Senoro Periode 1 sd 31 Juli 2026</t>
+          <t>Pembuatan Pallet Sample Air (packing Barang)</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-08-26 15:19:36</t>
+          <t>2026-08-26 18:30:06</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -880,32 +884,36 @@
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>7203250036</t>
+          <t>7201250141</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Penyediaan Jasa Penyewaan Alat Berat Werehouse</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>S250009SCM</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>010/BSS-JOB/WH/VII/2026</t>
+          <t>005/BSS-JOB/WS/V/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -920,22 +928,22 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>03 Desember 2027</t>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4500010848</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton</t>
+          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2 Januari 2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -945,16 +953,16 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Daily Rate</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -966,19 +974,19 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>01 Jul 2026</t>
+          <t>18 May 2026</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>18 May 2026</t>
         </is>
       </c>
       <c r="T4" t="n">
-        <v>1197000</v>
+        <v>1600000</v>
       </c>
       <c r="U4" t="n">
-        <v>21546000</v>
+        <v>1600000</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -1007,12 +1015,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Forklift 5 ton, Operasi di  Werehouse Senoro 2 Periode 1 sd 31 Juli 2026</t>
+          <t>Pickup Material di Luwuk tgl 18 Mei 2026 dari Lokasi ke Bandara</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-08-26 15:19:36</t>
+          <t>2026-08-26 18:30:06</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -1022,32 +1030,36 @@
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>7203250036</t>
+          <t>7201250141</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Penyediaan Jasa Penyewaan Alat Berat Werehouse</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>S250009SCM</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>010/BSS-JOB/WH/VII/2026</t>
+          <t>005/BSS-JOB/WS/V/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1062,22 +1074,22 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>03 Desember 2027</t>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4500010848</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton</t>
+          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2 Januari 2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1087,12 +1099,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Standby Rate</t>
+          <t>Helper Local (Skilled)</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -1100,7 +1112,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ls</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -1108,19 +1120,19 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>01 Jul 2026</t>
+          <t>18 May 2026</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="T5" t="n">
-        <v>598500</v>
+        <v>350000</v>
       </c>
       <c r="U5" t="n">
-        <v>1197000</v>
+        <v>700000</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -1149,12 +1161,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2 Unit Forklift Standby di CPP Senoro dan Werehouse Senoro 2 Periode 1 sd 31 Juli 2026</t>
+          <t>Personel untuk pengurusan Barang di Luwuk dan Personel untuk pengurusan barang di Jakarta</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-08-26 15:19:36</t>
+          <t>2026-08-26 18:30:06</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -1164,7 +1176,11 @@
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1207,13 +1223,21 @@
           <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>IDR</t>
@@ -1221,20 +1245,20 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>MOVING AIR FREIGHT TRANSPORT</t>
+          <t>JASA TRANSPORTASI DARI DAN KE BANDARA</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
+          <t>Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -1242,7 +1266,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>18 May 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1251,10 +1275,10 @@
         </is>
       </c>
       <c r="T6" t="n">
-        <v>200000</v>
+        <v>3250000</v>
       </c>
       <c r="U6" t="n">
-        <v>3200000</v>
+        <v>3250000</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1283,12 +1307,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Pengiriman Sample air dari Lokasi Cluster B ke Jakarta</t>
+          <t>Land transportasi dari bandara Cengkareng ke alamat penerima sample air PT.Haliburton</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-08-26 15:19:36</t>
+          <t>2026-08-26 18:30:06</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -1298,7 +1322,11 @@
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1318,12 +1346,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/WS/V/2026</t>
+          <t>008/BSS-JOB/WS/VII/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>09 Jul 2026</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1341,13 +1369,21 @@
           <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>Kendaraan Operasional Support Team JOB Survey Lokasi di Senoro</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>IDR</t>
@@ -1355,20 +1391,20 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>MOVING AIR FREIGHT TRANSPORT</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Pallet</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q7" t="n">
@@ -1376,19 +1412,19 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>18 May 2026</t>
+          <t>06 Jul 2026</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>18 May 2026</t>
+          <t>09 Jul 2026</t>
         </is>
       </c>
       <c r="T7" t="n">
-        <v>250000</v>
+        <v>1600000</v>
       </c>
       <c r="U7" t="n">
-        <v>250000</v>
+        <v>6400000</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -1417,12 +1453,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Pembuatan Pallet Sample Air (packing Barang)</t>
+          <t>Kendaraan Operasional Inova DN 1257 CL Support Team JOB Survey Lokasi di Senoro tgl 6 sd 9 Juli 2026</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-08-26 15:19:36</t>
+          <t>2026-08-26 18:30:06</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
@@ -1432,7 +1468,11 @@
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1452,12 +1492,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/WS/V/2026</t>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>04 Aug 2026</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1475,13 +1515,21 @@
           <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>IDR</t>
@@ -1510,12 +1558,12 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>18 May 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>18 May 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="T8" t="n">
@@ -1551,12 +1599,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Pickup Material di Luwuk tgl 18 Mei 2026 dari Lokasi ke Bandara</t>
+          <t>Pengambilan Material Pop Joint di Senoro 2 ke Luwuk</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-08-26 15:19:36</t>
+          <t>2026-08-26 18:30:06</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
@@ -1566,7 +1614,11 @@
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1586,12 +1638,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/WS/V/2026</t>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>04 Aug 2026</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1609,13 +1661,21 @@
           <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>IDR</t>
@@ -1623,20 +1683,20 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Helper Local (Skilled)</t>
+          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Pallet</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -1644,19 +1704,19 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>18 May 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="T9" t="n">
-        <v>350000</v>
+        <v>250000</v>
       </c>
       <c r="U9" t="n">
-        <v>700000</v>
+        <v>250000</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1685,12 +1745,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Personel untuk pengurusan Barang di Luwuk dan Personel untuk pengurusan barang di Jakarta</t>
+          <t>Pembuatan Pallet untuk Pop Joint</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-08-26 15:19:36</t>
+          <t>2026-08-26 18:30:06</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -1700,7 +1760,11 @@
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1720,12 +1784,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/WS/V/2026</t>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>04 Aug 2026</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1743,13 +1807,21 @@
           <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>IDR</t>
@@ -1757,20 +1829,20 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>JASA TRANSPORTASI DARI DAN KE BANDARA</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
+          <t>Helper Local (Skilled)</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -1778,19 +1850,19 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>04 Aug 2026</t>
         </is>
       </c>
       <c r="T10" t="n">
-        <v>3250000</v>
+        <v>350000</v>
       </c>
       <c r="U10" t="n">
-        <v>3250000</v>
+        <v>700000</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1819,12 +1891,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Land transportasi dari bandara Cengkareng ke alamat penerima sample air PT.Haliburton</t>
+          <t>Personel Handling di Luwuk-Bandara 1 orang dan Jakarta-Bogor 1 orang</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-08-26 15:19:36</t>
+          <t>2026-08-26 18:30:06</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
@@ -1834,7 +1906,11 @@
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1854,12 +1930,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>008/BSS-JOB/WS/VII/2026</t>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>09 Jul 2026</t>
+          <t>04 Aug 2026</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1877,13 +1953,21 @@
           <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Kendaraan Operasional Support Team JOB Survey Lokasi di Senoro</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>IDR</t>
@@ -1891,20 +1975,20 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>105</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q11" t="n">
@@ -1912,19 +1996,19 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>06 Jul 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>09 Jul 2026</t>
+          <t>04 Aug 2026</t>
         </is>
       </c>
       <c r="T11" t="n">
-        <v>1600000</v>
+        <v>200000</v>
       </c>
       <c r="U11" t="n">
-        <v>6400000</v>
+        <v>21000000</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -1953,12 +2037,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Kendaraan Operasional Inova DN 1257 CL Support Team JOB Survey Lokasi di Senoro tgl 6 sd 9 Juli 2026</t>
+          <t>Cargo Barang   Air Freight Material Pop Joint yang dikirim</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-08-26 15:19:36</t>
+          <t>2026-08-26 18:30:06</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
@@ -1968,7 +2052,11 @@
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1993,7 +2081,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4 Agustus 2026</t>
+          <t>04 Aug 2026</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2011,13 +2099,21 @@
           <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>IDR</t>
@@ -2025,12 +2121,12 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>JASA TRANSPORTASI DARI DAN KE BANDARA</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
         </is>
       </c>
       <c r="O12" t="n">
@@ -2038,7 +2134,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="Q12" t="n">
@@ -2046,19 +2142,19 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>04 Aug 2026</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>04 Aug 2026</t>
         </is>
       </c>
       <c r="T12" t="n">
-        <v>1600000</v>
+        <v>3250000</v>
       </c>
       <c r="U12" t="n">
-        <v>1600000</v>
+        <v>3250000</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -2087,12 +2183,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Pengambilan Material Pop Joint di Senoro 2 ke Luwuk</t>
+          <t>Pengiriman barang Pop Joint dari Bandara Cengkareng ke Bogor alamat  Lamda Multi Dinamika yard</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-08-26 15:19:36</t>
+          <t>2026-08-26 18:30:06</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
@@ -2102,7 +2198,11 @@
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="inlineStr"/>
-      <c r="AJ12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2122,12 +2222,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
+          <t>012/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4 Agustus 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2142,16 +2242,24 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4500011586</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>IDR</t>
@@ -2159,12 +2267,12 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>MOVING AIR FREIGHT TRANSPORT</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
+          <t>Provisional Sum (At Cost + 15% Fee)</t>
         </is>
       </c>
       <c r="O13" t="n">
@@ -2172,7 +2280,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Pallet</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q13" t="n">
@@ -2180,19 +2288,19 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="T13" t="n">
-        <v>250000</v>
+        <v>21000000</v>
       </c>
       <c r="U13" t="n">
-        <v>250000</v>
+        <v>24150000</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -2221,12 +2329,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Pembuatan Pallet untuk Pop Joint</t>
+          <t>Pembayaran Biaya Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-08-26 15:19:36</t>
+          <t>2026-08-26 18:30:06</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
@@ -2236,7 +2344,11 @@
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2256,12 +2368,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
+          <t>014/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4 Agustus 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2279,13 +2391,21 @@
           <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>IDR</t>
@@ -2293,20 +2413,20 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>MOVING SEA FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Helper Local (Skilled)</t>
+          <t>Jasa repacking for Seafreight, estimasi ukuran pallet 100x100x100 cm</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>2</v>
+        <v>6.63</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Pallet</t>
         </is>
       </c>
       <c r="Q14" t="n">
@@ -2314,19 +2434,19 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>15 Jul 2026</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>04 Aug 2026</t>
+          <t>15 Jul 2026</t>
         </is>
       </c>
       <c r="T14" t="n">
-        <v>350000</v>
+        <v>1000000</v>
       </c>
       <c r="U14" t="n">
-        <v>700000</v>
+        <v>6630000</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -2355,12 +2475,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Personel Handling di Luwuk-Bandara 1 orang dan Jakarta-Bogor 1 orang</t>
+          <t>3 Unit Pallet : dengan Ukuran 170x80x210 cm = 2,9 m3 190x150x75 cm = 2,1 m3 135x135x90 cm = 1,6 m3</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-08-26 15:19:36</t>
+          <t>2026-08-26 18:30:06</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr"/>
@@ -2370,7 +2490,11 @@
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2390,12 +2514,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
+          <t>014/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4 Agustus 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2413,13 +2537,21 @@
           <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>IDR</t>
@@ -2427,20 +2559,20 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>MOVING AIR FREIGHT TRANSPORT</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>105</v>
+        <v>1</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q15" t="n">
@@ -2448,19 +2580,19 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>16 Jul 2026</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>04 Aug 2026</t>
+          <t>16 Jul 2026</t>
         </is>
       </c>
       <c r="T15" t="n">
-        <v>200000</v>
+        <v>1600000</v>
       </c>
       <c r="U15" t="n">
-        <v>21000000</v>
+        <v>1600000</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -2489,12 +2621,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Cargo Barang   Air Freight Material Pop Joint yang dikirim</t>
+          <t>Pengurusan Pickup Barang dari Senoro 2 ke Jetty Tangkian</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-08-26 15:19:36</t>
+          <t>2026-08-26 18:30:06</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr"/>
@@ -2504,7 +2636,11 @@
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr"/>
       <c r="AI15" t="inlineStr"/>
-      <c r="AJ15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2524,12 +2660,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
+          <t>014/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4 Agustus 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2547,13 +2683,21 @@
           <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>IDR</t>
@@ -2561,12 +2705,12 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>JASA TRANSPORTASI DARI DAN KE BANDARA</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Tankian Jetty atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="O16" t="n">
@@ -2574,7 +2718,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q16" t="n">
@@ -2582,19 +2726,19 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>04 Aug 2026</t>
+          <t>16 Jul 2026</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>04 Aug 2026</t>
+          <t>16 Jul 2026</t>
         </is>
       </c>
       <c r="T16" t="n">
-        <v>3250000</v>
+        <v>6440000</v>
       </c>
       <c r="U16" t="n">
-        <v>3250000</v>
+        <v>6440000</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -2623,12 +2767,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Pengiriman barang Pop Joint dari Bandara Cengkareng ke Bogor alamat  Lamda Multi Dinamika yard</t>
+          <t>Trucking Barang X-Mas Tree dari Senoro 2 ke Jetty di Tankian</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-08-26 15:19:36</t>
+          <t>2026-08-26 18:30:06</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
@@ -2638,7 +2782,11 @@
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr"/>
       <c r="AI16" t="inlineStr"/>
-      <c r="AJ16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2658,12 +2806,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>015/BSS-JOB/WS/VIII/2026</t>
+          <t>014/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>5 Agustus 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2683,17 +2831,17 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4500011587</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Data Uji Coba</t>
+          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2703,20 +2851,20 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Provisional Sum (At Cost + 15% Fee)</t>
+          <t>forklift-loader cap min 5 Ton, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q17" t="n">
@@ -2724,19 +2872,19 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>25 Aug 2026</t>
+          <t>16 Jul 2026</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>25 Aug 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="T17" t="n">
-        <v>7500000</v>
+        <v>3500000</v>
       </c>
       <c r="U17" t="n">
-        <v>11500000</v>
+        <v>14000000</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -2765,12 +2913,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Harga 1 buah Pompa Air</t>
+          <t>Forklit di Palabuhan Tangkian, Surabaya,Jakarta, Batam</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-08-26 15:19:36</t>
+          <t>2026-08-26 18:30:06</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
@@ -2780,7 +2928,11 @@
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="inlineStr"/>
-      <c r="AJ17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2800,12 +2952,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>015/BSS-JOB/WS/VIII/2026</t>
+          <t>014/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>5 Agustus 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2825,17 +2977,17 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4500011587</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Data Uji Coba</t>
+          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2845,12 +2997,12 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>MOVING SEA FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Provisional Sum (At Cost + 15% Fee)</t>
+          <t>Surabaya - Luwuk/ Senoro atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
         </is>
       </c>
       <c r="O18" t="n">
@@ -2866,19 +3018,19 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>25 Aug 2026</t>
+          <t>20 Jul 2026</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>25 Aug 2026</t>
+          <t>27 Jul 2026</t>
         </is>
       </c>
       <c r="T18" t="n">
-        <v>2500000</v>
+        <v>22400000</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>22400000</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -2907,12 +3059,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Kabel Ukuran 2x2.5 mm panjang 50 Meter untuk Proyek</t>
+          <t>Pengiriman Barang dengan Kapal Cargo dari Jetty tankian ke Pelabuhan tanjung perak di surabaya</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-08-26 15:19:36</t>
+          <t>2026-08-26 18:30:06</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
@@ -2922,7 +3074,11 @@
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="inlineStr"/>
-      <c r="AJ18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2987,20 +3143,20 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>MOVING SEA FREIGHT TRANSPORT</t>
+          <t>TRANSPORTASI DARI SURABAYA KE JABODETABEK:</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Jasa repacking for Seafreight, estimasi ukuran pallet 100x100x100 cm</t>
+          <t>Trailler 20 feet</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>6.63</v>
+        <v>1</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Pallet</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="Q19" t="n">
@@ -3008,19 +3164,19 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>15 Jul 2026</t>
+          <t>28 Jul 2026</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>15 Jul 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="T19" t="n">
-        <v>1000000</v>
+        <v>14000000</v>
       </c>
       <c r="U19" t="n">
-        <v>6630000</v>
+        <v>14000000</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -3049,12 +3205,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>3 Unit Pallet : dengan Ukuran 170x80x210 cm = 2,9 m3 190x150x75 cm = 2,1 m3 135x135x90 cm = 1,6 m3</t>
+          <t>Trucking 3 unit Pallet dari Pelabuhan Surabaya ke Pelabuhan di Jakarta</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-08-26 15:19:36</t>
+          <t>2026-08-26 18:30:06</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
@@ -3064,7 +3220,11 @@
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr"/>
       <c r="AI19" t="inlineStr"/>
-      <c r="AJ19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3129,12 +3289,12 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>MOVING SEA FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Jabodetabek - Batam atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
         </is>
       </c>
       <c r="O20" t="n">
@@ -3142,7 +3302,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q20" t="n">
@@ -3150,19 +3310,19 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>16 Jul 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>16 Jul 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="T20" t="n">
-        <v>1600000</v>
+        <v>22400000</v>
       </c>
       <c r="U20" t="n">
-        <v>1600000</v>
+        <v>22400000</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -3191,12 +3351,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>Pengurusan Pickup Barang dari Senoro 2 ke Jetty Tangkian</t>
+          <t>Pengiriman Barang dengan Kapal Cargo dari Pelabuhan di Jakarta ke Pelabuhan di Batam, door ke Penerima Barang</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-08-26 15:19:36</t>
+          <t>2026-08-26 18:30:06</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
@@ -3206,7 +3366,11 @@
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="inlineStr"/>
-      <c r="AJ20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3226,12 +3390,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>014/BSS-JOB/WS/VIII/2026</t>
+          <t>015/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>11 Aug 2026</t>
+          <t>5 Agustus 2026</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3251,17 +3415,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011587</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+          <t>Data Uji Coba</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -3271,20 +3435,20 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Tankian Jetty atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Aqua 600 ml</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q21" t="n">
@@ -3292,19 +3456,19 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>16 Jul 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>16 Jul 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="T21" t="n">
-        <v>6440000</v>
+        <v>7500</v>
       </c>
       <c r="U21" t="n">
-        <v>6440000</v>
+        <v>180000</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -3333,12 +3497,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>Trucking Barang X-Mas Tree dari Senoro 2 ke Jetty di Tankian</t>
+          <t>Untuk crew lokasi senoro</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-08-26 15:19:36</t>
+          <t>2026-08-26 18:30:06</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
@@ -3348,7 +3512,11 @@
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="inlineStr"/>
-      <c r="AJ21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3368,12 +3536,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>014/BSS-JOB/WS/VIII/2026</t>
+          <t>015/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>11 Aug 2026</t>
+          <t>5 Agustus 2026</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -3393,17 +3561,17 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011587</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+          <t>Data Uji Coba</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -3413,20 +3581,20 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>forklift-loader cap min 5 Ton, call out, (hanya unit)</t>
+          <t>Provisional Sum (At Cost + 15% Fee)</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q22" t="n">
@@ -3434,19 +3602,19 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>16 Jul 2026</t>
+          <t>25 Aug 2026</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>11 Aug 2026</t>
+          <t>25 Aug 2026</t>
         </is>
       </c>
       <c r="T22" t="n">
-        <v>3500000</v>
+        <v>2500000</v>
       </c>
       <c r="U22" t="n">
-        <v>14000000</v>
+        <v>2875000</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -3475,12 +3643,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Forklit di Palabuhan Tangkian, Surabaya,Jakarta, Batam</t>
+          <t>Kabel Ukuran 2x2.5 mm panjang 50 Meter untuk Proyek</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-08-26 15:19:36</t>
+          <t>2026-08-26 18:30:06</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
@@ -3490,32 +3658,36 @@
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="inlineStr"/>
-      <c r="AJ22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7201250141</t>
+          <t>7203250036</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan Jasa Penyewaan Alat Berat Werehouse</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>S25048TPD</t>
+          <t>S250009SCM</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>014/BSS-JOB/WS/VIII/2026</t>
+          <t>010/BSS-JOB/WH/VII/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>11 Aug 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3530,22 +3702,22 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+          <t>03 Desember 2027</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500010848</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2 Januari 2026</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -3555,20 +3727,20 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>MOVING SEA FREIGHT TRANSPORT</t>
+          <t>MONTHLY BASIS</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Surabaya - Luwuk/ Senoro atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
+          <t>Daily Rate</t>
         </is>
       </c>
       <c r="O23" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q23" t="n">
@@ -3576,19 +3748,19 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>20 Jul 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>27 Jul 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="T23" t="n">
-        <v>22400000</v>
+        <v>1197000</v>
       </c>
       <c r="U23" t="n">
-        <v>22400000</v>
+        <v>28728000</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -3617,12 +3789,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>Pengiriman Barang dengan Kapal Cargo dari Jetty tankian ke Pelabuhan tanjung perak di surabaya</t>
+          <t>Untuk crew lokasi senoro</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-08-26 15:19:36</t>
+          <t>2026-08-26 18:30:06</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
@@ -3632,32 +3804,36 @@
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="inlineStr"/>
       <c r="AI23" t="inlineStr"/>
-      <c r="AJ23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7201250141</t>
+          <t>7203250036</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan Jasa Penyewaan Alat Berat Werehouse</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>S25048TPD</t>
+          <t>S250009SCM</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>014/BSS-JOB/WS/VIII/2026</t>
+          <t>010/BSS-JOB/WH/VII/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>11 Aug 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3672,22 +3848,22 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+          <t>03 Desember 2027</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500010848</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2 Januari 2026</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -3697,20 +3873,20 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>TRANSPORTASI DARI SURABAYA KE JABODETABEK:</t>
+          <t>MONTHLY BASIS</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Trailler 20 feet</t>
+          <t>Daily Rate</t>
         </is>
       </c>
       <c r="O24" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q24" t="n">
@@ -3718,7 +3894,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>28 Jul 2026</t>
+          <t>01 Jul 2026</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3727,10 +3903,10 @@
         </is>
       </c>
       <c r="T24" t="n">
-        <v>14000000</v>
+        <v>1197000</v>
       </c>
       <c r="U24" t="n">
-        <v>14000000</v>
+        <v>21546000</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -3759,12 +3935,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>Trucking 3 unit Pallet dari Pelabuhan Surabaya ke Pelabuhan di Jakarta</t>
+          <t>Forklift 5 ton, Operasi di  Werehouse Senoro 2 Periode 1 sd 31 Juli 2026</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-08-26 15:19:36</t>
+          <t>2026-08-26 18:30:06</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr"/>
@@ -3774,32 +3950,36 @@
       <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="inlineStr"/>
-      <c r="AJ24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7201250141</t>
+          <t>7203250036</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan Jasa Penyewaan Alat Berat Werehouse</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>S25048TPD</t>
+          <t>S250009SCM</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>014/BSS-JOB/WS/VIII/2026</t>
+          <t>010/BSS-JOB/WH/VII/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>11 Aug 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3814,22 +3994,22 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+          <t>03 Desember 2027</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500010848</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2 Januari 2026</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -3839,20 +4019,20 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>MOVING SEA FREIGHT TRANSPORT</t>
+          <t>MONTHLY BASIS</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Jabodetabek - Batam atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
+          <t>Standby Rate</t>
         </is>
       </c>
       <c r="O25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ls</t>
         </is>
       </c>
       <c r="Q25" t="n">
@@ -3860,19 +4040,19 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
+          <t>01 Jul 2026</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
           <t>31 Jul 2026</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>11 Aug 2026</t>
-        </is>
-      </c>
       <c r="T25" t="n">
-        <v>22400000</v>
+        <v>598500</v>
       </c>
       <c r="U25" t="n">
-        <v>22400000</v>
+        <v>1197000</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -3901,12 +4081,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>Pengiriman Barang dengan Kapal Cargo dari Pelabuhan di Jakarta ke Pelabuhan di Batam, door ke Penerima Barang</t>
+          <t>2 Unit Forklift Standby di CPP Senoro dan Werehouse Senoro 2 Periode 1 sd 31 Juli 2026</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-08-26 15:19:36</t>
+          <t>2026-08-26 18:30:06</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr"/>
@@ -3916,32 +4096,36 @@
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="inlineStr"/>
       <c r="AI25" t="inlineStr"/>
-      <c r="AJ25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>7201250141</t>
+          <t>7207250142</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>S25048TPD</t>
+          <t>S250551FLD-R1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>012/BSS-JOB/WS/VIII/2026</t>
+          <t>043/BSS-JOB/AB/VII/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3956,22 +4140,22 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>24 Month</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4500011586</t>
+          <t>4500011425</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
+          <t>Jasa Sewa Man Lift Untuk support Kegiatan Operation &amp; Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026, Refer CTR No. 7207250142-BSS-CTR-2026-020" (01 - 31 Juli 2026)</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>1 Jul 2026</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3981,20 +4165,20 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>MONTHLY BASIS</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Provisional Sum (At Cost + 15% Fee)</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q26" t="n">
@@ -4011,10 +4195,10 @@
         </is>
       </c>
       <c r="T26" t="n">
-        <v>21000000</v>
+        <v>75538000</v>
       </c>
       <c r="U26" t="n">
-        <v>24150000</v>
+        <v>1812912000</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -4043,12 +4227,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>Pembayaran Biaya Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
+          <t>Untuk crew lokasi senoro</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-08-26 15:19:36</t>
+          <t>2026-08-26 18:30:06</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr"/>
@@ -4058,7 +4242,11 @@
       <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="inlineStr"/>
-      <c r="AJ26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4190,7 +4378,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-08-26 15:19:36</t>
+          <t>2026-08-26 18:30:06</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr"/>
@@ -4274,15 +4462,15 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Aqua Galon Segel</t>
+          <t>Batu Agregate A</t>
         </is>
       </c>
       <c r="O28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="Q28" t="n">
@@ -4299,10 +4487,10 @@
         </is>
       </c>
       <c r="T28" t="n">
-        <v>53300</v>
+        <v>400000</v>
       </c>
       <c r="U28" t="n">
-        <v>533000</v>
+        <v>2000000</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -4331,12 +4519,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>Untuk konsumsi crew di senoro</t>
+          <t>Untuk timbunan jalan di senoro</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-08-26 15:19:36</t>
+          <t>2026-08-26 18:30:06</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr"/>
@@ -4370,7 +4558,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>016/BSS-JOB/WS/VIII/2026</t>
+          <t>017/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -4395,12 +4583,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4500011587</t>
+          <t>4500011588</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Pembelian Material Kabel dan Kayu untuk senoro</t>
+          <t>Pembelian Material dan Pengiriman barang ke Lokasi Senoro</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -4420,15 +4608,15 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Batu Agregate A</t>
+          <t>Aqua 600 ml</t>
         </is>
       </c>
       <c r="O29" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q29" t="n">
@@ -4445,10 +4633,10 @@
         </is>
       </c>
       <c r="T29" t="n">
-        <v>400000</v>
+        <v>7500</v>
       </c>
       <c r="U29" t="n">
-        <v>2000000</v>
+        <v>150000</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -4477,12 +4665,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>Untuk timbunan jalan di senoro</t>
+          <t>untuk crew di lokasi</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-08-26 15:19:36</t>
+          <t>2026-08-26 18:30:06</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr"/>
@@ -4494,7 +4682,299 @@
       <c r="AI29" t="inlineStr"/>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Gabungan (Barang &amp; Jasa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>017/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>05 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>4500011588</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Pembelian Material dan Pengiriman barang ke Lokasi Senoro</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Batu Kali</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
+        <v>10</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>100</v>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>26 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>26 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T30" t="n">
+        <v>325000</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3250000</v>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">untuk timbunanan </t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>2026-08-26 18:30:06</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr"/>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>Pekerjaan Gabungan (Barang &amp; Jasa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>017/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>05 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>4500011588</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Pembelian Material dan Pengiriman barang ke Lokasi Senoro</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Light / Medium truck 8T, Call Out, c/w operators</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>1</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>100</v>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>26 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>26 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T31" t="n">
+        <v>2250000</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2250000</v>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>untuk transprt material</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>2026-08-26 18:30:06</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr"/>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>Pekerjaan Gabungan (Barang &amp; Jasa)</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_transaksi_rincian.xlsx
+++ b/database_penyimpanan_aman/database_transaksi_rincian.xlsx
@@ -728,7 +728,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-08-26 18:30:06</t>
+          <t>2026-08-27 15:39:42</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-08-26 18:30:06</t>
+          <t>2026-08-27 15:39:42</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-08-26 18:30:06</t>
+          <t>2026-08-27 15:39:42</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-08-26 18:30:06</t>
+          <t>2026-08-27 15:39:42</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-08-26 18:30:06</t>
+          <t>2026-08-27 15:39:42</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-08-26 18:30:06</t>
+          <t>2026-08-27 15:39:42</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-08-26 18:30:06</t>
+          <t>2026-08-27 15:39:42</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-08-26 18:30:06</t>
+          <t>2026-08-27 15:39:42</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-08-26 18:30:06</t>
+          <t>2026-08-27 15:39:42</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-08-26 18:30:06</t>
+          <t>2026-08-27 15:39:42</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-08-26 18:30:06</t>
+          <t>2026-08-27 15:39:42</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
@@ -2222,12 +2222,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>012/BSS-JOB/WS/VIII/2026</t>
+          <t>014/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2242,22 +2242,22 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4500011586</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
+          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2267,20 +2267,20 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>MOVING SEA FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Provisional Sum (At Cost + 15% Fee)</t>
+          <t>Jasa repacking for Seafreight, estimasi ukuran pallet 100x100x100 cm</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>1</v>
+        <v>6.63</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Pallet</t>
         </is>
       </c>
       <c r="Q13" t="n">
@@ -2288,19 +2288,19 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>15 Jul 2026</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>15 Jul 2026</t>
         </is>
       </c>
       <c r="T13" t="n">
-        <v>21000000</v>
+        <v>1000000</v>
       </c>
       <c r="U13" t="n">
-        <v>24150000</v>
+        <v>6630000</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -2329,12 +2329,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Pembayaran Biaya Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
+          <t>3 Unit Pallet : dengan Ukuran 170x80x210 cm = 2,9 m3 190x150x75 cm = 2,1 m3 135x135x90 cm = 1,6 m3</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-08-26 18:30:06</t>
+          <t>2026-08-27 15:39:42</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
@@ -2413,20 +2413,20 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>MOVING SEA FREIGHT TRANSPORT</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Jasa repacking for Seafreight, estimasi ukuran pallet 100x100x100 cm</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>6.63</v>
+        <v>1</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Pallet</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q14" t="n">
@@ -2434,19 +2434,19 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>15 Jul 2026</t>
+          <t>16 Jul 2026</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>15 Jul 2026</t>
+          <t>16 Jul 2026</t>
         </is>
       </c>
       <c r="T14" t="n">
-        <v>1000000</v>
+        <v>1600000</v>
       </c>
       <c r="U14" t="n">
-        <v>6630000</v>
+        <v>1600000</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -2475,12 +2475,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>3 Unit Pallet : dengan Ukuran 170x80x210 cm = 2,9 m3 190x150x75 cm = 2,1 m3 135x135x90 cm = 1,6 m3</t>
+          <t>Pengurusan Pickup Barang dari Senoro 2 ke Jetty Tangkian</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-08-26 18:30:06</t>
+          <t>2026-08-27 15:39:42</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr"/>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Tankian Jetty atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="O15" t="n">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q15" t="n">
@@ -2589,10 +2589,10 @@
         </is>
       </c>
       <c r="T15" t="n">
-        <v>1600000</v>
+        <v>6440000</v>
       </c>
       <c r="U15" t="n">
-        <v>1600000</v>
+        <v>6440000</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -2621,12 +2621,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Pengurusan Pickup Barang dari Senoro 2 ke Jetty Tangkian</t>
+          <t>Trucking Barang X-Mas Tree dari Senoro 2 ke Jetty di Tankian</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-08-26 18:30:06</t>
+          <t>2026-08-27 15:39:42</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr"/>
@@ -2705,20 +2705,20 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Tankian Jetty atau sebaliknya c/w BBM &amp; driver</t>
+          <t>forklift-loader cap min 5 Ton, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q16" t="n">
@@ -2731,14 +2731,14 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>16 Jul 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="T16" t="n">
-        <v>6440000</v>
+        <v>3500000</v>
       </c>
       <c r="U16" t="n">
-        <v>6440000</v>
+        <v>14000000</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -2767,12 +2767,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Trucking Barang X-Mas Tree dari Senoro 2 ke Jetty di Tankian</t>
+          <t>Forklit di Palabuhan Tangkian, Surabaya,Jakarta, Batam</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-08-26 18:30:06</t>
+          <t>2026-08-27 15:39:42</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
@@ -2851,20 +2851,20 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>MOVING SEA FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>forklift-loader cap min 5 Ton, call out, (hanya unit)</t>
+          <t>Surabaya - Luwuk/ Senoro atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q17" t="n">
@@ -2872,19 +2872,19 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>16 Jul 2026</t>
+          <t>20 Jul 2026</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>11 Aug 2026</t>
+          <t>27 Jul 2026</t>
         </is>
       </c>
       <c r="T17" t="n">
-        <v>3500000</v>
+        <v>22400000</v>
       </c>
       <c r="U17" t="n">
-        <v>14000000</v>
+        <v>22400000</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -2913,12 +2913,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Forklit di Palabuhan Tangkian, Surabaya,Jakarta, Batam</t>
+          <t>Pengiriman Barang dengan Kapal Cargo dari Jetty tankian ke Pelabuhan tanjung perak di surabaya</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-08-26 18:30:06</t>
+          <t>2026-08-27 15:39:42</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
@@ -2997,12 +2997,12 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>MOVING SEA FREIGHT TRANSPORT</t>
+          <t>TRANSPORTASI DARI SURABAYA KE JABODETABEK:</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Surabaya - Luwuk/ Senoro atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
+          <t>Trailler 20 feet</t>
         </is>
       </c>
       <c r="O18" t="n">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="Q18" t="n">
@@ -3018,19 +3018,19 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>20 Jul 2026</t>
+          <t>28 Jul 2026</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>27 Jul 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="T18" t="n">
-        <v>22400000</v>
+        <v>14000000</v>
       </c>
       <c r="U18" t="n">
-        <v>22400000</v>
+        <v>14000000</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -3059,12 +3059,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Pengiriman Barang dengan Kapal Cargo dari Jetty tankian ke Pelabuhan tanjung perak di surabaya</t>
+          <t>Trucking 3 unit Pallet dari Pelabuhan Surabaya ke Pelabuhan di Jakarta</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-08-26 18:30:06</t>
+          <t>2026-08-27 15:39:42</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
@@ -3143,12 +3143,12 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>TRANSPORTASI DARI SURABAYA KE JABODETABEK:</t>
+          <t>MOVING SEA FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Trailler 20 feet</t>
+          <t>Jabodetabek - Batam atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
         </is>
       </c>
       <c r="O19" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q19" t="n">
@@ -3164,19 +3164,19 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>28 Jul 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="T19" t="n">
-        <v>14000000</v>
+        <v>22400000</v>
       </c>
       <c r="U19" t="n">
-        <v>14000000</v>
+        <v>22400000</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -3205,12 +3205,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Trucking 3 unit Pallet dari Pelabuhan Surabaya ke Pelabuhan di Jakarta</t>
+          <t>Pengiriman Barang dengan Kapal Cargo dari Pelabuhan di Jakarta ke Pelabuhan di Batam, door ke Penerima Barang</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-08-26 18:30:06</t>
+          <t>2026-08-27 15:39:42</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>014/BSS-JOB/WS/VIII/2026</t>
+          <t>015/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>11 Aug 2026</t>
+          <t>5 Agustus 2026</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -3269,17 +3269,17 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011587</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+          <t>Data Uji Coba</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -3289,20 +3289,20 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>MOVING SEA FREIGHT TRANSPORT</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Jabodetabek - Batam atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
+          <t>Aqua 600 ml</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q20" t="n">
@@ -3310,19 +3310,19 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>11 Aug 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="T20" t="n">
-        <v>22400000</v>
+        <v>7500</v>
       </c>
       <c r="U20" t="n">
-        <v>22400000</v>
+        <v>180000</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -3351,12 +3351,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>Pengiriman Barang dengan Kapal Cargo dari Pelabuhan di Jakarta ke Pelabuhan di Batam, door ke Penerima Barang</t>
+          <t>Untuk crew lokasi senoro</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-08-26 18:30:06</t>
+          <t>2026-08-27 15:39:42</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
@@ -3368,7 +3368,7 @@
       <c r="AI20" t="inlineStr"/>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
     </row>
@@ -3435,20 +3435,20 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Aqua 600 ml</t>
+          <t>Provisional Sum (At Cost + 15% Fee)</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q21" t="n">
@@ -3456,19 +3456,19 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>25 Aug 2026</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>25 Aug 2026</t>
         </is>
       </c>
       <c r="T21" t="n">
-        <v>7500</v>
+        <v>2500000</v>
       </c>
       <c r="U21" t="n">
-        <v>180000</v>
+        <v>2875000</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -3497,12 +3497,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>Untuk crew lokasi senoro</t>
+          <t>Kabel Ukuran 2x2.5 mm panjang 50 Meter untuk Proyek</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-08-26 18:30:06</t>
+          <t>2026-08-27 15:39:42</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
@@ -3521,27 +3521,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>7201250141</t>
+          <t>7207250142</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>S25048TPD</t>
+          <t>S250551FLD-R1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>015/BSS-JOB/WS/VIII/2026</t>
+          <t>043/BSS-JOB/AB/VII/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>5 Agustus 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -3556,22 +3556,22 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+          <t>24 Month</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4500011587</t>
+          <t>4500011425</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Data Uji Coba</t>
+          <t>Jasa Sewa Man Lift Untuk support Kegiatan Operation &amp; Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026, Refer CTR No. 7207250142-BSS-CTR-2026-020" (01 - 31 Juli 2026)</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>1 Jul 2026</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -3581,20 +3581,20 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>MONTHLY BASIS</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Provisional Sum (At Cost + 15% Fee)</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q22" t="n">
@@ -3602,19 +3602,19 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>25 Aug 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>25 Aug 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="T22" t="n">
-        <v>2500000</v>
+        <v>75538000</v>
       </c>
       <c r="U22" t="n">
-        <v>2875000</v>
+        <v>1812912000</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -3643,12 +3643,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Kabel Ukuran 2x2.5 mm panjang 50 Meter untuk Proyek</t>
+          <t>Untuk crew lokasi senoro</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-08-26 18:30:06</t>
+          <t>2026-08-27 15:39:42</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
@@ -3660,34 +3660,34 @@
       <c r="AI22" t="inlineStr"/>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7203250036</t>
+          <t>7201250141</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Penyediaan Jasa Penyewaan Alat Berat Werehouse</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>S250009SCM</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>010/BSS-JOB/WH/VII/2026</t>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3702,22 +3702,22 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>03 Desember 2027</t>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4500010848</t>
+          <t>4500011587</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton</t>
+          <t>Pembelian Material Kabel dan Kayu untuk senoro</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2 Januari 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Daily Rate</t>
+          <t>Aqua 600 ml</t>
         </is>
       </c>
       <c r="O23" t="n">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="T23" t="n">
-        <v>1197000</v>
+        <v>7500</v>
       </c>
       <c r="U23" t="n">
-        <v>28728000</v>
+        <v>180000</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-08-26 18:30:06</t>
+          <t>2026-08-27 15:39:42</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
@@ -3806,34 +3806,34 @@
       <c r="AI23" t="inlineStr"/>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7203250036</t>
+          <t>7201250141</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Penyediaan Jasa Penyewaan Alat Berat Werehouse</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>S250009SCM</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>010/BSS-JOB/WH/VII/2026</t>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>03 Desember 2027</t>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>4500010848</t>
+          <t>4500011587</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton</t>
+          <t>Pembelian Material Kabel dan Kayu untuk senoro</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2 Januari 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -3873,20 +3873,20 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Daily Rate</t>
+          <t>Batu Agregate A</t>
         </is>
       </c>
       <c r="O24" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="Q24" t="n">
@@ -3894,19 +3894,19 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>01 Jul 2026</t>
+          <t>26 Aug 2026</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>26 Aug 2026</t>
         </is>
       </c>
       <c r="T24" t="n">
-        <v>1197000</v>
+        <v>400000</v>
       </c>
       <c r="U24" t="n">
-        <v>21546000</v>
+        <v>2000000</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -3935,12 +3935,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>Forklift 5 ton, Operasi di  Werehouse Senoro 2 Periode 1 sd 31 Juli 2026</t>
+          <t>Untuk timbunan jalan di senoro</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-08-26 18:30:06</t>
+          <t>2026-08-27 15:39:42</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr"/>
@@ -3952,34 +3952,34 @@
       <c r="AI24" t="inlineStr"/>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7203250036</t>
+          <t>7201250141</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Penyediaan Jasa Penyewaan Alat Berat Werehouse</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>S250009SCM</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>010/BSS-JOB/WH/VII/2026</t>
+          <t>017/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3994,22 +3994,22 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>03 Desember 2027</t>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4500010848</t>
+          <t>4500011588</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton</t>
+          <t>Pembelian Material dan Pengiriman barang ke Lokasi Senoro</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2 Januari 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -4019,20 +4019,20 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Standby Rate</t>
+          <t>Aqua 600 ml</t>
         </is>
       </c>
       <c r="O25" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ls</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q25" t="n">
@@ -4040,19 +4040,19 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>01 Jul 2026</t>
+          <t>26 Aug 2026</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>26 Aug 2026</t>
         </is>
       </c>
       <c r="T25" t="n">
-        <v>598500</v>
+        <v>7500</v>
       </c>
       <c r="U25" t="n">
-        <v>1197000</v>
+        <v>150000</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -4081,12 +4081,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2 Unit Forklift Standby di CPP Senoro dan Werehouse Senoro 2 Periode 1 sd 31 Juli 2026</t>
+          <t>untuk crew di lokasi</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-08-26 18:30:06</t>
+          <t>2026-08-27 15:39:42</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr"/>
@@ -4098,34 +4098,34 @@
       <c r="AI25" t="inlineStr"/>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Gabungan (Barang &amp; Jasa)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>7207250142</t>
+          <t>7201250141</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>S250551FLD-R1</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>043/BSS-JOB/AB/VII/2026</t>
+          <t>017/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4140,22 +4140,22 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>24 Month</t>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4500011425</t>
+          <t>4500011588</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift Untuk support Kegiatan Operation &amp; Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026, Refer CTR No. 7207250142-BSS-CTR-2026-020" (01 - 31 Juli 2026)</t>
+          <t>Pembelian Material dan Pengiriman barang ke Lokasi Senoro</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1 Jul 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -4165,20 +4165,20 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP</t>
+          <t>Batu Kali</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="Q26" t="n">
@@ -4186,19 +4186,19 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>26 Aug 2026</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>26 Aug 2026</t>
         </is>
       </c>
       <c r="T26" t="n">
-        <v>75538000</v>
+        <v>325000</v>
       </c>
       <c r="U26" t="n">
-        <v>1812912000</v>
+        <v>3250000</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -4227,12 +4227,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>Untuk crew lokasi senoro</t>
+          <t>untuk timbunanan</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-08-26 18:30:06</t>
+          <t>2026-08-27 15:39:42</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr"/>
@@ -4244,7 +4244,7 @@
       <c r="AI26" t="inlineStr"/>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Gabungan (Barang &amp; Jasa)</t>
         </is>
       </c>
     </row>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>016/BSS-JOB/WS/VIII/2026</t>
+          <t>017/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -4291,12 +4291,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>4500011587</t>
+          <t>4500011588</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Pembelian Material Kabel dan Kayu untuk senoro</t>
+          <t>Pembelian Material dan Pengiriman barang ke Lokasi Senoro</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -4311,20 +4311,20 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Aqua 600 ml</t>
+          <t>Light / Medium truck 8T, Call Out, c/w operators</t>
         </is>
       </c>
       <c r="O27" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q27" t="n">
@@ -4332,19 +4332,19 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>26 Aug 2026</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>26 Aug 2026</t>
         </is>
       </c>
       <c r="T27" t="n">
-        <v>7500</v>
+        <v>2250000</v>
       </c>
       <c r="U27" t="n">
-        <v>180000</v>
+        <v>2250000</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>Untuk crew lokasi senoro</t>
+          <t>untuk transprt material</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-08-26 18:30:06</t>
+          <t>2026-08-27 15:39:42</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr"/>
@@ -4390,34 +4390,34 @@
       <c r="AI27" t="inlineStr"/>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Gabungan (Barang &amp; Jasa)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>7201250141</t>
+          <t>7203250036</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan Jasa Penyewaan Alat Berat Werehouse</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>S25048TPD</t>
+          <t>S250009SCM</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>016/BSS-JOB/WS/VIII/2026</t>
+          <t>010/BSS-JOB/WH/VII/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -4432,22 +4432,22 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>03 Desember 2027</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>4500011587</t>
+          <t>4500010848</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Pembelian Material Kabel dan Kayu untuk senoro</t>
+          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>2 Januari 2026</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -4457,20 +4457,20 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>MONTHLY BASIS</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Batu Agregate A</t>
+          <t>Daily Rate</t>
         </is>
       </c>
       <c r="O28" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q28" t="n">
@@ -4478,19 +4478,19 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>26 Aug 2026</t>
+          <t>01 Jul 2026</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>26 Aug 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="T28" t="n">
-        <v>400000</v>
+        <v>1197000</v>
       </c>
       <c r="U28" t="n">
-        <v>2000000</v>
+        <v>26334000</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -4519,12 +4519,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>Untuk timbunan jalan di senoro</t>
+          <t>Untuk crew lokasi senoro</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-08-26 18:30:06</t>
+          <t>2026-08-27 15:39:42</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr"/>
@@ -4536,34 +4536,34 @@
       <c r="AI28" t="inlineStr"/>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>7201250141</t>
+          <t>7203250036</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan Jasa Penyewaan Alat Berat Werehouse</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>S25048TPD</t>
+          <t>S250009SCM</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>017/BSS-JOB/WS/VIII/2026</t>
+          <t>010/BSS-JOB/WH/VII/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -4578,22 +4578,22 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>03 Desember 2027</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4500011588</t>
+          <t>4500010848</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Pembelian Material dan Pengiriman barang ke Lokasi Senoro</t>
+          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>2 Januari 2026</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -4603,20 +4603,20 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>MONTHLY BASIS</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Aqua 600 ml</t>
+          <t>Daily Rate</t>
         </is>
       </c>
       <c r="O29" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q29" t="n">
@@ -4624,19 +4624,19 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>26 Aug 2026</t>
+          <t>01 Jul 2026</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>26 Aug 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="T29" t="n">
-        <v>7500</v>
+        <v>1197000</v>
       </c>
       <c r="U29" t="n">
-        <v>150000</v>
+        <v>19152000</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -4665,12 +4665,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>untuk crew di lokasi</t>
+          <t>Forklift 5 ton, Operasi di  Werehouse Senoro 2 Periode 1 sd 31 Juli 2026</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-08-26 18:30:06</t>
+          <t>2026-08-27 15:39:42</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr"/>
@@ -4682,34 +4682,34 @@
       <c r="AI29" t="inlineStr"/>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>Pekerjaan Gabungan (Barang &amp; Jasa)</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>7201250141</t>
+          <t>7203250036</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan Jasa Penyewaan Alat Berat Werehouse</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>S25048TPD</t>
+          <t>S250009SCM</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>017/BSS-JOB/WS/VIII/2026</t>
+          <t>010/BSS-JOB/WH/VII/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -4724,22 +4724,22 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>03 Desember 2027</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>4500011588</t>
+          <t>4500010848</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Pembelian Material dan Pengiriman barang ke Lokasi Senoro</t>
+          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>2 Januari 2026</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -4749,20 +4749,20 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>MONTHLY BASIS</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Batu Kali</t>
+          <t>Standby Rate</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>Ls</t>
         </is>
       </c>
       <c r="Q30" t="n">
@@ -4770,19 +4770,19 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>26 Aug 2026</t>
+          <t>01 Jul 2026</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>26 Aug 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="T30" t="n">
-        <v>325000</v>
+        <v>598500</v>
       </c>
       <c r="U30" t="n">
-        <v>3250000</v>
+        <v>1197000</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -4811,12 +4811,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t xml:space="preserve">untuk timbunanan </t>
+          <t>2 Unit Forklift Standby di CPP Senoro dan Werehouse Senoro 2 Periode 1 sd 31 Juli 2026</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-08-26 18:30:06</t>
+          <t>2026-08-27 15:39:42</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr"/>
@@ -4828,7 +4828,7 @@
       <c r="AI30" t="inlineStr"/>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>Pekerjaan Gabungan (Barang &amp; Jasa)</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>017/BSS-JOB/WS/VIII/2026</t>
+          <t>012/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>4500011588</t>
+          <t>4500011586</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Pembelian Material dan Pengiriman barang ke Lokasi Senoro</t>
+          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Light / Medium truck 8T, Call Out, c/w operators</t>
+          <t>Add Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O31" t="n">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q31" t="n">
@@ -4916,19 +4916,19 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>26 Aug 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>26 Aug 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="T31" t="n">
-        <v>2250000</v>
+        <v>21000000</v>
       </c>
       <c r="U31" t="n">
-        <v>2250000</v>
+        <v>24150000</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -4957,12 +4957,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>untuk transprt material</t>
+          <t>Pembayaran Biaya Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-08-26 18:30:06</t>
+          <t>2026-08-27 15:39:42</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr"/>
@@ -4974,7 +4974,7 @@
       <c r="AI31" t="inlineStr"/>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>Pekerjaan Gabungan (Barang &amp; Jasa)</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_transaksi_rincian.xlsx
+++ b/database_penyimpanan_aman/database_transaksi_rincian.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ31"/>
+  <dimension ref="A1:AJ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -728,7 +728,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-08-27 15:39:42</t>
+          <t>2026-09-07 13:58:41</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-08-27 15:39:42</t>
+          <t>2026-09-07 13:58:41</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-08-27 15:39:42</t>
+          <t>2026-09-07 13:58:41</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-08-27 15:39:42</t>
+          <t>2026-09-07 13:58:41</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-08-27 15:39:42</t>
+          <t>2026-09-07 13:58:41</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-08-27 15:39:42</t>
+          <t>2026-09-07 13:58:41</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-08-27 15:39:42</t>
+          <t>2026-09-07 13:58:41</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-08-27 15:39:42</t>
+          <t>2026-09-07 13:58:41</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-08-27 15:39:42</t>
+          <t>2026-09-07 13:58:41</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-08-27 15:39:42</t>
+          <t>2026-09-07 13:58:41</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-08-27 15:39:42</t>
+          <t>2026-09-07 13:58:41</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-08-27 15:39:42</t>
+          <t>2026-09-07 13:58:41</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-08-27 15:39:42</t>
+          <t>2026-09-07 13:58:41</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr"/>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-08-27 15:39:42</t>
+          <t>2026-09-07 13:58:41</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr"/>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-08-27 15:39:42</t>
+          <t>2026-09-07 13:58:41</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-08-27 15:39:42</t>
+          <t>2026-09-07 13:58:41</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-08-27 15:39:42</t>
+          <t>2026-09-07 13:58:41</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-08-27 15:39:42</t>
+          <t>2026-09-07 13:58:41</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-08-27 15:39:42</t>
+          <t>2026-09-07 13:58:41</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-08-27 15:39:42</t>
+          <t>2026-09-07 13:58:41</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-08-27 15:39:42</t>
+          <t>2026-09-07 13:58:41</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
@@ -3794,7 +3794,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-08-27 15:39:42</t>
+          <t>2026-09-07 13:58:41</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-08-27 15:39:42</t>
+          <t>2026-09-07 13:58:41</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr"/>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-08-27 15:39:42</t>
+          <t>2026-09-07 13:58:41</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr"/>
@@ -4232,7 +4232,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-08-27 15:39:42</t>
+          <t>2026-09-07 13:58:41</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr"/>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-08-27 15:39:42</t>
+          <t>2026-09-07 13:58:41</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr"/>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-08-27 15:39:42</t>
+          <t>2026-09-07 13:58:41</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr"/>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-08-27 15:39:42</t>
+          <t>2026-09-07 13:58:41</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr"/>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-08-27 15:39:42</t>
+          <t>2026-09-07 13:58:41</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr"/>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-08-27 15:39:42</t>
+          <t>2026-09-07 13:58:41</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr"/>
@@ -4978,6 +4978,298 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>001/BSS-JOB/WS/I/2026</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>17 Jan 2026</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>4500011581</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Material Pendukung Pekerjaan Sealant Cluster B</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>17 Jan 2026</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>SAFETY EQUIPMENT</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Barricade Tape/ police line 3" panjang @300m</t>
+        </is>
+      </c>
+      <c r="O32" t="n">
+        <v>4</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>100</v>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>17 Jan 2026</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>17 Jan 2026</t>
+        </is>
+      </c>
+      <c r="T32" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>Untuk Keperluan sumur di cluster B</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:58:41</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr"/>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>001/BSS-JOB/WS/I/2026</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>17 Jan 2026</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>4500011581</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Material Pendukung Pekerjaan Sealant Cluster B</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>17 Jan 2026</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Kabel 2x1.5mm NYA/NYM @50m</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>100</v>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>17 Jan 2026</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>17 Jan 2026</t>
+        </is>
+      </c>
+      <c r="T33" t="n">
+        <v>712500</v>
+      </c>
+      <c r="U33" t="n">
+        <v>285000</v>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>Untuk Keperluan sumur di cluster B</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:58:41</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr"/>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database_penyimpanan_aman/database_transaksi_rincian.xlsx
+++ b/database_penyimpanan_aman/database_transaksi_rincian.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ33"/>
+  <dimension ref="A1:AJ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -728,7 +728,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-09-07 13:58:41</t>
+          <t>2026-09-07 18:00:35</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-09-07 13:58:41</t>
+          <t>2026-09-07 18:00:35</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-09-07 13:58:41</t>
+          <t>2026-09-07 18:00:35</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-09-07 13:58:41</t>
+          <t>2026-09-07 18:00:35</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-09-07 13:58:41</t>
+          <t>2026-09-07 18:00:35</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-09-07 13:58:41</t>
+          <t>2026-09-07 18:00:35</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-09-07 13:58:41</t>
+          <t>2026-09-07 18:00:35</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-09-07 13:58:41</t>
+          <t>2026-09-07 18:00:35</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-09-07 13:58:41</t>
+          <t>2026-09-07 18:00:35</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-09-07 13:58:41</t>
+          <t>2026-09-07 18:00:35</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-09-07 13:58:41</t>
+          <t>2026-09-07 18:00:35</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
@@ -2222,12 +2222,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>014/BSS-JOB/WS/VIII/2026</t>
+          <t>015/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11 Aug 2026</t>
+          <t>5 Agustus 2026</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2247,17 +2247,17 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011587</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+          <t>Data Uji Coba</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2267,20 +2267,20 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>MOVING SEA FREIGHT TRANSPORT</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Jasa repacking for Seafreight, estimasi ukuran pallet 100x100x100 cm</t>
+          <t>Aqua 600 ml</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>6.63</v>
+        <v>24</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Pallet</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q13" t="n">
@@ -2288,19 +2288,19 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>15 Jul 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>15 Jul 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="T13" t="n">
-        <v>1000000</v>
+        <v>7500</v>
       </c>
       <c r="U13" t="n">
-        <v>6630000</v>
+        <v>180000</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -2329,12 +2329,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>3 Unit Pallet : dengan Ukuran 170x80x210 cm = 2,9 m3 190x150x75 cm = 2,1 m3 135x135x90 cm = 1,6 m3</t>
+          <t>Untuk crew lokasi senoro</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-09-07 13:58:41</t>
+          <t>2026-09-07 18:00:35</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
@@ -2346,7 +2346,7 @@
       <c r="AI13" t="inlineStr"/>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
     </row>
@@ -2368,12 +2368,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>014/BSS-JOB/WS/VIII/2026</t>
+          <t>015/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>11 Aug 2026</t>
+          <t>5 Agustus 2026</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011587</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+          <t>Data Uji Coba</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2413,12 +2413,12 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Provisional Sum (At Cost + 15% Fee)</t>
         </is>
       </c>
       <c r="O14" t="n">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q14" t="n">
@@ -2434,19 +2434,19 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>16 Jul 2026</t>
+          <t>25 Aug 2026</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>16 Jul 2026</t>
+          <t>25 Aug 2026</t>
         </is>
       </c>
       <c r="T14" t="n">
-        <v>1600000</v>
+        <v>2500000</v>
       </c>
       <c r="U14" t="n">
-        <v>1600000</v>
+        <v>2875000</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -2475,12 +2475,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Pengurusan Pickup Barang dari Senoro 2 ke Jetty Tangkian</t>
+          <t>Kabel Ukuran 2x2.5 mm panjang 50 Meter untuk Proyek</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-09-07 13:58:41</t>
+          <t>2026-09-07 18:00:35</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr"/>
@@ -2492,34 +2492,34 @@
       <c r="AI14" t="inlineStr"/>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>7201250141</t>
+          <t>7207250142</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>S25048TPD</t>
+          <t>S250551FLD-R1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>014/BSS-JOB/WS/VIII/2026</t>
+          <t>043/BSS-JOB/AB/VII/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>11 Aug 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2534,22 +2534,22 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+          <t>24 Month</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011425</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+          <t>Jasa Sewa Man Lift Untuk support Kegiatan Operation &amp; Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026, Refer CTR No. 7207250142-BSS-CTR-2026-020" (01 - 31 Juli 2026)</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1 Jul 2026</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2559,20 +2559,20 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>MONTHLY BASIS</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Tankian Jetty atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q15" t="n">
@@ -2580,19 +2580,19 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>16 Jul 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>16 Jul 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="T15" t="n">
-        <v>6440000</v>
+        <v>75538000</v>
       </c>
       <c r="U15" t="n">
-        <v>6440000</v>
+        <v>1812912000</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -2621,12 +2621,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Trucking Barang X-Mas Tree dari Senoro 2 ke Jetty di Tankian</t>
+          <t>Untuk crew lokasi senoro</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-09-07 13:58:41</t>
+          <t>2026-09-07 18:00:35</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr"/>
@@ -2660,12 +2660,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>014/BSS-JOB/WS/VIII/2026</t>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>11 Aug 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2680,22 +2680,22 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011587</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+          <t>Pembelian Material Kabel dan Kayu untuk senoro</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2705,20 +2705,20 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>forklift-loader cap min 5 Ton, call out, (hanya unit)</t>
+          <t>Aqua 600 ml</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q16" t="n">
@@ -2726,19 +2726,19 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>16 Jul 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>11 Aug 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="T16" t="n">
-        <v>3500000</v>
+        <v>7500</v>
       </c>
       <c r="U16" t="n">
-        <v>14000000</v>
+        <v>180000</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -2767,12 +2767,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Forklit di Palabuhan Tangkian, Surabaya,Jakarta, Batam</t>
+          <t>Untuk crew lokasi senoro</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-09-07 13:58:41</t>
+          <t>2026-09-07 18:00:35</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
@@ -2784,7 +2784,7 @@
       <c r="AI16" t="inlineStr"/>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
     </row>
@@ -2806,12 +2806,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>014/BSS-JOB/WS/VIII/2026</t>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11 Aug 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2826,22 +2826,22 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011587</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+          <t>Pembelian Material Kabel dan Kayu untuk senoro</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2851,20 +2851,20 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>MOVING SEA FREIGHT TRANSPORT</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Surabaya - Luwuk/ Senoro atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
+          <t>Batu Agregate A</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="Q17" t="n">
@@ -2872,19 +2872,19 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>20 Jul 2026</t>
+          <t>26 Aug 2026</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>27 Jul 2026</t>
+          <t>26 Aug 2026</t>
         </is>
       </c>
       <c r="T17" t="n">
-        <v>22400000</v>
+        <v>400000</v>
       </c>
       <c r="U17" t="n">
-        <v>22400000</v>
+        <v>2000000</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -2913,12 +2913,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Pengiriman Barang dengan Kapal Cargo dari Jetty tankian ke Pelabuhan tanjung perak di surabaya</t>
+          <t>Untuk timbunan jalan di senoro</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-09-07 13:58:41</t>
+          <t>2026-09-07 18:00:35</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
@@ -2930,7 +2930,7 @@
       <c r="AI17" t="inlineStr"/>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
     </row>
@@ -2952,12 +2952,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>014/BSS-JOB/WS/VIII/2026</t>
+          <t>017/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>11 Aug 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2972,22 +2972,22 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011588</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+          <t>Pembelian Material dan Pengiriman barang ke Lokasi Senoro</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2997,20 +2997,20 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>TRANSPORTASI DARI SURABAYA KE JABODETABEK:</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Trailler 20 feet</t>
+          <t>Aqua 600 ml</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q18" t="n">
@@ -3018,19 +3018,19 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>28 Jul 2026</t>
+          <t>26 Aug 2026</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>26 Aug 2026</t>
         </is>
       </c>
       <c r="T18" t="n">
-        <v>14000000</v>
+        <v>7500</v>
       </c>
       <c r="U18" t="n">
-        <v>14000000</v>
+        <v>150000</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -3059,12 +3059,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Trucking 3 unit Pallet dari Pelabuhan Surabaya ke Pelabuhan di Jakarta</t>
+          <t>untuk crew di lokasi</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-09-07 13:58:41</t>
+          <t>2026-09-07 18:00:35</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
@@ -3076,7 +3076,7 @@
       <c r="AI18" t="inlineStr"/>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Gabungan (Barang &amp; Jasa)</t>
         </is>
       </c>
     </row>
@@ -3098,12 +3098,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>014/BSS-JOB/WS/VIII/2026</t>
+          <t>017/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>11 Aug 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3118,22 +3118,22 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011588</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+          <t>Pembelian Material dan Pengiriman barang ke Lokasi Senoro</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -3143,20 +3143,20 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>MOVING SEA FREIGHT TRANSPORT</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Jabodetabek - Batam atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
+          <t>Batu Kali</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="Q19" t="n">
@@ -3164,19 +3164,19 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>26 Aug 2026</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>11 Aug 2026</t>
+          <t>26 Aug 2026</t>
         </is>
       </c>
       <c r="T19" t="n">
-        <v>22400000</v>
+        <v>325000</v>
       </c>
       <c r="U19" t="n">
-        <v>22400000</v>
+        <v>3250000</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -3205,12 +3205,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Pengiriman Barang dengan Kapal Cargo dari Pelabuhan di Jakarta ke Pelabuhan di Batam, door ke Penerima Barang</t>
+          <t>untuk timbunanan</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-09-07 13:58:41</t>
+          <t>2026-09-07 18:00:35</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
@@ -3222,7 +3222,7 @@
       <c r="AI19" t="inlineStr"/>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Gabungan (Barang &amp; Jasa)</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>015/BSS-JOB/WS/VIII/2026</t>
+          <t>017/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>5 Agustus 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -3264,17 +3264,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4500011587</t>
+          <t>4500011588</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Data Uji Coba</t>
+          <t>Pembelian Material dan Pengiriman barang ke Lokasi Senoro</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -3289,20 +3289,20 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Aqua 600 ml</t>
+          <t>Light / Medium truck 8T, Call Out, c/w operators</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q20" t="n">
@@ -3310,19 +3310,19 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>26 Aug 2026</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>26 Aug 2026</t>
         </is>
       </c>
       <c r="T20" t="n">
-        <v>7500</v>
+        <v>2250000</v>
       </c>
       <c r="U20" t="n">
-        <v>180000</v>
+        <v>2250000</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -3351,12 +3351,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>Untuk crew lokasi senoro</t>
+          <t>untuk transprt material</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-09-07 13:58:41</t>
+          <t>2026-09-07 18:00:35</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
@@ -3368,34 +3368,34 @@
       <c r="AI20" t="inlineStr"/>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Gabungan (Barang &amp; Jasa)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>7201250141</t>
+          <t>7203250036</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan Jasa Penyewaan Alat Berat Werehouse</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>S25048TPD</t>
+          <t>S250009SCM</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>015/BSS-JOB/WS/VIII/2026</t>
+          <t>010/BSS-JOB/WH/VII/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>5 Agustus 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3410,22 +3410,22 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+          <t>03 Desember 2027</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>4500011587</t>
+          <t>4500010848</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Data Uji Coba</t>
+          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>2 Januari 2026</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -3435,20 +3435,20 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>MONTHLY BASIS</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Provisional Sum (At Cost + 15% Fee)</t>
+          <t>Daily Rate</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q21" t="n">
@@ -3456,19 +3456,19 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>25 Aug 2026</t>
+          <t>01 Jul 2026</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>25 Aug 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="T21" t="n">
-        <v>2500000</v>
+        <v>1197000</v>
       </c>
       <c r="U21" t="n">
-        <v>2875000</v>
+        <v>26334000</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -3497,12 +3497,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>Kabel Ukuran 2x2.5 mm panjang 50 Meter untuk Proyek</t>
+          <t>Untuk crew lokasi senoro</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-09-07 13:58:41</t>
+          <t>2026-09-07 18:00:35</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
@@ -3514,29 +3514,29 @@
       <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>7207250142</t>
+          <t>7203250036</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+          <t>Penyediaan Jasa Penyewaan Alat Berat Werehouse</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>S250551FLD-R1</t>
+          <t>S250009SCM</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>043/BSS-JOB/AB/VII/2026</t>
+          <t>010/BSS-JOB/WH/VII/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3556,22 +3556,22 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>24 Month</t>
+          <t>03 Desember 2027</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4500011425</t>
+          <t>4500010848</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift Untuk support Kegiatan Operation &amp; Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026, Refer CTR No. 7207250142-BSS-CTR-2026-020" (01 - 31 Juli 2026)</t>
+          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1 Jul 2026</t>
+          <t>2 Januari 2026</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -3586,15 +3586,15 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP</t>
+          <t>Daily Rate</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q22" t="n">
@@ -3602,19 +3602,19 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>01 Jul 2026</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="T22" t="n">
-        <v>75538000</v>
+        <v>1197000</v>
       </c>
       <c r="U22" t="n">
-        <v>1812912000</v>
+        <v>19152000</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -3643,12 +3643,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Untuk crew lokasi senoro</t>
+          <t>Forklift 5 ton, Operasi di  Werehouse Senoro 2 Periode 1 sd 31 Juli 2026</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-09-07 13:58:41</t>
+          <t>2026-09-07 18:00:35</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
@@ -3667,27 +3667,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7201250141</t>
+          <t>7203250036</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan Jasa Penyewaan Alat Berat Werehouse</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>S25048TPD</t>
+          <t>S250009SCM</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>016/BSS-JOB/WS/VIII/2026</t>
+          <t>010/BSS-JOB/WH/VII/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3702,22 +3702,22 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>03 Desember 2027</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4500011587</t>
+          <t>4500010848</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Pembelian Material Kabel dan Kayu untuk senoro</t>
+          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>2 Januari 2026</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -3727,20 +3727,20 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>MONTHLY BASIS</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Aqua 600 ml</t>
+          <t>Standby Rate</t>
         </is>
       </c>
       <c r="O23" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Ls</t>
         </is>
       </c>
       <c r="Q23" t="n">
@@ -3748,19 +3748,19 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>01 Jul 2026</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="T23" t="n">
-        <v>7500</v>
+        <v>598500</v>
       </c>
       <c r="U23" t="n">
-        <v>180000</v>
+        <v>1197000</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -3789,12 +3789,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>Untuk crew lokasi senoro</t>
+          <t>2 Unit Forklift Standby di CPP Senoro dan Werehouse Senoro 2 Periode 1 sd 31 Juli 2026</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-09-07 13:58:41</t>
+          <t>2026-09-07 18:00:35</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
@@ -3806,7 +3806,7 @@
       <c r="AI23" t="inlineStr"/>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
     </row>
@@ -3828,7 +3828,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>016/BSS-JOB/WS/VIII/2026</t>
+          <t>012/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>4500011587</t>
+          <t>4500011586</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Pembelian Material Kabel dan Kayu untuk senoro</t>
+          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3873,20 +3873,20 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Batu Agregate A</t>
+          <t>Add Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q24" t="n">
@@ -3894,19 +3894,19 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>26 Aug 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>26 Aug 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="T24" t="n">
-        <v>400000</v>
+        <v>21000000</v>
       </c>
       <c r="U24" t="n">
-        <v>2000000</v>
+        <v>24150000</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -3935,12 +3935,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>Untuk timbunan jalan di senoro</t>
+          <t>Pembayaran Biaya Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-09-07 13:58:41</t>
+          <t>2026-09-07 18:00:35</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr"/>
@@ -3952,7 +3952,7 @@
       <c r="AI24" t="inlineStr"/>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
     </row>
@@ -3974,12 +3974,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>017/BSS-JOB/WS/VIII/2026</t>
+          <t>001/BSS-JOB/WS/I/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>17 Jan 2026</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3999,17 +3999,17 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4500011588</t>
+          <t>4500011581</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Pembelian Material dan Pengiriman barang ke Lokasi Senoro</t>
+          <t>Material Pendukung Pekerjaan Sealant Cluster B</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>17 Jan 2026</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -4019,20 +4019,20 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>SAFETY EQUIPMENT</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Aqua 600 ml</t>
+          <t>Barricade Tape/ police line 3" panjang @300m</t>
         </is>
       </c>
       <c r="O25" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q25" t="n">
@@ -4040,19 +4040,19 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>26 Aug 2026</t>
+          <t>17 Jan 2026</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>26 Aug 2026</t>
+          <t>17 Jan 2026</t>
         </is>
       </c>
       <c r="T25" t="n">
-        <v>7500</v>
+        <v>250000</v>
       </c>
       <c r="U25" t="n">
-        <v>150000</v>
+        <v>1000000</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -4081,12 +4081,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>untuk crew di lokasi</t>
+          <t>Untuk Keperluan sumur di cluster B</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-09-07 13:58:41</t>
+          <t>2026-09-07 18:00:35</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr"/>
@@ -4098,7 +4098,7 @@
       <c r="AI25" t="inlineStr"/>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>Pekerjaan Gabungan (Barang &amp; Jasa)</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
     </row>
@@ -4120,12 +4120,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>017/BSS-JOB/WS/VIII/2026</t>
+          <t>001/BSS-JOB/WS/I/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>17 Jan 2026</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4145,17 +4145,17 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4500011588</t>
+          <t>4500011581</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Pembelian Material dan Pengiriman barang ke Lokasi Senoro</t>
+          <t>Material Pendukung Pekerjaan Sealant Cluster B</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>17 Jan 2026</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -4170,15 +4170,15 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Batu Kali</t>
+          <t>Kabel 2x1.5mm NYA/NYM @50m</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>10</v>
+        <v>0.4</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q26" t="n">
@@ -4186,19 +4186,19 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>26 Aug 2026</t>
+          <t>17 Jan 2026</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>26 Aug 2026</t>
+          <t>17 Jan 2026</t>
         </is>
       </c>
       <c r="T26" t="n">
-        <v>325000</v>
+        <v>712500</v>
       </c>
       <c r="U26" t="n">
-        <v>3250000</v>
+        <v>285000</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -4227,12 +4227,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>untuk timbunanan</t>
+          <t>Untuk Keperluan sumur di cluster B</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-09-07 13:58:41</t>
+          <t>2026-09-07 18:00:35</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr"/>
@@ -4244,7 +4244,7 @@
       <c r="AI26" t="inlineStr"/>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>Pekerjaan Gabungan (Barang &amp; Jasa)</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
     </row>
@@ -4266,12 +4266,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>017/BSS-JOB/WS/VIII/2026</t>
+          <t>014/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -4286,22 +4286,22 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>4500011588</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Pembelian Material dan Pengiriman barang ke Lokasi Senoro</t>
+          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -4311,20 +4311,20 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>MOVING SEA FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Light / Medium truck 8T, Call Out, c/w operators</t>
+          <t>Jasa repacking for Seafreight, estimasi ukuran pallet 100x100x100 cm</t>
         </is>
       </c>
       <c r="O27" t="n">
-        <v>1</v>
+        <v>6.63</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Pallet</t>
         </is>
       </c>
       <c r="Q27" t="n">
@@ -4332,19 +4332,19 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>26 Aug 2026</t>
+          <t>15 Jul 2026</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>26 Aug 2026</t>
+          <t>15 Jul 2026</t>
         </is>
       </c>
       <c r="T27" t="n">
-        <v>2250000</v>
+        <v>1000000</v>
       </c>
       <c r="U27" t="n">
-        <v>2250000</v>
+        <v>6630000</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>untuk transprt material</t>
+          <t>3 Unit Pallet : dengan Ukuran 170x80x210 cm = 2,9 m3 190x150x75 cm = 2,1 m3 135x135x90 cm = 1,6 m3</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-09-07 13:58:41</t>
+          <t>2026-09-07 18:00:35</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr"/>
@@ -4390,34 +4390,34 @@
       <c r="AI27" t="inlineStr"/>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>Pekerjaan Gabungan (Barang &amp; Jasa)</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>7203250036</t>
+          <t>7201250141</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Penyediaan Jasa Penyewaan Alat Berat Werehouse</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>S250009SCM</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>010/BSS-JOB/WH/VII/2026</t>
+          <t>014/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -4432,22 +4432,22 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>03 Desember 2027</t>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>4500010848</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton</t>
+          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2 Januari 2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -4457,20 +4457,20 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Daily Rate</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O28" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q28" t="n">
@@ -4478,19 +4478,19 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>01 Jul 2026</t>
+          <t>16 Jul 2026</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>16 Jul 2026</t>
         </is>
       </c>
       <c r="T28" t="n">
-        <v>1197000</v>
+        <v>1600000</v>
       </c>
       <c r="U28" t="n">
-        <v>26334000</v>
+        <v>1600000</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -4519,12 +4519,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>Untuk crew lokasi senoro</t>
+          <t>Pengurusan Pickup Barang dari Senoro 2 ke Jetty Tangkian</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-09-07 13:58:41</t>
+          <t>2026-09-07 18:00:35</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr"/>
@@ -4543,27 +4543,27 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>7203250036</t>
+          <t>7201250141</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Penyediaan Jasa Penyewaan Alat Berat Werehouse</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>S250009SCM</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>010/BSS-JOB/WH/VII/2026</t>
+          <t>014/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -4578,22 +4578,22 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>03 Desember 2027</t>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4500010848</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton</t>
+          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2 Januari 2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -4603,20 +4603,20 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Daily Rate</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Tankian Jetty atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="O29" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q29" t="n">
@@ -4624,19 +4624,19 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>01 Jul 2026</t>
+          <t>16 Jul 2026</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>16 Jul 2026</t>
         </is>
       </c>
       <c r="T29" t="n">
-        <v>1197000</v>
+        <v>6440000</v>
       </c>
       <c r="U29" t="n">
-        <v>19152000</v>
+        <v>6440000</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -4665,12 +4665,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>Forklift 5 ton, Operasi di  Werehouse Senoro 2 Periode 1 sd 31 Juli 2026</t>
+          <t>Trucking Barang X-Mas Tree dari Senoro 2 ke Jetty di Tankian</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-09-07 13:58:41</t>
+          <t>2026-09-07 18:00:35</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr"/>
@@ -4689,27 +4689,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>7203250036</t>
+          <t>7201250141</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Penyediaan Jasa Penyewaan Alat Berat Werehouse</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>S250009SCM</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>010/BSS-JOB/WH/VII/2026</t>
+          <t>014/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -4724,22 +4724,22 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>03 Desember 2027</t>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>4500010848</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton</t>
+          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2 Januari 2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -4749,20 +4749,20 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Standby Rate</t>
+          <t>forklift-loader cap min 5 Ton, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ls</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q30" t="n">
@@ -4770,19 +4770,19 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>01 Jul 2026</t>
+          <t>16 Jul 2026</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="T30" t="n">
-        <v>598500</v>
+        <v>3500000</v>
       </c>
       <c r="U30" t="n">
-        <v>1197000</v>
+        <v>14000000</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -4811,12 +4811,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2 Unit Forklift Standby di CPP Senoro dan Werehouse Senoro 2 Periode 1 sd 31 Juli 2026</t>
+          <t>Forklit di Palabuhan Tangkian, Surabaya,Jakarta, Batam</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-09-07 13:58:41</t>
+          <t>2026-09-07 18:00:35</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr"/>
@@ -4850,12 +4850,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>012/BSS-JOB/WS/VIII/2026</t>
+          <t>014/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -4870,22 +4870,22 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>4500011586</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
+          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>MOVING SEA FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Add Cost + Fee 15%</t>
+          <t>Surabaya - Luwuk/ Senoro atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
         </is>
       </c>
       <c r="O31" t="n">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q31" t="n">
@@ -4916,19 +4916,19 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>20 Jul 2026</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>27 Jul 2026</t>
         </is>
       </c>
       <c r="T31" t="n">
-        <v>21000000</v>
+        <v>22400000</v>
       </c>
       <c r="U31" t="n">
-        <v>24150000</v>
+        <v>22400000</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -4957,12 +4957,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>Pembayaran Biaya Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
+          <t>Pengiriman Barang dengan Kapal Cargo dari Jetty tankian ke Pelabuhan tanjung perak di surabaya</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-09-07 13:58:41</t>
+          <t>2026-09-07 18:00:35</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr"/>
@@ -4996,12 +4996,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>001/BSS-JOB/WS/I/2026</t>
+          <t>014/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>17 Jan 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -5016,22 +5016,22 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>4500011581</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Material Pendukung Pekerjaan Sealant Cluster B</t>
+          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>17 Jan 2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -5041,20 +5041,20 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>SAFETY EQUIPMENT</t>
+          <t>MOVING SEA FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Barricade Tape/ police line 3" panjang @300m</t>
+          <t>Jabodetabek - Batam atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
         </is>
       </c>
       <c r="O32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q32" t="n">
@@ -5062,19 +5062,19 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>17 Jan 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>17 Jan 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="T32" t="n">
-        <v>250000</v>
+        <v>22400000</v>
       </c>
       <c r="U32" t="n">
-        <v>1000000</v>
+        <v>22400000</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -5103,12 +5103,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>Untuk Keperluan sumur di cluster B</t>
+          <t>Pengiriman Barang dengan Kapal Cargo dari Pelabuhan Sunda Kelapa  ke Pelabuhan di Batam</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-09-07 13:58:41</t>
+          <t>2026-09-07 18:00:35</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr"/>
@@ -5120,153 +5120,7 @@
       <c r="AI32" t="inlineStr"/>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>S25048TPD</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>001/BSS-JOB/WS/I/2026</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>17 Jan 2026</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>4500011581</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Material Pendukung Pekerjaan Sealant Cluster B</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>17 Jan 2026</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>IDR</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>PENGADAAN MATERIAL</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>Kabel 2x1.5mm NYA/NYM @50m</t>
-        </is>
-      </c>
-      <c r="O33" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
-      <c r="Q33" t="n">
-        <v>100</v>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>17 Jan 2026</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>17 Jan 2026</t>
-        </is>
-      </c>
-      <c r="T33" t="n">
-        <v>712500</v>
-      </c>
-      <c r="U33" t="n">
-        <v>285000</v>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>Cabang Luwuk</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>0167 0167 8888 303</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>PT. BANGGAI SENTRAL SULAWESI</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>Accounts Payable - Finance Department</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>Untuk Keperluan sumur di cluster B</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>2026-09-07 13:58:41</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr"/>
-      <c r="AD33" t="inlineStr"/>
-      <c r="AE33" t="inlineStr"/>
-      <c r="AF33" t="inlineStr"/>
-      <c r="AG33" t="inlineStr"/>
-      <c r="AH33" t="inlineStr"/>
-      <c r="AI33" t="inlineStr"/>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_transaksi_rincian.xlsx
+++ b/database_penyimpanan_aman/database_transaksi_rincian.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ32"/>
+  <dimension ref="A1:AK33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -597,6 +597,11 @@
           <t>Jenis BASTP</t>
         </is>
       </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>Nomor WAN / SA</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -728,7 +733,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-09-07 18:00:35</t>
+          <t>2026-09-07 22:13:27</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -743,6 +748,7 @@
           <t>Pekerjaan Jasa</t>
         </is>
       </c>
+      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -874,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-09-07 18:00:35</t>
+          <t>2026-09-07 22:13:27</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -889,6 +895,7 @@
           <t>Pekerjaan Jasa</t>
         </is>
       </c>
+      <c r="AK3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1020,7 +1027,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-09-07 18:00:35</t>
+          <t>2026-09-07 22:13:27</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -1035,6 +1042,7 @@
           <t>Pekerjaan Jasa</t>
         </is>
       </c>
+      <c r="AK4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1166,7 +1174,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-09-07 18:00:35</t>
+          <t>2026-09-07 22:13:27</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -1181,6 +1189,7 @@
           <t>Pekerjaan Jasa</t>
         </is>
       </c>
+      <c r="AK5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1312,7 +1321,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-09-07 18:00:35</t>
+          <t>2026-09-07 22:13:27</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -1327,6 +1336,7 @@
           <t>Pekerjaan Jasa</t>
         </is>
       </c>
+      <c r="AK6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1458,7 +1468,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-09-07 18:00:35</t>
+          <t>2026-09-07 22:13:27</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
@@ -1473,6 +1483,7 @@
           <t>Pekerjaan Jasa</t>
         </is>
       </c>
+      <c r="AK7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1604,7 +1615,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-09-07 18:00:35</t>
+          <t>2026-09-07 22:13:27</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
@@ -1619,6 +1630,7 @@
           <t>Pekerjaan Jasa</t>
         </is>
       </c>
+      <c r="AK8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1750,7 +1762,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-09-07 18:00:35</t>
+          <t>2026-09-07 22:13:27</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -1765,6 +1777,7 @@
           <t>Pekerjaan Jasa</t>
         </is>
       </c>
+      <c r="AK9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1896,7 +1909,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-09-07 18:00:35</t>
+          <t>2026-09-07 22:13:27</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
@@ -1911,6 +1924,7 @@
           <t>Pekerjaan Jasa</t>
         </is>
       </c>
+      <c r="AK10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2042,7 +2056,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-09-07 18:00:35</t>
+          <t>2026-09-07 22:13:27</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
@@ -2057,6 +2071,7 @@
           <t>Pekerjaan Jasa</t>
         </is>
       </c>
+      <c r="AK11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2188,7 +2203,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-09-07 18:00:35</t>
+          <t>2026-09-07 22:13:27</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
@@ -2203,6 +2218,7 @@
           <t>Pekerjaan Jasa</t>
         </is>
       </c>
+      <c r="AK12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2334,7 +2350,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-09-07 18:00:35</t>
+          <t>2026-09-07 22:13:27</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
@@ -2349,6 +2365,7 @@
           <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
+      <c r="AK13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2480,7 +2497,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-09-07 18:00:35</t>
+          <t>2026-09-07 22:13:27</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr"/>
@@ -2495,31 +2512,32 @@
           <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
+      <c r="AK14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>7207250142</t>
+          <t>7201250141</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>S250551FLD-R1</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>043/BSS-JOB/AB/VII/2026</t>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2534,22 +2552,22 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>24 Month</t>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4500011425</t>
+          <t>4500011587</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift Untuk support Kegiatan Operation &amp; Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026, Refer CTR No. 7207250142-BSS-CTR-2026-020" (01 - 31 Juli 2026)</t>
+          <t>Pembelian Material Kabel dan Kayu untuk senoro</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1 Jul 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2559,12 +2577,12 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP</t>
+          <t>Aqua 600 ml</t>
         </is>
       </c>
       <c r="O15" t="n">
@@ -2589,10 +2607,10 @@
         </is>
       </c>
       <c r="T15" t="n">
-        <v>75538000</v>
+        <v>7500</v>
       </c>
       <c r="U15" t="n">
-        <v>1812912000</v>
+        <v>180000</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -2626,7 +2644,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-09-07 18:00:35</t>
+          <t>2026-09-07 22:13:27</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr"/>
@@ -2638,9 +2656,10 @@
       <c r="AI15" t="inlineStr"/>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
-        </is>
-      </c>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2710,15 +2729,15 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Aqua 600 ml</t>
+          <t>Batu Agregate A</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="Q16" t="n">
@@ -2726,19 +2745,19 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>26 Aug 2026</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>26 Aug 2026</t>
         </is>
       </c>
       <c r="T16" t="n">
-        <v>7500</v>
+        <v>400000</v>
       </c>
       <c r="U16" t="n">
-        <v>180000</v>
+        <v>2000000</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -2767,12 +2786,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Untuk crew lokasi senoro</t>
+          <t>Untuk timbunan jalan di senoro</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-09-07 18:00:35</t>
+          <t>2026-09-07 22:13:27</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
@@ -2787,6 +2806,7 @@
           <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
+      <c r="AK16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2806,7 +2826,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>016/BSS-JOB/WS/VIII/2026</t>
+          <t>017/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2831,12 +2851,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4500011587</t>
+          <t>4500011588</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Pembelian Material Kabel dan Kayu untuk senoro</t>
+          <t>Pembelian Material dan Pengiriman barang ke Lokasi Senoro</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2856,15 +2876,15 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Batu Agregate A</t>
+          <t>Aqua 600 ml</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q17" t="n">
@@ -2881,10 +2901,10 @@
         </is>
       </c>
       <c r="T17" t="n">
-        <v>400000</v>
+        <v>7500</v>
       </c>
       <c r="U17" t="n">
-        <v>2000000</v>
+        <v>150000</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -2913,12 +2933,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Untuk timbunan jalan di senoro</t>
+          <t>untuk crew di lokasi</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-09-07 18:00:35</t>
+          <t>2026-09-07 22:13:27</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
@@ -2930,9 +2950,10 @@
       <c r="AI17" t="inlineStr"/>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
-        </is>
-      </c>
+          <t>Pekerjaan Gabungan (Barang &amp; Jasa)</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3002,15 +3023,15 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Aqua 600 ml</t>
+          <t>Batu Kali</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="Q18" t="n">
@@ -3027,10 +3048,10 @@
         </is>
       </c>
       <c r="T18" t="n">
-        <v>7500</v>
+        <v>325000</v>
       </c>
       <c r="U18" t="n">
-        <v>150000</v>
+        <v>3250000</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -3059,12 +3080,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>untuk crew di lokasi</t>
+          <t>untuk timbunanan</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-09-07 18:00:35</t>
+          <t>2026-09-07 22:13:27</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
@@ -3079,6 +3100,7 @@
           <t>Pekerjaan Gabungan (Barang &amp; Jasa)</t>
         </is>
       </c>
+      <c r="AK18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3143,20 +3165,20 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Batu Kali</t>
+          <t>Light / Medium truck 8T, Call Out, c/w operators</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q19" t="n">
@@ -3173,10 +3195,10 @@
         </is>
       </c>
       <c r="T19" t="n">
-        <v>325000</v>
+        <v>2250000</v>
       </c>
       <c r="U19" t="n">
-        <v>3250000</v>
+        <v>2250000</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -3205,12 +3227,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>untuk timbunanan</t>
+          <t>untuk transprt material</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-09-07 18:00:35</t>
+          <t>2026-09-07 22:13:27</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
@@ -3225,31 +3247,32 @@
           <t>Pekerjaan Gabungan (Barang &amp; Jasa)</t>
         </is>
       </c>
+      <c r="AK19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>7201250141</t>
+          <t>7203250036</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan Jasa Penyewaan Alat Berat Werehouse</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>S25048TPD</t>
+          <t>S250009SCM</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>017/BSS-JOB/WS/VIII/2026</t>
+          <t>010/BSS-JOB/WH/VII/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -3264,22 +3287,22 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>03 Desember 2027</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4500011588</t>
+          <t>4500010848</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Pembelian Material dan Pengiriman barang ke Lokasi Senoro</t>
+          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>2 Januari 2026</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -3289,20 +3312,20 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>MONTHLY BASIS</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Light / Medium truck 8T, Call Out, c/w operators</t>
+          <t>Daily Rate</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q20" t="n">
@@ -3310,19 +3333,19 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>26 Aug 2026</t>
+          <t>01 Jul 2026</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>26 Aug 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="T20" t="n">
-        <v>2250000</v>
+        <v>1197000</v>
       </c>
       <c r="U20" t="n">
-        <v>2250000</v>
+        <v>26334000</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -3351,12 +3374,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>untuk transprt material</t>
+          <t>Untuk crew lokasi senoro</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-09-07 18:00:35</t>
+          <t>2026-09-07 22:13:27</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
@@ -3368,9 +3391,10 @@
       <c r="AI20" t="inlineStr"/>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>Pekerjaan Gabungan (Barang &amp; Jasa)</t>
-        </is>
-      </c>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3444,11 +3468,11 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q21" t="n">
@@ -3468,7 +3492,7 @@
         <v>1197000</v>
       </c>
       <c r="U21" t="n">
-        <v>26334000</v>
+        <v>19152000</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -3497,12 +3521,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>Untuk crew lokasi senoro</t>
+          <t>Forklift 5 ton, Operasi di  Werehouse Senoro 2 Periode 1 sd 31 Juli 2026</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-09-07 18:00:35</t>
+          <t>2026-09-07 22:13:27</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
@@ -3517,6 +3541,7 @@
           <t>Pekerjaan Jasa</t>
         </is>
       </c>
+      <c r="AK21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3586,15 +3611,15 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Daily Rate</t>
+          <t>Standby Rate</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ls</t>
         </is>
       </c>
       <c r="Q22" t="n">
@@ -3611,11 +3636,11 @@
         </is>
       </c>
       <c r="T22" t="n">
+        <v>598500</v>
+      </c>
+      <c r="U22" t="n">
         <v>1197000</v>
       </c>
-      <c r="U22" t="n">
-        <v>19152000</v>
-      </c>
       <c r="V22" t="inlineStr">
         <is>
           <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
@@ -3643,12 +3668,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Forklift 5 ton, Operasi di  Werehouse Senoro 2 Periode 1 sd 31 Juli 2026</t>
+          <t>2 Unit Forklift Standby di CPP Senoro dan Werehouse Senoro 2 Periode 1 sd 31 Juli 2026</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-09-07 18:00:35</t>
+          <t>2026-09-07 22:13:27</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
@@ -3663,31 +3688,32 @@
           <t>Pekerjaan Jasa</t>
         </is>
       </c>
+      <c r="AK22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7203250036</t>
+          <t>7201250141</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Penyediaan Jasa Penyewaan Alat Berat Werehouse</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>S250009SCM</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>010/BSS-JOB/WH/VII/2026</t>
+          <t>001/BSS-JOB/WS/I/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>17 Jan 2026</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3702,22 +3728,22 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>03 Desember 2027</t>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4500010848</t>
+          <t>4500011581</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton</t>
+          <t>Material Pendukung Pekerjaan Sealant Cluster B</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2 Januari 2026</t>
+          <t>17 Jan 2026</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -3727,20 +3753,20 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>SAFETY EQUIPMENT</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Standby Rate</t>
+          <t>Barricade Tape/ police line 3" panjang @300m</t>
         </is>
       </c>
       <c r="O23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ls</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q23" t="n">
@@ -3748,19 +3774,19 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>01 Jul 2026</t>
+          <t>17 Jan 2026</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>17 Jan 2026</t>
         </is>
       </c>
       <c r="T23" t="n">
-        <v>598500</v>
+        <v>250000</v>
       </c>
       <c r="U23" t="n">
-        <v>1197000</v>
+        <v>1000000</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -3789,12 +3815,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2 Unit Forklift Standby di CPP Senoro dan Werehouse Senoro 2 Periode 1 sd 31 Juli 2026</t>
+          <t>Untuk Keperluan sumur di cluster B</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-09-07 18:00:35</t>
+          <t>2026-09-07 22:13:27</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
@@ -3806,9 +3832,10 @@
       <c r="AI23" t="inlineStr"/>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
-        </is>
-      </c>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3828,12 +3855,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>012/BSS-JOB/WS/VIII/2026</t>
+          <t>001/BSS-JOB/WS/I/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>17 Jan 2026</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3853,17 +3880,17 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>4500011586</t>
+          <t>4500011581</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
+          <t>Material Pendukung Pekerjaan Sealant Cluster B</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>17 Jan 2026</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -3873,20 +3900,20 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Add Cost + Fee 15%</t>
+          <t>Kabel 2x1.5mm NYA/NYM @50m</t>
         </is>
       </c>
       <c r="O24" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q24" t="n">
@@ -3894,19 +3921,19 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>17 Jan 2026</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>17 Jan 2026</t>
         </is>
       </c>
       <c r="T24" t="n">
-        <v>21000000</v>
+        <v>712500</v>
       </c>
       <c r="U24" t="n">
-        <v>24150000</v>
+        <v>285000</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -3935,12 +3962,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>Pembayaran Biaya Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
+          <t>Untuk Keperluan sumur di cluster B</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-09-07 18:00:35</t>
+          <t>2026-09-07 22:13:27</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr"/>
@@ -3952,9 +3979,10 @@
       <c r="AI24" t="inlineStr"/>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
-        </is>
-      </c>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3974,12 +4002,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>001/BSS-JOB/WS/I/2026</t>
+          <t>014/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>17 Jan 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3994,22 +4022,22 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4500011581</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Material Pendukung Pekerjaan Sealant Cluster B</t>
+          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>17 Jan 2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -4019,20 +4047,20 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>SAFETY EQUIPMENT</t>
+          <t>MOVING SEA FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Barricade Tape/ police line 3" panjang @300m</t>
+          <t>Jasa repacking for Seafreight, estimasi ukuran pallet 100x100x100 cm</t>
         </is>
       </c>
       <c r="O25" t="n">
-        <v>4</v>
+        <v>6.63</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Pallet</t>
         </is>
       </c>
       <c r="Q25" t="n">
@@ -4040,19 +4068,19 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>17 Jan 2026</t>
+          <t>15 Jul 2026</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>17 Jan 2026</t>
+          <t>15 Jul 2026</t>
         </is>
       </c>
       <c r="T25" t="n">
-        <v>250000</v>
+        <v>1000000</v>
       </c>
       <c r="U25" t="n">
-        <v>1000000</v>
+        <v>6630000</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -4081,12 +4109,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>Untuk Keperluan sumur di cluster B</t>
+          <t>3 Unit Pallet : dengan Ukuran 170x80x210 cm = 2,9 m3 190x150x75 cm = 2,1 m3 135x135x90 cm = 1,6 m3</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-09-07 18:00:35</t>
+          <t>2026-09-07 22:13:27</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr"/>
@@ -4098,9 +4126,10 @@
       <c r="AI25" t="inlineStr"/>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
-        </is>
-      </c>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4120,12 +4149,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>001/BSS-JOB/WS/I/2026</t>
+          <t>014/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>17 Jan 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4140,22 +4169,22 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4500011581</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Material Pendukung Pekerjaan Sealant Cluster B</t>
+          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>17 Jan 2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -4165,20 +4194,20 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Kabel 2x1.5mm NYA/NYM @50m</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q26" t="n">
@@ -4186,19 +4215,19 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>17 Jan 2026</t>
+          <t>16 Jul 2026</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>17 Jan 2026</t>
+          <t>16 Jul 2026</t>
         </is>
       </c>
       <c r="T26" t="n">
-        <v>712500</v>
+        <v>1600000</v>
       </c>
       <c r="U26" t="n">
-        <v>285000</v>
+        <v>1600000</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -4227,12 +4256,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>Untuk Keperluan sumur di cluster B</t>
+          <t>Pengurusan Pickup Barang dari Senoro 2 ke Jetty Tangkian</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-09-07 18:00:35</t>
+          <t>2026-09-07 22:13:27</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr"/>
@@ -4244,9 +4273,10 @@
       <c r="AI26" t="inlineStr"/>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
-        </is>
-      </c>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4311,20 +4341,20 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>MOVING SEA FREIGHT TRANSPORT</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Jasa repacking for Seafreight, estimasi ukuran pallet 100x100x100 cm</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Tankian Jetty atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="O27" t="n">
-        <v>6.63</v>
+        <v>1</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Pallet</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q27" t="n">
@@ -4332,19 +4362,19 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>15 Jul 2026</t>
+          <t>16 Jul 2026</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>15 Jul 2026</t>
+          <t>16 Jul 2026</t>
         </is>
       </c>
       <c r="T27" t="n">
-        <v>1000000</v>
+        <v>6440000</v>
       </c>
       <c r="U27" t="n">
-        <v>6630000</v>
+        <v>6440000</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -4373,12 +4403,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>3 Unit Pallet : dengan Ukuran 170x80x210 cm = 2,9 m3 190x150x75 cm = 2,1 m3 135x135x90 cm = 1,6 m3</t>
+          <t>Trucking Barang X-Mas Tree dari Senoro 2 ke Jetty di Tankian</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-09-07 18:00:35</t>
+          <t>2026-09-07 22:13:27</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr"/>
@@ -4393,6 +4423,7 @@
           <t>Pekerjaan Jasa</t>
         </is>
       </c>
+      <c r="AK27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4457,16 +4488,16 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>forklift-loader cap min 5 Ton, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="O28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
@@ -4483,14 +4514,14 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>16 Jul 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="T28" t="n">
-        <v>1600000</v>
+        <v>3500000</v>
       </c>
       <c r="U28" t="n">
-        <v>1600000</v>
+        <v>14000000</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -4519,12 +4550,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>Pengurusan Pickup Barang dari Senoro 2 ke Jetty Tangkian</t>
+          <t>Forklit di Palabuhan Tangkian, Surabaya,Jakarta, Batam</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-09-07 18:00:35</t>
+          <t>2026-09-07 22:13:27</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr"/>
@@ -4539,6 +4570,7 @@
           <t>Pekerjaan Jasa</t>
         </is>
       </c>
+      <c r="AK28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4603,12 +4635,12 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>MOVING SEA FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Tankian Jetty atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Surabaya - Luwuk/ Senoro atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
         </is>
       </c>
       <c r="O29" t="n">
@@ -4624,19 +4656,19 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>16 Jul 2026</t>
+          <t>20 Jul 2026</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>16 Jul 2026</t>
+          <t>27 Jul 2026</t>
         </is>
       </c>
       <c r="T29" t="n">
-        <v>6440000</v>
+        <v>22400000</v>
       </c>
       <c r="U29" t="n">
-        <v>6440000</v>
+        <v>22400000</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -4665,12 +4697,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>Trucking Barang X-Mas Tree dari Senoro 2 ke Jetty di Tankian</t>
+          <t>Pengiriman Barang dengan Kapal Cargo dari Jetty tankian ke Pelabuhan tanjung perak di surabaya</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-09-07 18:00:35</t>
+          <t>2026-09-07 22:13:27</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr"/>
@@ -4685,6 +4717,7 @@
           <t>Pekerjaan Jasa</t>
         </is>
       </c>
+      <c r="AK29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4749,20 +4782,20 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>MOVING SEA FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>forklift-loader cap min 5 Ton, call out, (hanya unit)</t>
+          <t>Jabodetabek - Batam atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q30" t="n">
@@ -4770,7 +4803,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>16 Jul 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -4779,10 +4812,10 @@
         </is>
       </c>
       <c r="T30" t="n">
-        <v>3500000</v>
+        <v>22400000</v>
       </c>
       <c r="U30" t="n">
-        <v>14000000</v>
+        <v>22400000</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -4811,12 +4844,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>Forklit di Palabuhan Tangkian, Surabaya,Jakarta, Batam</t>
+          <t>Pengiriman Barang dengan Kapal Cargo dari Pelabuhan Sunda Kelapa  ke Pelabuhan di Batam</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-09-07 18:00:35</t>
+          <t>2026-09-07 22:13:27</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr"/>
@@ -4831,6 +4864,7 @@
           <t>Pekerjaan Jasa</t>
         </is>
       </c>
+      <c r="AK30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4850,12 +4884,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>014/BSS-JOB/WS/VIII/2026</t>
+          <t>014A/BSS-JOB/WS/VII/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>11 Aug 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -4880,12 +4914,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+          <t>Pengiriman X-Mas Tree dari Pelabuhan Surabaya ke Pelabuhan Sunda Kelapa di Jakarta</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>01 Jul 2026</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -4895,12 +4929,12 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>MOVING SEA FREIGHT TRANSPORT</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Surabaya - Luwuk/ Senoro atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
+          <t>Transportasi dari Surabaya ke Jabodetabek: Trailler 20 feet</t>
         </is>
       </c>
       <c r="O31" t="n">
@@ -4916,19 +4950,19 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>20 Jul 2026</t>
+          <t>28 Jul 2026</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>27 Jul 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="T31" t="n">
-        <v>22400000</v>
+        <v>14000000</v>
       </c>
       <c r="U31" t="n">
-        <v>22400000</v>
+        <v>12600000</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -4957,12 +4991,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>Pengiriman Barang dengan Kapal Cargo dari Jetty tankian ke Pelabuhan tanjung perak di surabaya</t>
+          <t>Pengiriman X-Mas Tree dari Pelabuhan Surabaya ke Pelabuhan Sunda Kelapa di Jakarta</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-09-07 18:00:35</t>
+          <t>2026-09-07 22:13:27</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr"/>
@@ -4977,6 +5011,7 @@
           <t>Pekerjaan Jasa</t>
         </is>
       </c>
+      <c r="AK31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4996,12 +5031,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>014/BSS-JOB/WS/VIII/2026</t>
+          <t>012/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>11 Aug 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -5016,22 +5051,22 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011586</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -5041,12 +5076,12 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>MOVING SEA FREIGHT TRANSPORT</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Jabodetabek - Batam atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
+          <t>Transportasi dari Surabaya ke Jabodetabek: Trailler 20 feet</t>
         </is>
       </c>
       <c r="O32" t="n">
@@ -5062,19 +5097,19 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
+          <t>28 Jul 2026</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
           <t>31 Jul 2026</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>11 Aug 2026</t>
-        </is>
-      </c>
       <c r="T32" t="n">
-        <v>22400000</v>
+        <v>14000000</v>
       </c>
       <c r="U32" t="n">
-        <v>22400000</v>
+        <v>12600000</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -5103,12 +5138,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>Pengiriman Barang dengan Kapal Cargo dari Pelabuhan Sunda Kelapa  ke Pelabuhan di Batam</t>
+          <t>Pengiriman X-Mas Tree dari Pelabuhan Surabaya ke Pelabuhan Sunda Kelapa di Jakarta</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-09-07 18:00:35</t>
+          <t>2026-09-07 22:13:27</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr"/>
@@ -5123,6 +5158,162 @@
           <t>Pekerjaan Jasa</t>
         </is>
       </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>100004581</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>S250551FLD-R1</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>043/BSS-JOB/AB/VII/2026</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>31 Jul 2026</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>24 Month</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>4500011425</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Man Lift Untuk support Kegiatan Operation &amp; Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026, Refer CTR No. 7207250142-BSS-CTR-2026-020" (01 - 31 Juli 2026)</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>1 Jul 2026</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Transportasi dari Surabaya ke Jabodetabek: Trailler 20 feet</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>1</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>100</v>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>28 Jul 2026</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>31 Jul 2026</t>
+        </is>
+      </c>
+      <c r="T33" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="U33" t="n">
+        <v>12600000</v>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>Pengiriman X-Mas Tree dari Pelabuhan Surabaya ke Pelabuhan Sunda Kelapa di Jakarta</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>2026-09-07 22:13:27</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr"/>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>10000784</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/database_penyimpanan_aman/database_transaksi_rincian.xlsx
+++ b/database_penyimpanan_aman/database_transaksi_rincian.xlsx
@@ -733,7 +733,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-09-07 22:13:27</t>
+          <t>2026-09-08 07:14:14</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-09-07 22:13:27</t>
+          <t>2026-09-08 07:14:14</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-09-07 22:13:27</t>
+          <t>2026-09-08 07:14:14</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-09-07 22:13:27</t>
+          <t>2026-09-08 07:14:14</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-09-07 22:13:27</t>
+          <t>2026-09-08 07:14:14</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-09-07 22:13:27</t>
+          <t>2026-09-08 07:14:14</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-09-07 22:13:27</t>
+          <t>2026-09-08 07:14:14</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-09-07 22:13:27</t>
+          <t>2026-09-08 07:14:14</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-09-07 22:13:27</t>
+          <t>2026-09-08 07:14:14</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-09-07 22:13:27</t>
+          <t>2026-09-08 07:14:14</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
@@ -2203,7 +2203,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-09-07 22:13:27</t>
+          <t>2026-09-08 07:14:14</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-09-07 22:13:27</t>
+          <t>2026-09-08 07:14:14</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-09-07 22:13:27</t>
+          <t>2026-09-08 07:14:14</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr"/>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-09-07 22:13:27</t>
+          <t>2026-09-08 07:14:14</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr"/>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-09-07 22:13:27</t>
+          <t>2026-09-08 07:14:14</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-09-07 22:13:27</t>
+          <t>2026-09-08 07:14:14</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-09-07 22:13:27</t>
+          <t>2026-09-08 07:14:14</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-09-07 22:13:27</t>
+          <t>2026-09-08 07:14:14</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-09-07 22:13:27</t>
+          <t>2026-09-08 07:14:14</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-09-07 22:13:27</t>
+          <t>2026-09-08 07:14:14</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-09-07 22:13:27</t>
+          <t>2026-09-08 07:14:14</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-09-07 22:13:27</t>
+          <t>2026-09-08 07:14:14</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-09-07 22:13:27</t>
+          <t>2026-09-08 07:14:14</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr"/>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-09-07 22:13:27</t>
+          <t>2026-09-08 07:14:14</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr"/>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-09-07 22:13:27</t>
+          <t>2026-09-08 07:14:14</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr"/>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-09-07 22:13:27</t>
+          <t>2026-09-08 07:14:14</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr"/>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-09-07 22:13:27</t>
+          <t>2026-09-08 07:14:14</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr"/>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-09-07 22:13:27</t>
+          <t>2026-09-08 07:14:14</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr"/>
@@ -4849,7 +4849,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-09-07 22:13:27</t>
+          <t>2026-09-08 07:14:14</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr"/>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-09-07 22:13:27</t>
+          <t>2026-09-08 07:14:14</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr"/>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-09-07 22:13:27</t>
+          <t>2026-09-08 07:14:14</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr"/>
@@ -5227,12 +5227,12 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>MONTHLY BASIS</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Transportasi dari Surabaya ke Jabodetabek: Trailler 20 feet</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
         </is>
       </c>
       <c r="O33" t="n">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>28 Jul 2026</t>
+          <t>01 Jul 2026</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -5257,10 +5257,10 @@
         </is>
       </c>
       <c r="T33" t="n">
-        <v>14000000</v>
+        <v>62818000</v>
       </c>
       <c r="U33" t="n">
-        <v>12600000</v>
+        <v>62818000</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -5289,12 +5289,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>Pengiriman X-Mas Tree dari Pelabuhan Surabaya ke Pelabuhan Sunda Kelapa di Jakarta</t>
+          <t>Jasa sewa Manlift Periode Bulan Juli 2026</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-09-07 22:13:27</t>
+          <t>2026-09-08 07:14:14</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr"/>

--- a/database_penyimpanan_aman/database_transaksi_rincian.xlsx
+++ b/database_penyimpanan_aman/database_transaksi_rincian.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK33"/>
+  <dimension ref="A1:AK34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-09-08 07:14:14</t>
+          <t>2026-09-08 11:52:30</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-09-08 07:14:14</t>
+          <t>2026-09-08 11:52:30</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-09-08 07:14:14</t>
+          <t>2026-09-08 11:52:30</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-09-08 07:14:14</t>
+          <t>2026-09-08 11:52:30</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-09-08 07:14:14</t>
+          <t>2026-09-08 11:52:30</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-09-08 07:14:14</t>
+          <t>2026-09-08 11:52:30</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-09-08 07:14:14</t>
+          <t>2026-09-08 11:52:30</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-09-08 07:14:14</t>
+          <t>2026-09-08 11:52:30</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-09-08 07:14:14</t>
+          <t>2026-09-08 11:52:30</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-09-08 07:14:14</t>
+          <t>2026-09-08 11:52:30</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
@@ -2203,7 +2203,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-09-08 07:14:14</t>
+          <t>2026-09-08 11:52:30</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
@@ -2223,27 +2223,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>7201250141</t>
+          <t>7203250036</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan Jasa Penyewaan Alat Berat Werehouse</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>S25048TPD</t>
+          <t>S250009SCM</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>015/BSS-JOB/WS/VIII/2026</t>
+          <t>010/BSS-JOB/WH/VII/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>5 Agustus 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2258,22 +2258,22 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+          <t>03 Desember 2027</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4500011587</t>
+          <t>4500010848</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Data Uji Coba</t>
+          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>2 Januari 2026</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2283,16 +2283,16 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>MONTHLY BASIS</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Aqua 600 ml</t>
+          <t>Daily Rate</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -2304,19 +2304,19 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>01 Jul 2026</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="T13" t="n">
-        <v>7500</v>
+        <v>1197000</v>
       </c>
       <c r="U13" t="n">
-        <v>180000</v>
+        <v>26334000</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-09-08 07:14:14</t>
+          <t>2026-09-08 11:52:30</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
@@ -2362,7 +2362,7 @@
       <c r="AI13" t="inlineStr"/>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr"/>
@@ -2370,27 +2370,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>7201250141</t>
+          <t>7203250036</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan Jasa Penyewaan Alat Berat Werehouse</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>S25048TPD</t>
+          <t>S250009SCM</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>015/BSS-JOB/WS/VIII/2026</t>
+          <t>010/BSS-JOB/WH/VII/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>5 Agustus 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2405,22 +2405,22 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+          <t>03 Desember 2027</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4500011587</t>
+          <t>4500010848</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Data Uji Coba</t>
+          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>2 Januari 2026</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2430,20 +2430,20 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>MONTHLY BASIS</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Provisional Sum (At Cost + 15% Fee)</t>
+          <t>Daily Rate</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q14" t="n">
@@ -2451,19 +2451,19 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>25 Aug 2026</t>
+          <t>01 Jul 2026</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>25 Aug 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="T14" t="n">
-        <v>2500000</v>
+        <v>1197000</v>
       </c>
       <c r="U14" t="n">
-        <v>2875000</v>
+        <v>19152000</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -2492,12 +2492,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Kabel Ukuran 2x2.5 mm panjang 50 Meter untuk Proyek</t>
+          <t>Forklift 5 ton, Operasi di  Werehouse Senoro 2 Periode 1 sd 31 Juli 2026</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-09-08 07:14:14</t>
+          <t>2026-09-08 11:52:30</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr"/>
@@ -2509,7 +2509,7 @@
       <c r="AI14" t="inlineStr"/>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr"/>
@@ -2517,27 +2517,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>7201250141</t>
+          <t>7203250036</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan Jasa Penyewaan Alat Berat Werehouse</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>S25048TPD</t>
+          <t>S250009SCM</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>016/BSS-JOB/WS/VIII/2026</t>
+          <t>010/BSS-JOB/WH/VII/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2552,22 +2552,22 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>03 Desember 2027</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4500011587</t>
+          <t>4500010848</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Pembelian Material Kabel dan Kayu untuk senoro</t>
+          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>2 Januari 2026</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2577,20 +2577,20 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>MONTHLY BASIS</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Aqua 600 ml</t>
+          <t>Standby Rate</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Ls</t>
         </is>
       </c>
       <c r="Q15" t="n">
@@ -2598,19 +2598,19 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>01 Jul 2026</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="T15" t="n">
-        <v>7500</v>
+        <v>598500</v>
       </c>
       <c r="U15" t="n">
-        <v>180000</v>
+        <v>1197000</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -2639,12 +2639,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Untuk crew lokasi senoro</t>
+          <t>2 Unit Forklift Standby di CPP Senoro dan Werehouse Senoro 2 Periode 1 sd 31 Juli 2026</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-09-08 07:14:14</t>
+          <t>2026-09-08 11:52:30</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr"/>
@@ -2656,7 +2656,7 @@
       <c r="AI15" t="inlineStr"/>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr"/>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>016/BSS-JOB/WS/VIII/2026</t>
+          <t>001/BSS-JOB/WS/I/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>17 Jan 2026</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2704,17 +2704,17 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4500011587</t>
+          <t>4500011581</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Pembelian Material Kabel dan Kayu untuk senoro</t>
+          <t>Material Pendukung Pekerjaan Sealant Cluster B</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>17 Jan 2026</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2724,20 +2724,20 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>SAFETY EQUIPMENT</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Batu Agregate A</t>
+          <t>Barricade Tape/ police line 3" panjang @300m</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q16" t="n">
@@ -2745,19 +2745,19 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>26 Aug 2026</t>
+          <t>17 Jan 2026</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>26 Aug 2026</t>
+          <t>17 Jan 2026</t>
         </is>
       </c>
       <c r="T16" t="n">
-        <v>400000</v>
+        <v>250000</v>
       </c>
       <c r="U16" t="n">
-        <v>2000000</v>
+        <v>1000000</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -2786,12 +2786,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Untuk timbunan jalan di senoro</t>
+          <t>Untuk Keperluan sumur di cluster B</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-09-08 07:14:14</t>
+          <t>2026-09-08 11:52:30</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
@@ -2826,12 +2826,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>017/BSS-JOB/WS/VIII/2026</t>
+          <t>001/BSS-JOB/WS/I/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>17 Jan 2026</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2851,17 +2851,17 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4500011588</t>
+          <t>4500011581</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Pembelian Material dan Pengiriman barang ke Lokasi Senoro</t>
+          <t>Material Pendukung Pekerjaan Sealant Cluster B</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>17 Jan 2026</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2876,11 +2876,11 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Aqua 600 ml</t>
+          <t>Kabel 2x1.5mm NYA/NYM @50m</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>20</v>
+        <v>0.4</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -2892,19 +2892,19 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>26 Aug 2026</t>
+          <t>17 Jan 2026</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>26 Aug 2026</t>
+          <t>17 Jan 2026</t>
         </is>
       </c>
       <c r="T17" t="n">
-        <v>7500</v>
+        <v>712500</v>
       </c>
       <c r="U17" t="n">
-        <v>150000</v>
+        <v>285000</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -2933,12 +2933,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>untuk crew di lokasi</t>
+          <t>Untuk Keperluan sumur di cluster B</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-09-08 07:14:14</t>
+          <t>2026-09-08 11:52:30</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
@@ -2950,7 +2950,7 @@
       <c r="AI17" t="inlineStr"/>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>Pekerjaan Gabungan (Barang &amp; Jasa)</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr"/>
@@ -2973,12 +2973,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>017/BSS-JOB/WS/VIII/2026</t>
+          <t>014/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2993,22 +2993,22 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4500011588</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Pembelian Material dan Pengiriman barang ke Lokasi Senoro</t>
+          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -3018,20 +3018,20 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>MOVING SEA FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Batu Kali</t>
+          <t>Jasa repacking for Seafreight, estimasi ukuran pallet 100x100x100 cm</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>10</v>
+        <v>6.63</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>Pallet</t>
         </is>
       </c>
       <c r="Q18" t="n">
@@ -3039,19 +3039,19 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>26 Aug 2026</t>
+          <t>15 Jul 2026</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>26 Aug 2026</t>
+          <t>15 Jul 2026</t>
         </is>
       </c>
       <c r="T18" t="n">
-        <v>325000</v>
+        <v>1000000</v>
       </c>
       <c r="U18" t="n">
-        <v>3250000</v>
+        <v>6630000</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -3080,12 +3080,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>untuk timbunanan</t>
+          <t>3 Unit Pallet : dengan Ukuran 170x80x210 cm = 2,9 m3 190x150x75 cm = 2,1 m3 135x135x90 cm = 1,6 m3</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-09-08 07:14:14</t>
+          <t>2026-09-08 11:52:30</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
@@ -3097,7 +3097,7 @@
       <c r="AI18" t="inlineStr"/>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>Pekerjaan Gabungan (Barang &amp; Jasa)</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr"/>
@@ -3120,12 +3120,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>017/BSS-JOB/WS/VIII/2026</t>
+          <t>014/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3140,22 +3140,22 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4500011588</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Pembelian Material dan Pengiriman barang ke Lokasi Senoro</t>
+          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Light / Medium truck 8T, Call Out, c/w operators</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O19" t="n">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q19" t="n">
@@ -3186,19 +3186,19 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>26 Aug 2026</t>
+          <t>16 Jul 2026</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>26 Aug 2026</t>
+          <t>16 Jul 2026</t>
         </is>
       </c>
       <c r="T19" t="n">
-        <v>2250000</v>
+        <v>1600000</v>
       </c>
       <c r="U19" t="n">
-        <v>2250000</v>
+        <v>1600000</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -3227,12 +3227,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>untuk transprt material</t>
+          <t>Pengurusan Pickup Barang dari Senoro 2 ke Jetty Tangkian</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-09-08 07:14:14</t>
+          <t>2026-09-08 11:52:30</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
@@ -3244,7 +3244,7 @@
       <c r="AI19" t="inlineStr"/>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>Pekerjaan Gabungan (Barang &amp; Jasa)</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr"/>
@@ -3252,27 +3252,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>7203250036</t>
+          <t>7201250141</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Penyediaan Jasa Penyewaan Alat Berat Werehouse</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>S250009SCM</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>010/BSS-JOB/WH/VII/2026</t>
+          <t>014/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -3287,22 +3287,22 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>03 Desember 2027</t>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4500010848</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton</t>
+          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2 Januari 2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -3312,20 +3312,20 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>LAND TRANSPORTATION</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Daily Rate</t>
+          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Tankian Jetty atau sebaliknya c/w BBM &amp; driver</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q20" t="n">
@@ -3333,19 +3333,19 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>01 Jul 2026</t>
+          <t>16 Jul 2026</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>16 Jul 2026</t>
         </is>
       </c>
       <c r="T20" t="n">
-        <v>1197000</v>
+        <v>6440000</v>
       </c>
       <c r="U20" t="n">
-        <v>26334000</v>
+        <v>6440000</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>Untuk crew lokasi senoro</t>
+          <t>Trucking Barang X-Mas Tree dari Senoro 2 ke Jetty di Tankian</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-09-08 07:14:14</t>
+          <t>2026-09-08 11:52:30</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
@@ -3399,27 +3399,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>7203250036</t>
+          <t>7201250141</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Penyediaan Jasa Penyewaan Alat Berat Werehouse</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>S250009SCM</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>010/BSS-JOB/WH/VII/2026</t>
+          <t>014/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3434,22 +3434,22 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>03 Desember 2027</t>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>4500010848</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton</t>
+          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2 Januari 2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -3459,16 +3459,16 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Daily Rate</t>
+          <t>forklift-loader cap min 5 Ton, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -3480,19 +3480,19 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>01 Jul 2026</t>
+          <t>16 Jul 2026</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="T21" t="n">
-        <v>1197000</v>
+        <v>3500000</v>
       </c>
       <c r="U21" t="n">
-        <v>19152000</v>
+        <v>14000000</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>Forklift 5 ton, Operasi di  Werehouse Senoro 2 Periode 1 sd 31 Juli 2026</t>
+          <t>Forklit di Palabuhan Tangkian, Surabaya,Jakarta, Batam</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-09-08 07:14:14</t>
+          <t>2026-09-08 11:52:30</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
@@ -3546,27 +3546,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>7203250036</t>
+          <t>7201250141</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Penyediaan Jasa Penyewaan Alat Berat Werehouse</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>S250009SCM</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>010/BSS-JOB/WH/VII/2026</t>
+          <t>014/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -3581,22 +3581,22 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>03 Desember 2027</t>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4500010848</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton</t>
+          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2 Januari 2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -3606,20 +3606,20 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>MOVING SEA FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Standby Rate</t>
+          <t>Surabaya - Luwuk/ Senoro atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ls</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q22" t="n">
@@ -3627,19 +3627,19 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>01 Jul 2026</t>
+          <t>20 Jul 2026</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>27 Jul 2026</t>
         </is>
       </c>
       <c r="T22" t="n">
-        <v>598500</v>
+        <v>22400000</v>
       </c>
       <c r="U22" t="n">
-        <v>1197000</v>
+        <v>22400000</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -3668,12 +3668,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2 Unit Forklift Standby di CPP Senoro dan Werehouse Senoro 2 Periode 1 sd 31 Juli 2026</t>
+          <t>Pengiriman Barang dengan Kapal Cargo dari Jetty tankian ke Pelabuhan tanjung perak di surabaya</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-09-08 07:14:14</t>
+          <t>2026-09-08 11:52:30</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>001/BSS-JOB/WS/I/2026</t>
+          <t>014/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>17 Jan 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3728,22 +3728,22 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4500011581</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Material Pendukung Pekerjaan Sealant Cluster B</t>
+          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>17 Jan 2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -3753,20 +3753,20 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>SAFETY EQUIPMENT</t>
+          <t>MOVING SEA FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Barricade Tape/ police line 3" panjang @300m</t>
+          <t>Jabodetabek - Batam atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
         </is>
       </c>
       <c r="O23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q23" t="n">
@@ -3774,19 +3774,19 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>17 Jan 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>17 Jan 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="T23" t="n">
-        <v>250000</v>
+        <v>22400000</v>
       </c>
       <c r="U23" t="n">
-        <v>1000000</v>
+        <v>22400000</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -3815,12 +3815,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>Untuk Keperluan sumur di cluster B</t>
+          <t>Pengiriman Barang dengan Kapal Cargo dari Pelabuhan Sunda Kelapa  ke Pelabuhan di Batam</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-09-08 07:14:14</t>
+          <t>2026-09-08 11:52:30</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
@@ -3832,7 +3832,7 @@
       <c r="AI23" t="inlineStr"/>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr"/>
@@ -3855,12 +3855,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>001/BSS-JOB/WS/I/2026</t>
+          <t>014A/BSS-JOB/WS/VII/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>17 Jan 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3875,22 +3875,22 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>4500011581</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Material Pendukung Pekerjaan Sealant Cluster B</t>
+          <t>Pengiriman X-Mas Tree dari Pelabuhan Surabaya ke Pelabuhan Sunda Kelapa di Jakarta</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>17 Jan 2026</t>
+          <t>01 Jul 2026</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -3900,16 +3900,16 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Kabel 2x1.5mm NYA/NYM @50m</t>
+          <t>Transportasi dari Surabaya ke Jabodetabek: Trailler 20 feet</t>
         </is>
       </c>
       <c r="O24" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
@@ -3921,19 +3921,19 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>17 Jan 2026</t>
+          <t>28 Jul 2026</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>17 Jan 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="T24" t="n">
-        <v>712500</v>
+        <v>14000000</v>
       </c>
       <c r="U24" t="n">
-        <v>285000</v>
+        <v>12600000</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -3962,12 +3962,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>Untuk Keperluan sumur di cluster B</t>
+          <t>Pengiriman X-Mas Tree dari Pelabuhan Surabaya ke Pelabuhan Sunda Kelapa di Jakarta</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-09-08 07:14:14</t>
+          <t>2026-09-08 11:52:30</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr"/>
@@ -3979,7 +3979,7 @@
       <c r="AI24" t="inlineStr"/>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr"/>
@@ -3987,27 +3987,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7201250141</t>
+          <t>7207250142</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>S25048TPD</t>
+          <t>S250551FLD-R1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>014/BSS-JOB/WS/VIII/2026</t>
+          <t>043/BSS-JOB/AB/VII/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>11 Aug 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -4022,22 +4022,22 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+          <t>24 Month</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011425</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+          <t>Jasa Sewa Man Lift Untuk support Kegiatan Operation &amp; Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026, Refer CTR No. 7207250142-BSS-CTR-2026-020" (01 - 31 Juli 2026)</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1 Jul 2026</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -4047,20 +4047,20 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>MOVING SEA FREIGHT TRANSPORT</t>
+          <t>MONTHLY BASIS</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Jasa repacking for Seafreight, estimasi ukuran pallet 100x100x100 cm</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
         </is>
       </c>
       <c r="O25" t="n">
-        <v>6.63</v>
+        <v>1</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Pallet</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q25" t="n">
@@ -4068,19 +4068,19 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>15 Jul 2026</t>
+          <t>01 Jul 2026</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>15 Jul 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="T25" t="n">
-        <v>1000000</v>
+        <v>62818000</v>
       </c>
       <c r="U25" t="n">
-        <v>6630000</v>
+        <v>62818000</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -4109,12 +4109,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>3 Unit Pallet : dengan Ukuran 170x80x210 cm = 2,9 m3 190x150x75 cm = 2,1 m3 135x135x90 cm = 1,6 m3</t>
+          <t>Jasa sewa Manlift Periode Bulan Juli 2026</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-09-08 07:14:14</t>
+          <t>2026-09-08 11:52:30</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr"/>
@@ -4129,7 +4129,11 @@
           <t>Pekerjaan Jasa</t>
         </is>
       </c>
-      <c r="AK25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>10000784</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4149,12 +4153,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>014/BSS-JOB/WS/VIII/2026</t>
+          <t>002/BSS-JOB/WS/I/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>11 Aug 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4169,22 +4173,22 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+          <t>Material Pendukung Pekerjaan Sealant Cluster B</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -4194,20 +4198,20 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Add Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q26" t="n">
@@ -4215,19 +4219,19 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>16 Jul 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>16 Jul 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="T26" t="n">
-        <v>1600000</v>
+        <v>10000</v>
       </c>
       <c r="U26" t="n">
-        <v>1600000</v>
+        <v>1437500</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -4256,12 +4260,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>Pengurusan Pickup Barang dari Senoro 2 ke Jetty Tangkian</t>
+          <t>Garam Kasar Untuk Pekerjaan Sealant di Cluster B</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-09-08 07:14:14</t>
+          <t>2026-09-08 11:52:30</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr"/>
@@ -4273,10 +4277,14 @@
       <c r="AI26" t="inlineStr"/>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr"/>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4296,12 +4304,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>014/BSS-JOB/WS/VIII/2026</t>
+          <t>002/BSS-JOB/WS/I/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>11 Aug 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -4316,22 +4324,22 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+          <t>Material Pendukung Pekerjaan Sealant Cluster B</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -4341,20 +4349,20 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Tankian Jetty atau sebaliknya c/w BBM &amp; driver</t>
+          <t>Add Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O27" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q27" t="n">
@@ -4362,19 +4370,19 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>16 Jul 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>16 Jul 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="T27" t="n">
-        <v>6440000</v>
+        <v>15000</v>
       </c>
       <c r="U27" t="n">
-        <v>6440000</v>
+        <v>0</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -4403,12 +4411,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>Trucking Barang X-Mas Tree dari Senoro 2 ke Jetty di Tankian</t>
+          <t>Belerang Untuk Pekerjaan Sealant di Cluster B</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-09-08 07:14:14</t>
+          <t>2026-09-08 11:52:30</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr"/>
@@ -4420,10 +4428,14 @@
       <c r="AI27" t="inlineStr"/>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr"/>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4443,12 +4455,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>014/BSS-JOB/WS/VIII/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>11 Aug 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -4463,22 +4475,22 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -4488,20 +4500,20 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>forklift-loader cap min 5 Ton, call out, (hanya unit)</t>
+          <t>Add Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q28" t="n">
@@ -4509,19 +4521,19 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>16 Jul 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>11 Aug 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="T28" t="n">
-        <v>3500000</v>
+        <v>7654600</v>
       </c>
       <c r="U28" t="n">
-        <v>14000000</v>
+        <v>8802790</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -4550,12 +4562,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>Forklit di Palabuhan Tangkian, Surabaya,Jakarta, Batam</t>
+          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-09-08 07:14:14</t>
+          <t>2026-09-08 11:52:30</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr"/>
@@ -4567,10 +4579,14 @@
       <c r="AI28" t="inlineStr"/>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr"/>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4590,12 +4606,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>014/BSS-JOB/WS/VIII/2026</t>
+          <t>015/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>11 Aug 2026</t>
+          <t>16 Aug 2026</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -4620,12 +4636,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+          <t>Penyediaan  Paket Acara Peringatan  Hari Kemerdekaan RI Kegiatan Well Services 2026</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>16 Aug 2026</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -4635,12 +4651,12 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>MOVING SEA FREIGHT TRANSPORT</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Surabaya - Luwuk/ Senoro atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
+          <t>Add Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O29" t="n">
@@ -4656,19 +4672,19 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>20 Jul 2026</t>
+          <t>16 Aug 2026</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>27 Jul 2026</t>
+          <t>16 Aug 2026</t>
         </is>
       </c>
       <c r="T29" t="n">
-        <v>22400000</v>
+        <v>13000000</v>
       </c>
       <c r="U29" t="n">
-        <v>22400000</v>
+        <v>14950000</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -4697,12 +4713,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>Pengiriman Barang dengan Kapal Cargo dari Jetty tankian ke Pelabuhan tanjung perak di surabaya</t>
+          <t>Penyediaan  Paket Acara Peringatan  Hari Kemerdekaan RI Kegiatan Well Services 2026</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-09-08 07:14:14</t>
+          <t>2026-09-08 11:52:30</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr"/>
@@ -4717,7 +4733,11 @@
           <t>Pekerjaan Jasa</t>
         </is>
       </c>
-      <c r="AK29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4737,12 +4757,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>014/BSS-JOB/WS/VIII/2026</t>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>11 Aug 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -4757,7 +4777,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4767,12 +4787,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+          <t>ADDITIONAL CAMP SERVICES, Food &amp; beverage, main course ,Food &amp; beverage, snack coffee/ tea &amp; desert</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>08 Aug 2026</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -4782,16 +4802,16 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>MOVING SEA FREIGHT TRANSPORT</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Jabodetabek - Batam atau sebaliknya, AU = max 20 ton ( 20,000 kg atau 1 Kontainer 20 feet)</t>
+          <t>Food &amp; beverage, main course</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>1</v>
+        <v>2578</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
@@ -4803,19 +4823,19 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>08 Aug 2026</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>11 Aug 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="T30" t="n">
-        <v>22400000</v>
+        <v>65000</v>
       </c>
       <c r="U30" t="n">
-        <v>22400000</v>
+        <v>167570000</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -4844,12 +4864,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>Pengiriman Barang dengan Kapal Cargo dari Pelabuhan Sunda Kelapa  ke Pelabuhan di Batam</t>
+          <t>ADDITIONAL CAMP SERVICES, Food &amp; beverage, main course</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-09-08 07:14:14</t>
+          <t>2026-09-08 11:52:30</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr"/>
@@ -4864,7 +4884,11 @@
           <t>Pekerjaan Jasa</t>
         </is>
       </c>
-      <c r="AK30" t="inlineStr"/>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4884,12 +4908,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>014A/BSS-JOB/WS/VII/2026</t>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -4904,7 +4928,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4914,12 +4938,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Pengiriman X-Mas Tree dari Pelabuhan Surabaya ke Pelabuhan Sunda Kelapa di Jakarta</t>
+          <t>ADDITIONAL CAMP SERVICES, Food &amp; beverage, main course ,Food &amp; beverage, snack coffee/ tea &amp; desert</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>01 Jul 2026</t>
+          <t>08 Aug 2026</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -4929,16 +4953,16 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Transportasi dari Surabaya ke Jabodetabek: Trailler 20 feet</t>
+          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
         </is>
       </c>
       <c r="O31" t="n">
-        <v>1</v>
+        <v>1157</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
@@ -4950,19 +4974,19 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>28 Jul 2026</t>
+          <t>08 Aug 2026</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="T31" t="n">
-        <v>14000000</v>
+        <v>33000</v>
       </c>
       <c r="U31" t="n">
-        <v>12600000</v>
+        <v>38181000</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -4991,12 +5015,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>Pengiriman X-Mas Tree dari Pelabuhan Surabaya ke Pelabuhan Sunda Kelapa di Jakarta</t>
+          <t>ADDITIONAL CAMP SERVICES, Food &amp; beverage, snack coffee/ tea &amp; desert</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-09-08 07:14:14</t>
+          <t>2026-09-08 11:52:30</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr"/>
@@ -5011,7 +5035,11 @@
           <t>Pekerjaan Jasa</t>
         </is>
       </c>
-      <c r="AK31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5031,12 +5059,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>012/BSS-JOB/WS/VIII/2026</t>
+          <t>017/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>25 Aug 2026</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -5056,17 +5084,17 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>4500011586</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
+          <t>Pembelian Material dan Pengiriman barang ke Lokasi Senoro</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>25 Aug 2026</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -5076,12 +5104,12 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Transportasi dari Surabaya ke Jabodetabek: Trailler 20 feet</t>
+          <t>Add Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O32" t="n">
@@ -5097,19 +5125,19 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>28 Jul 2026</t>
+          <t>25 Aug 2026</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>25 Aug 2026</t>
         </is>
       </c>
       <c r="T32" t="n">
-        <v>14000000</v>
+        <v>1160000</v>
       </c>
       <c r="U32" t="n">
-        <v>12600000</v>
+        <v>1334000</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -5138,12 +5166,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>Pengiriman X-Mas Tree dari Pelabuhan Surabaya ke Pelabuhan Sunda Kelapa di Jakarta</t>
+          <t>Material Kabel Ukuran 3x2,5 mm Untuk Kegiatan SBHP di Senoro 2</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-09-08 07:14:14</t>
+          <t>2026-09-08 11:52:30</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr"/>
@@ -5155,39 +5183,39 @@
       <c r="AI32" t="inlineStr"/>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Gabungan (Barang &amp; Jasa)</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>100004581</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>7207250142</t>
+          <t>7201250141</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>S250551FLD-R1</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>043/BSS-JOB/AB/VII/2026</t>
+          <t>017/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>25 Aug 2026</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -5202,22 +5230,22 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>24 Month</t>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>4500011425</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift Untuk support Kegiatan Operation &amp; Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026, Refer CTR No. 7207250142-BSS-CTR-2026-020" (01 - 31 Juli 2026)</t>
+          <t>Pembelian Material dan Pengiriman barang ke Lokasi Senoro</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1 Jul 2026</t>
+          <t>25 Aug 2026</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -5227,12 +5255,12 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O33" t="n">
@@ -5240,7 +5268,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q33" t="n">
@@ -5248,19 +5276,19 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>01 Jul 2026</t>
+          <t>25 Aug 2026</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>25 Aug 2026</t>
         </is>
       </c>
       <c r="T33" t="n">
-        <v>62818000</v>
+        <v>1600000</v>
       </c>
       <c r="U33" t="n">
-        <v>62818000</v>
+        <v>1600000</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -5289,12 +5317,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>Jasa sewa Manlift Periode Bulan Juli 2026</t>
+          <t>Kendaraan Untuk Pengiriman Barang  dari Luwuk Ke Lokasi Senoro 2</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-09-08 07:14:14</t>
+          <t>2026-09-08 11:52:30</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr"/>
@@ -5306,12 +5334,163 @@
       <c r="AI33" t="inlineStr"/>
       <c r="AJ33" t="inlineStr">
         <is>
+          <t>Pekerjaan Gabungan (Barang &amp; Jasa)</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>012/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>05 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>4500011586</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Add Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>1</v>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>100</v>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>16 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>16 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T34" t="n">
+        <v>21000000</v>
+      </c>
+      <c r="U34" t="n">
+        <v>24150000</v>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:52:30</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr"/>
+      <c r="AJ34" t="inlineStr">
+        <is>
           <t>Pekerjaan Jasa</t>
         </is>
       </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>10000784</t>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>1000025786</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_transaksi_rincian.xlsx
+++ b/database_penyimpanan_aman/database_transaksi_rincian.xlsx
@@ -733,7 +733,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-09-08 11:52:30</t>
+          <t>2026-09-08 13:01:38</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-09-08 11:52:30</t>
+          <t>2026-09-08 13:01:38</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-09-08 11:52:30</t>
+          <t>2026-09-08 13:01:38</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-09-08 11:52:30</t>
+          <t>2026-09-08 13:01:38</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-09-08 11:52:30</t>
+          <t>2026-09-08 13:01:38</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-09-08 11:52:30</t>
+          <t>2026-09-08 13:01:38</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-09-08 11:52:30</t>
+          <t>2026-09-08 13:01:38</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-09-08 11:52:30</t>
+          <t>2026-09-08 13:01:38</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-09-08 11:52:30</t>
+          <t>2026-09-08 13:01:38</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-09-08 11:52:30</t>
+          <t>2026-09-08 13:01:38</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
@@ -2203,7 +2203,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-09-08 11:52:30</t>
+          <t>2026-09-08 13:01:38</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-09-08 11:52:30</t>
+          <t>2026-09-08 13:01:38</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-09-08 11:52:30</t>
+          <t>2026-09-08 13:01:38</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr"/>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-09-08 11:52:30</t>
+          <t>2026-09-08 13:01:38</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr"/>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-09-08 11:52:30</t>
+          <t>2026-09-08 13:01:38</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-09-08 11:52:30</t>
+          <t>2026-09-08 13:01:38</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-09-08 11:52:30</t>
+          <t>2026-09-08 13:01:38</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-09-08 11:52:30</t>
+          <t>2026-09-08 13:01:38</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-09-08 11:52:30</t>
+          <t>2026-09-08 13:01:38</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-09-08 11:52:30</t>
+          <t>2026-09-08 13:01:38</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-09-08 11:52:30</t>
+          <t>2026-09-08 13:01:38</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-09-08 11:52:30</t>
+          <t>2026-09-08 13:01:38</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-09-08 11:52:30</t>
+          <t>2026-09-08 13:01:38</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr"/>
@@ -3987,27 +3987,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7207250142</t>
+          <t>7201250141</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>S250551FLD-R1</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>043/BSS-JOB/AB/VII/2026</t>
+          <t>002/BSS-JOB/WS/I/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -4022,22 +4022,22 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>24 Month</t>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4500011425</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift Untuk support Kegiatan Operation &amp; Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026, Refer CTR No. 7207250142-BSS-CTR-2026-020" (01 - 31 Juli 2026)</t>
+          <t>Material Pendukung Pekerjaan Sealant Cluster B</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1 Jul 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -4047,20 +4047,20 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
+          <t>Add Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O25" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q25" t="n">
@@ -4068,19 +4068,19 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>01 Jul 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="T25" t="n">
-        <v>62818000</v>
+        <v>10000</v>
       </c>
       <c r="U25" t="n">
-        <v>62818000</v>
+        <v>1437500</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -4109,12 +4109,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>Jasa sewa Manlift Periode Bulan Juli 2026</t>
+          <t>Garam Kasar Untuk Pekerjaan Sealant di Cluster B</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-09-08 11:52:30</t>
+          <t>2026-09-08 13:01:38</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr"/>
@@ -4126,12 +4126,12 @@
       <c r="AI25" t="inlineStr"/>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>10000784</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4228,10 +4228,10 @@
         </is>
       </c>
       <c r="T26" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="U26" t="n">
-        <v>1437500</v>
+        <v>0</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -4260,12 +4260,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>Garam Kasar Untuk Pekerjaan Sealant di Cluster B</t>
+          <t>Belerang Untuk Pekerjaan Sealant di Cluster B</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-09-08 11:52:30</t>
+          <t>2026-09-08 13:01:38</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr"/>
@@ -4304,12 +4304,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>002/BSS-JOB/WS/I/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Material Pendukung Pekerjaan Sealant Cluster B</t>
+          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -4358,11 +4358,11 @@
         </is>
       </c>
       <c r="O27" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q27" t="n">
@@ -4370,19 +4370,19 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="T27" t="n">
-        <v>15000</v>
+        <v>7654600</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>8802790</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -4411,12 +4411,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>Belerang Untuk Pekerjaan Sealant di Cluster B</t>
+          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-09-08 11:52:30</t>
+          <t>2026-09-08 13:01:38</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr"/>
@@ -4455,12 +4455,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>015/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>16 Aug 2026</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -4475,22 +4475,22 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+          <t>Penyediaan  Paket Acara Peringatan  Hari Kemerdekaan RI Kegiatan Well Services 2026</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>16 Aug 2026</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -4521,19 +4521,19 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>16 Aug 2026</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>16 Aug 2026</t>
         </is>
       </c>
       <c r="T28" t="n">
-        <v>7654600</v>
+        <v>13000000</v>
       </c>
       <c r="U28" t="n">
-        <v>8802790</v>
+        <v>14950000</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -4562,12 +4562,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+          <t>Penyediaan  Paket Acara Peringatan  Hari Kemerdekaan RI Kegiatan Well Services 2026</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-09-08 11:52:30</t>
+          <t>2026-09-08 13:01:38</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr"/>
@@ -4579,7 +4579,7 @@
       <c r="AI28" t="inlineStr"/>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -4606,12 +4606,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>015/BSS-JOB/WS/VIII/2026</t>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>16 Aug 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Penyediaan  Paket Acara Peringatan  Hari Kemerdekaan RI Kegiatan Well Services 2026</t>
+          <t>ADDITIONAL CAMP SERVICES, Food &amp; beverage, main course ,Food &amp; beverage, snack coffee/ tea &amp; desert</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>16 Aug 2026</t>
+          <t>08 Aug 2026</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -4651,16 +4651,16 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Add Cost + Fee 15%</t>
+          <t>Food &amp; beverage, main course</t>
         </is>
       </c>
       <c r="O29" t="n">
-        <v>1</v>
+        <v>2578</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
@@ -4672,19 +4672,19 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>16 Aug 2026</t>
+          <t>08 Aug 2026</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>16 Aug 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="T29" t="n">
-        <v>13000000</v>
+        <v>65000</v>
       </c>
       <c r="U29" t="n">
-        <v>14950000</v>
+        <v>167570000</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>Penyediaan  Paket Acara Peringatan  Hari Kemerdekaan RI Kegiatan Well Services 2026</t>
+          <t>ADDITIONAL CAMP SERVICES, Food &amp; beverage, main course</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-09-08 11:52:30</t>
+          <t>2026-09-08 13:01:38</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr"/>
@@ -4807,11 +4807,11 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Food &amp; beverage, main course</t>
+          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>2578</v>
+        <v>1157</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
@@ -4832,10 +4832,10 @@
         </is>
       </c>
       <c r="T30" t="n">
-        <v>65000</v>
+        <v>33000</v>
       </c>
       <c r="U30" t="n">
-        <v>167570000</v>
+        <v>38181000</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -4864,12 +4864,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES, Food &amp; beverage, main course</t>
+          <t>ADDITIONAL CAMP SERVICES, Food &amp; beverage, snack coffee/ tea &amp; desert</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-09-08 11:52:30</t>
+          <t>2026-09-08 13:01:38</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr"/>
@@ -4908,12 +4908,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>016/BSS-JOB/WS/VIII/2026</t>
+          <t>017/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>31 Aug 2026</t>
+          <t>25 Aug 2026</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES, Food &amp; beverage, main course ,Food &amp; beverage, snack coffee/ tea &amp; desert</t>
+          <t>Pembelian Material dan Pengiriman barang ke Lokasi Senoro</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>08 Aug 2026</t>
+          <t>25 Aug 2026</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -4953,16 +4953,16 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
+          <t>Add Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O31" t="n">
-        <v>1157</v>
+        <v>1</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
@@ -4974,19 +4974,19 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>08 Aug 2026</t>
+          <t>25 Aug 2026</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>31 Aug 2026</t>
+          <t>25 Aug 2026</t>
         </is>
       </c>
       <c r="T31" t="n">
-        <v>33000</v>
+        <v>1160000</v>
       </c>
       <c r="U31" t="n">
-        <v>38181000</v>
+        <v>1334000</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -5015,12 +5015,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES, Food &amp; beverage, snack coffee/ tea &amp; desert</t>
+          <t>Material Kabel Ukuran 3x2,5 mm Untuk Kegiatan SBHP di Senoro 2</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-09-08 11:52:30</t>
+          <t>2026-09-08 13:01:38</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr"/>
@@ -5032,7 +5032,7 @@
       <c r="AI31" t="inlineStr"/>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Gabungan (Barang &amp; Jasa)</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Add Cost + Fee 15%</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O32" t="n">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q32" t="n">
@@ -5134,10 +5134,10 @@
         </is>
       </c>
       <c r="T32" t="n">
-        <v>1160000</v>
+        <v>1600000</v>
       </c>
       <c r="U32" t="n">
-        <v>1334000</v>
+        <v>1600000</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -5166,12 +5166,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>Material Kabel Ukuran 3x2,5 mm Untuk Kegiatan SBHP di Senoro 2</t>
+          <t>Kendaraan Untuk Pengiriman Barang  dari Luwuk Ke Lokasi Senoro 2</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-09-08 11:52:30</t>
+          <t>2026-09-08 13:01:38</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr"/>
@@ -5210,12 +5210,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>017/BSS-JOB/WS/VIII/2026</t>
+          <t>012/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>25 Aug 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -5235,17 +5235,17 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011586</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Pembelian Material dan Pengiriman barang ke Lokasi Senoro</t>
+          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>25 Aug 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Add Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O33" t="n">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q33" t="n">
@@ -5276,19 +5276,19 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>25 Aug 2026</t>
+          <t>16 Aug 2026</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>25 Aug 2026</t>
+          <t>16 Aug 2026</t>
         </is>
       </c>
       <c r="T33" t="n">
-        <v>1600000</v>
+        <v>21000000</v>
       </c>
       <c r="U33" t="n">
-        <v>1600000</v>
+        <v>24150000</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -5317,12 +5317,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>Kendaraan Untuk Pengiriman Barang  dari Luwuk Ke Lokasi Senoro 2</t>
+          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-09-08 11:52:30</t>
+          <t>2026-09-08 13:01:38</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr"/>
@@ -5334,39 +5334,39 @@
       <c r="AI33" t="inlineStr"/>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>Pekerjaan Gabungan (Barang &amp; Jasa)</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1000025786</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>7201250141</t>
+          <t>7207250142</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>S25048TPD</t>
+          <t>S250551FLD-R1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>012/BSS-JOB/WS/VIII/2026</t>
+          <t>043/BSS-JOB/AB/VII/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -5381,22 +5381,22 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>24 Month</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>4500011586</t>
+          <t>4500011425</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
+          <t>Jasa Sewa Man Lift Untuk support Kegiatan Operation &amp; Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026, Refer CTR No. 7207250142-BSS-CTR-2026-020" (01 - 31 Juli 2026)</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>1 Jul 2026</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Add Cost + Fee 15%</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
         </is>
       </c>
       <c r="O34" t="n">
@@ -5436,10 +5436,10 @@
         </is>
       </c>
       <c r="T34" t="n">
-        <v>21000000</v>
+        <v>62818000</v>
       </c>
       <c r="U34" t="n">
-        <v>24150000</v>
+        <v>72240700</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-09-08 11:52:30</t>
+          <t>2026-09-08 13:01:38</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr"/>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>1000025786</t>
+          <t>-</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_transaksi_rincian.xlsx
+++ b/database_penyimpanan_aman/database_transaksi_rincian.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK34"/>
+  <dimension ref="A1:AK46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-09-08 13:01:38</t>
+          <t>2026-09-09 15:24:35</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:01:38</t>
+          <t>2026-09-09 15:24:35</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-09-08 13:01:38</t>
+          <t>2026-09-09 15:24:35</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-09-08 13:01:38</t>
+          <t>2026-09-09 15:24:35</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-09-08 13:01:38</t>
+          <t>2026-09-09 15:24:35</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-09-08 13:01:38</t>
+          <t>2026-09-09 15:24:35</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-09-08 13:01:38</t>
+          <t>2026-09-09 15:24:35</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-09-08 13:01:38</t>
+          <t>2026-09-09 15:24:35</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-09-08 13:01:38</t>
+          <t>2026-09-09 15:24:35</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-09-08 13:01:38</t>
+          <t>2026-09-09 15:24:35</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
@@ -2203,7 +2203,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-09-08 13:01:38</t>
+          <t>2026-09-09 15:24:35</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-09-08 13:01:38</t>
+          <t>2026-09-09 15:24:35</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-09-08 13:01:38</t>
+          <t>2026-09-09 15:24:35</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr"/>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-09-08 13:01:38</t>
+          <t>2026-09-09 15:24:35</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr"/>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-09-08 13:01:38</t>
+          <t>2026-09-09 15:24:35</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-09-08 13:01:38</t>
+          <t>2026-09-09 15:24:35</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-09-08 13:01:38</t>
+          <t>2026-09-09 15:24:35</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-09-08 13:01:38</t>
+          <t>2026-09-09 15:24:35</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-09-08 13:01:38</t>
+          <t>2026-09-09 15:24:35</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-09-08 13:01:38</t>
+          <t>2026-09-09 15:24:35</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-09-08 13:01:38</t>
+          <t>2026-09-09 15:24:35</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-09-08 13:01:38</t>
+          <t>2026-09-09 15:24:35</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-09-08 13:01:38</t>
+          <t>2026-09-09 15:24:35</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr"/>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-09-08 13:01:38</t>
+          <t>2026-09-09 15:24:35</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr"/>
@@ -4265,7 +4265,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-09-08 13:01:38</t>
+          <t>2026-09-09 15:24:35</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr"/>
@@ -4416,7 +4416,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-09-08 13:01:38</t>
+          <t>2026-09-09 15:24:35</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr"/>
@@ -4567,7 +4567,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-09-08 13:01:38</t>
+          <t>2026-09-09 15:24:35</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr"/>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-09-08 13:01:38</t>
+          <t>2026-09-09 15:24:35</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr"/>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-09-08 13:01:38</t>
+          <t>2026-09-09 15:24:35</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr"/>
@@ -4908,12 +4908,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>017/BSS-JOB/WS/VIII/2026</t>
+          <t>012/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>25 Aug 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -4933,17 +4933,17 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011586</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Pembelian Material dan Pengiriman barang ke Lokasi Senoro</t>
+          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>25 Aug 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -4974,19 +4974,19 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>25 Aug 2026</t>
+          <t>16 Aug 2026</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>25 Aug 2026</t>
+          <t>16 Aug 2026</t>
         </is>
       </c>
       <c r="T31" t="n">
-        <v>1160000</v>
+        <v>21000000</v>
       </c>
       <c r="U31" t="n">
-        <v>1334000</v>
+        <v>24150000</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -5015,12 +5015,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>Material Kabel Ukuran 3x2,5 mm Untuk Kegiatan SBHP di Senoro 2</t>
+          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-09-08 13:01:38</t>
+          <t>2026-09-09 15:24:35</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr"/>
@@ -5032,39 +5032,39 @@
       <c r="AI31" t="inlineStr"/>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>Pekerjaan Gabungan (Barang &amp; Jasa)</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1000025786</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>7201250141</t>
+          <t>7207250142</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>S25048TPD</t>
+          <t>S250551FLD-R1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>017/BSS-JOB/WS/VIII/2026</t>
+          <t>043/BSS-JOB/AB/VII/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>25 Aug 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -5079,22 +5079,22 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>24 Month</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011425</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Pembelian Material dan Pengiriman barang ke Lokasi Senoro</t>
+          <t>Jasa Sewa Man Lift Untuk support Kegiatan Operation &amp; Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026, Refer CTR No. 7207250142-BSS-CTR-2026-020" (01 - 31 Juli 2026)</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>25 Aug 2026</t>
+          <t>1 Jul 2026</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
         </is>
       </c>
       <c r="O32" t="n">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q32" t="n">
@@ -5125,19 +5125,19 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>25 Aug 2026</t>
+          <t>16 Aug 2026</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>25 Aug 2026</t>
+          <t>16 Aug 2026</t>
         </is>
       </c>
       <c r="T32" t="n">
-        <v>1600000</v>
+        <v>62818000</v>
       </c>
       <c r="U32" t="n">
-        <v>1600000</v>
+        <v>72240700</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -5166,12 +5166,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>Kendaraan Untuk Pengiriman Barang  dari Luwuk Ke Lokasi Senoro 2</t>
+          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-09-08 13:01:38</t>
+          <t>2026-09-09 15:24:35</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr"/>
@@ -5183,7 +5183,7 @@
       <c r="AI32" t="inlineStr"/>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>Pekerjaan Gabungan (Barang &amp; Jasa)</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>012/BSS-JOB/WS/VIII/2026</t>
+          <t>017/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>25 Aug 2026</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -5235,17 +5235,17 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>4500011586</t>
+          <t>4500011682</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
+          <t>Penyediaan electric cable pendukung wellservice camp</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>24 Aug 2026</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -5276,19 +5276,19 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>16 Aug 2026</t>
+          <t>25 Aug 2026</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>16 Aug 2026</t>
+          <t>25 Aug 2026</t>
         </is>
       </c>
       <c r="T33" t="n">
-        <v>21000000</v>
+        <v>1160000</v>
       </c>
       <c r="U33" t="n">
-        <v>24150000</v>
+        <v>1334000</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -5317,12 +5317,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
+          <t>Penyediaan electric cable pendukung wellservice camp Ukuran 3x25 mm NYM</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-09-08 13:01:38</t>
+          <t>2026-09-09 15:24:35</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr"/>
@@ -5334,39 +5334,39 @@
       <c r="AI33" t="inlineStr"/>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>1000025786</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>7207250142</t>
+          <t>7201250141</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>S250551FLD-R1</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>043/BSS-JOB/AB/VII/2026</t>
+          <t>018/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>25 Aug 2026</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -5381,22 +5381,22 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>24 Month</t>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>4500011425</t>
+          <t>4500011683</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift Untuk support Kegiatan Operation &amp; Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026, Refer CTR No. 7207250142-BSS-CTR-2026-020" (01 - 31 Juli 2026)</t>
+          <t>Transport pengangkut electric cable pendukung wellservice camp</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>1 Jul 2026</t>
+          <t>24 Aug 2026</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -5406,12 +5406,12 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O34" t="n">
@@ -5419,7 +5419,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q34" t="n">
@@ -5427,19 +5427,19 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>16 Aug 2026</t>
+          <t>25 Aug 2026</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>16 Aug 2026</t>
+          <t>25 Aug 2026</t>
         </is>
       </c>
       <c r="T34" t="n">
-        <v>62818000</v>
+        <v>1600000</v>
       </c>
       <c r="U34" t="n">
-        <v>72240700</v>
+        <v>1600000</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -5468,12 +5468,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
+          <t>Transport pengangkut electric cable pendukung wellservice camp</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-09-08 13:01:38</t>
+          <t>2026-09-09 15:24:35</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr"/>
@@ -5494,6 +5494,1818 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>019/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>26 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Pengiriman 4 ea Set Valve dari Senoro 2 ke SPM Batam</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>24 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Batam - Luwuk/ Senoro atau sebaliknya</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>15</v>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>100</v>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>24 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>26 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T35" t="n">
+        <v>150000</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2250000</v>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>Cargo Manifest Barang Seat Valve No GS08/01 Tgl 24 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>2026-09-09 15:24:35</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr"/>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>019/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>26 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Pengiriman 4 ea Set Valve dari Senoro 2 ke SPM Batam</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>24 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Balikpapan - Batam atau sebaliknya</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>1</v>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Pallet</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>100</v>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>24 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>24 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T36" t="n">
+        <v>200000</v>
+      </c>
+      <c r="U36" t="n">
+        <v>200000</v>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>Pembuatan Wooden Pallet Box</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>2026-09-09 15:24:35</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr"/>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>019/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>26 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Pengiriman 4 ea Set Valve dari Senoro 2 ke SPM Batam</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>24 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="O37" t="n">
+        <v>1</v>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>100</v>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>24 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>24 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T37" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>Kendaraan Untuk Pengiriman dari Luwuk ke Bandara Luwuk</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>2026-09-09 15:24:35</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr"/>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr"/>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 04/09/2026</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>03 Sep 2026</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Add Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="O38" t="n">
+        <v>1</v>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>100</v>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="T38" t="n">
+        <v>5054500</v>
+      </c>
+      <c r="U38" t="n">
+        <v>5812675</v>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 04/09/2026</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>2026-09-09 15:24:35</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr"/>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr"/>
+      <c r="AI38" t="inlineStr"/>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>021/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>(Provsum)  Penyediaan kontainer box untuk penyimpanan APD dan Dokumen</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>03 Sep 2026</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Add Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="O39" t="n">
+        <v>2</v>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>100</v>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="T39" t="n">
+        <v>175000</v>
+      </c>
+      <c r="U39" t="n">
+        <v>517499.9999999999</v>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>Kontainer box ukuran 95 untuk Penyimpanan APD dan Dokument</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>2026-09-09 15:24:35</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr"/>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr"/>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>021/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>(Provsum)  Penyediaan kontainer box untuk penyimpanan APD dan Dokumen</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>03 Sep 2026</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Add Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="O40" t="n">
+        <v>1</v>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>100</v>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="T40" t="n">
+        <v>100000</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>Kontainer box ukuran 52 untuk Penyimpanan APD dan Dokument</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>2026-09-09 15:24:35</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr"/>
+      <c r="AD40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr"/>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr"/>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>022/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Civil Enginner melakukan Survey untuk pengukuran dudukan X-Mas Tree di Sumur Senoro 16</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>03 Sep 2026</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
+        </is>
+      </c>
+      <c r="O41" t="n">
+        <v>1</v>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>100</v>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="T41" t="n">
+        <v>750000</v>
+      </c>
+      <c r="U41" t="n">
+        <v>750000</v>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>Tenaga Civil Engineer melakukan survey di Lokasi Sumur Senoro 16</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>2026-09-09 15:24:35</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr"/>
+      <c r="AD41" t="inlineStr"/>
+      <c r="AE41" t="inlineStr"/>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr"/>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>022/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Civil Enginner melakukan Survey untuk pengukuran dudukan X-Mas Tree di Sumur Senoro 16</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>03 Sep 2026</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="O42" t="n">
+        <v>1</v>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>100</v>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="T42" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>Kendaraan Operasional Double Cabin DN 8890 RG untuk transportasi Survey ke Lokasi</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>2026-09-09 15:24:35</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr"/>
+      <c r="AD42" t="inlineStr"/>
+      <c r="AE42" t="inlineStr"/>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr"/>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>023/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
+        </is>
+      </c>
+      <c r="O43" t="n">
+        <v>22</v>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>100</v>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>08 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T43" t="n">
+        <v>750000</v>
+      </c>
+      <c r="U43" t="n">
+        <v>16500000</v>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>Personel GS - Koordinator Lapangan atas Nama Nur Afiata</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>2026-09-09 15:24:35</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr"/>
+      <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr"/>
+      <c r="AI43" t="inlineStr"/>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>023/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
+        </is>
+      </c>
+      <c r="O44" t="n">
+        <v>24</v>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>100</v>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>08 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T44" t="n">
+        <v>750000</v>
+      </c>
+      <c r="U44" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>Personel GS -HSE Officer  Lapangan atas I Gusti Ngurah Dwipayana</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>2026-09-09 15:24:35</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr"/>
+      <c r="AD44" t="inlineStr"/>
+      <c r="AE44" t="inlineStr"/>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr"/>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>023/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Welder (GTAW)</t>
+        </is>
+      </c>
+      <c r="O45" t="n">
+        <v>24</v>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>100</v>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>08 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T45" t="n">
+        <v>500000</v>
+      </c>
+      <c r="U45" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>Welder = Tenaga Paramedic atas Nama Meilita Bella di Lokasi Senoro</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>2026-09-09 15:24:35</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr"/>
+      <c r="AD45" t="inlineStr"/>
+      <c r="AE45" t="inlineStr"/>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr"/>
+      <c r="AI45" t="inlineStr"/>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>023/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Welder (GTAW)</t>
+        </is>
+      </c>
+      <c r="O46" t="n">
+        <v>24</v>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>100</v>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>08 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T46" t="n">
+        <v>500000</v>
+      </c>
+      <c r="U46" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>Welder = Tenaga Paramedic atas Nama Widiya Satuwo di Lokasi Senoro</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>2026-09-09 15:24:35</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr"/>
+      <c r="AD46" t="inlineStr"/>
+      <c r="AE46" t="inlineStr"/>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr"/>
+      <c r="AI46" t="inlineStr"/>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database_penyimpanan_aman/database_transaksi_rincian.xlsx
+++ b/database_penyimpanan_aman/database_transaksi_rincian.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK46"/>
+  <dimension ref="A1:AK98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-09-09 15:24:35</t>
+          <t>2026-09-10 13:42:18</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-09-09 15:24:35</t>
+          <t>2026-09-10 13:42:18</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-09-09 15:24:35</t>
+          <t>2026-09-10 13:42:18</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-09-09 15:24:35</t>
+          <t>2026-09-10 13:42:18</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-09-09 15:24:35</t>
+          <t>2026-09-10 13:42:18</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-09-09 15:24:35</t>
+          <t>2026-09-10 13:42:18</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-09-09 15:24:35</t>
+          <t>2026-09-10 13:42:18</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-09-09 15:24:35</t>
+          <t>2026-09-10 13:42:18</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-09-09 15:24:35</t>
+          <t>2026-09-10 13:42:18</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-09-09 15:24:35</t>
+          <t>2026-09-10 13:42:18</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
@@ -2203,7 +2203,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-09-09 15:24:35</t>
+          <t>2026-09-10 13:42:18</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-09-09 15:24:35</t>
+          <t>2026-09-10 13:42:18</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-09-09 15:24:35</t>
+          <t>2026-09-10 13:42:18</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr"/>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-09-09 15:24:35</t>
+          <t>2026-09-10 13:42:18</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr"/>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-09-09 15:24:35</t>
+          <t>2026-09-10 13:42:18</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-09-09 15:24:35</t>
+          <t>2026-09-10 13:42:18</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-09-09 15:24:35</t>
+          <t>2026-09-10 13:42:18</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-09-09 15:24:35</t>
+          <t>2026-09-10 13:42:18</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-09-09 15:24:35</t>
+          <t>2026-09-10 13:42:18</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-09-09 15:24:35</t>
+          <t>2026-09-10 13:42:18</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-09-09 15:24:35</t>
+          <t>2026-09-10 13:42:18</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-09-09 15:24:35</t>
+          <t>2026-09-10 13:42:18</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-09-09 15:24:35</t>
+          <t>2026-09-10 13:42:18</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr"/>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-09-09 15:24:35</t>
+          <t>2026-09-10 13:42:18</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr"/>
@@ -4265,7 +4265,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-09-09 15:24:35</t>
+          <t>2026-09-10 13:42:18</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr"/>
@@ -4416,7 +4416,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-09-09 15:24:35</t>
+          <t>2026-09-10 13:42:18</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr"/>
@@ -4567,7 +4567,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-09-09 15:24:35</t>
+          <t>2026-09-10 13:42:18</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr"/>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-09-09 15:24:35</t>
+          <t>2026-09-10 13:42:18</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr"/>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-09-09 15:24:35</t>
+          <t>2026-09-10 13:42:18</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr"/>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-09-09 15:24:35</t>
+          <t>2026-09-10 13:42:18</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr"/>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-09-09 15:24:35</t>
+          <t>2026-09-10 13:42:18</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr"/>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-09-09 15:24:35</t>
+          <t>2026-09-10 13:42:18</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr"/>
@@ -5473,7 +5473,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-09-09 15:24:35</t>
+          <t>2026-09-10 13:42:18</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr"/>
@@ -5624,7 +5624,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-09-09 15:24:35</t>
+          <t>2026-09-10 13:42:18</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr"/>
@@ -5775,7 +5775,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-09-09 15:24:35</t>
+          <t>2026-09-10 13:42:18</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr"/>
@@ -5926,7 +5926,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-09-09 15:24:35</t>
+          <t>2026-09-10 13:42:18</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr"/>
@@ -6077,7 +6077,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-09-09 15:24:35</t>
+          <t>2026-09-10 13:42:18</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr"/>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-09-09 15:24:35</t>
+          <t>2026-09-10 13:42:18</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr"/>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-09-09 15:24:35</t>
+          <t>2026-09-10 13:42:18</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr"/>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-09-09 15:24:35</t>
+          <t>2026-09-10 13:42:18</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr"/>
@@ -6681,7 +6681,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-09-09 15:24:35</t>
+          <t>2026-09-10 13:42:18</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr"/>
@@ -6832,7 +6832,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-09-09 15:24:35</t>
+          <t>2026-09-10 13:42:18</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr"/>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-09-09 15:24:35</t>
+          <t>2026-09-10 13:42:18</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr"/>
@@ -7134,7 +7134,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-09-09 15:24:35</t>
+          <t>2026-09-10 13:42:18</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr"/>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-09-09 15:24:35</t>
+          <t>2026-09-10 13:42:18</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr"/>
@@ -7306,6 +7306,7858 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Operator Crane</t>
+        </is>
+      </c>
+      <c r="O47" t="n">
+        <v>13</v>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>100</v>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>08 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>20 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T47" t="n">
+        <v>750000</v>
+      </c>
+      <c r="U47" t="n">
+        <v>9750000</v>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>Operator Crane Shift Siang atas nama Rasid A Laugi</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr"/>
+      <c r="AD47" t="inlineStr"/>
+      <c r="AE47" t="inlineStr"/>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr"/>
+      <c r="AI47" t="inlineStr"/>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Operator Crane</t>
+        </is>
+      </c>
+      <c r="O48" t="n">
+        <v>9</v>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>100</v>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>23 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T48" t="n">
+        <v>750000</v>
+      </c>
+      <c r="U48" t="n">
+        <v>6750000</v>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>Operator Crane Shift Siang atas nama Wanhar</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr"/>
+      <c r="AD48" t="inlineStr"/>
+      <c r="AE48" t="inlineStr"/>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr"/>
+      <c r="AI48" t="inlineStr"/>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Operator Crane</t>
+        </is>
+      </c>
+      <c r="O49" t="n">
+        <v>17</v>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>100</v>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>08 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T49" t="n">
+        <v>750000</v>
+      </c>
+      <c r="U49" t="n">
+        <v>12750000</v>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>Operator Crane Shift Malam  atas nama Ilsan Adjedar</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr"/>
+      <c r="AD49" t="inlineStr"/>
+      <c r="AE49" t="inlineStr"/>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="inlineStr"/>
+      <c r="AI49" t="inlineStr"/>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Rigger</t>
+        </is>
+      </c>
+      <c r="O50" t="n">
+        <v>22</v>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>100</v>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>08 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T50" t="n">
+        <v>650000</v>
+      </c>
+      <c r="U50" t="n">
+        <v>14300000</v>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>Rigger  Crane Shift Siang  atas nama Tison</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr"/>
+      <c r="AD50" t="inlineStr"/>
+      <c r="AE50" t="inlineStr"/>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="inlineStr"/>
+      <c r="AH50" t="inlineStr"/>
+      <c r="AI50" t="inlineStr"/>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Rigger</t>
+        </is>
+      </c>
+      <c r="O51" t="n">
+        <v>21</v>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>100</v>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>08 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T51" t="n">
+        <v>650000</v>
+      </c>
+      <c r="U51" t="n">
+        <v>13650000</v>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>Rigger  Crane Shift Malam  atas nama Agus Dg Mangata</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr"/>
+      <c r="AD51" t="inlineStr"/>
+      <c r="AE51" t="inlineStr"/>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="inlineStr"/>
+      <c r="AH51" t="inlineStr"/>
+      <c r="AI51" t="inlineStr"/>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Operator Heavy Equipment (Vacuum Truck)</t>
+        </is>
+      </c>
+      <c r="O52" t="n">
+        <v>21</v>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>100</v>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>09 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T52" t="n">
+        <v>500000</v>
+      </c>
+      <c r="U52" t="n">
+        <v>10500000</v>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>Operator Heavy Equipment (Vacuum Truck) atas nama Wijayanto Sucipto</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr"/>
+      <c r="AD52" t="inlineStr"/>
+      <c r="AE52" t="inlineStr"/>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="inlineStr"/>
+      <c r="AH52" t="inlineStr"/>
+      <c r="AI52" t="inlineStr"/>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Mechanic/ Electrician</t>
+        </is>
+      </c>
+      <c r="O53" t="n">
+        <v>23</v>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>100</v>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>09 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T53" t="n">
+        <v>600000</v>
+      </c>
+      <c r="U53" t="n">
+        <v>13800000</v>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Sugeng</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr"/>
+      <c r="AD53" t="inlineStr"/>
+      <c r="AE53" t="inlineStr"/>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="inlineStr"/>
+      <c r="AH53" t="inlineStr"/>
+      <c r="AI53" t="inlineStr"/>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Mechanic/ Electrician</t>
+        </is>
+      </c>
+      <c r="O54" t="n">
+        <v>23</v>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>100</v>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>09 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T54" t="n">
+        <v>600000</v>
+      </c>
+      <c r="U54" t="n">
+        <v>13800000</v>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Ahmad Dhani</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr"/>
+      <c r="AD54" t="inlineStr"/>
+      <c r="AE54" t="inlineStr"/>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="inlineStr"/>
+      <c r="AH54" t="inlineStr"/>
+      <c r="AI54" t="inlineStr"/>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
+        </is>
+      </c>
+      <c r="O55" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>100</v>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>09 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T55" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="U55" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr"/>
+      <c r="AD55" t="inlineStr"/>
+      <c r="AE55" t="inlineStr"/>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="inlineStr"/>
+      <c r="AH55" t="inlineStr"/>
+      <c r="AI55" t="inlineStr"/>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Portacamp - Living camp,ukuran 40FT (8 sleepers)</t>
+        </is>
+      </c>
+      <c r="O56" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>100</v>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>09 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T56" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="U56" t="n">
+        <v>9600000</v>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>Portacamp - Living camp,ukuran 40FT (8 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr"/>
+      <c r="AD56" t="inlineStr"/>
+      <c r="AE56" t="inlineStr"/>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="inlineStr"/>
+      <c r="AH56" t="inlineStr"/>
+      <c r="AI56" t="inlineStr"/>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+        </is>
+      </c>
+      <c r="O57" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>100</v>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>09 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T57" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="U57" t="n">
+        <v>44400000</v>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr"/>
+      <c r="AD57" t="inlineStr"/>
+      <c r="AE57" t="inlineStr"/>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="inlineStr"/>
+      <c r="AH57" t="inlineStr"/>
+      <c r="AI57" t="inlineStr"/>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+        </is>
+      </c>
+      <c r="O58" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>100</v>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>09 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T58" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="U58" t="n">
+        <v>44400000</v>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr"/>
+      <c r="AD58" t="inlineStr"/>
+      <c r="AE58" t="inlineStr"/>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="inlineStr"/>
+      <c r="AH58" t="inlineStr"/>
+      <c r="AI58" t="inlineStr"/>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+        </is>
+      </c>
+      <c r="O59" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>100</v>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>09 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T59" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="U59" t="n">
+        <v>11100000</v>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr"/>
+      <c r="AD59" t="inlineStr"/>
+      <c r="AE59" t="inlineStr"/>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="inlineStr"/>
+      <c r="AH59" t="inlineStr"/>
+      <c r="AI59" t="inlineStr"/>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+        </is>
+      </c>
+      <c r="O60" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>100</v>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>09 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T60" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="U60" t="n">
+        <v>11100000</v>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr"/>
+      <c r="AD60" t="inlineStr"/>
+      <c r="AE60" t="inlineStr"/>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="inlineStr"/>
+      <c r="AH60" t="inlineStr"/>
+      <c r="AI60" t="inlineStr"/>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Penyediaan Car &amp; Tansportation Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>06 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="O61" t="n">
+        <v>25</v>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>100</v>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T61" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="U61" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>Kendaraan Innova DN 1259 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr"/>
+      <c r="AD61" t="inlineStr"/>
+      <c r="AE61" t="inlineStr"/>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="inlineStr"/>
+      <c r="AH61" t="inlineStr"/>
+      <c r="AI61" t="inlineStr"/>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Penyediaan Car &amp; Tansportation Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>06 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="O62" t="n">
+        <v>15</v>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>100</v>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>21 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T62" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="U62" t="n">
+        <v>24000000</v>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>Kendaraan Innova DN 1258 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr"/>
+      <c r="AD62" t="inlineStr"/>
+      <c r="AE62" t="inlineStr"/>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="inlineStr"/>
+      <c r="AH62" t="inlineStr"/>
+      <c r="AI62" t="inlineStr"/>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Penyediaan Car &amp; Tansportation Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>06 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="O63" t="n">
+        <v>25</v>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>100</v>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T63" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="U63" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>Kendaraan Innova DN 1257 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr"/>
+      <c r="AD63" t="inlineStr"/>
+      <c r="AE63" t="inlineStr"/>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="inlineStr"/>
+      <c r="AH63" t="inlineStr"/>
+      <c r="AI63" t="inlineStr"/>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Penyediaan Car &amp; Tansportation Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>06 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="O64" t="n">
+        <v>4</v>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>100</v>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>11 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>14 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T64" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="U64" t="n">
+        <v>6400000</v>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>Kendaraan Pajero DN 1904 RA Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr"/>
+      <c r="AD64" t="inlineStr"/>
+      <c r="AE64" t="inlineStr"/>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="inlineStr"/>
+      <c r="AH64" t="inlineStr"/>
+      <c r="AI64" t="inlineStr"/>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Penyediaan Car &amp; Tansportation Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>06 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="O65" t="n">
+        <v>25</v>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>100</v>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T65" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="U65" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>Kendaraan Hilux DN 1916 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr"/>
+      <c r="AD65" t="inlineStr"/>
+      <c r="AE65" t="inlineStr"/>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="inlineStr"/>
+      <c r="AH65" t="inlineStr"/>
+      <c r="AI65" t="inlineStr"/>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Penyediaan Car &amp; Tansportation Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>06 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="O66" t="n">
+        <v>22</v>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>100</v>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>08 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T66" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="U66" t="n">
+        <v>35200000</v>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>Kendaraan Hilux DN 1917 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr"/>
+      <c r="AD66" t="inlineStr"/>
+      <c r="AE66" t="inlineStr"/>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="inlineStr"/>
+      <c r="AH66" t="inlineStr"/>
+      <c r="AI66" t="inlineStr"/>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Penyediaan Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
+        </is>
+      </c>
+      <c r="O67" t="n">
+        <v>7</v>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>100</v>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>08 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>14 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T67" t="n">
+        <v>8500000</v>
+      </c>
+      <c r="U67" t="n">
+        <v>59500000</v>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>Crane Tadano 70 ton Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr"/>
+      <c r="AD67" t="inlineStr"/>
+      <c r="AE67" t="inlineStr"/>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="inlineStr"/>
+      <c r="AH67" t="inlineStr"/>
+      <c r="AI67" t="inlineStr"/>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Penyediaan Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
+        </is>
+      </c>
+      <c r="O68" t="n">
+        <v>9</v>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>100</v>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>23 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T68" t="n">
+        <v>8500000</v>
+      </c>
+      <c r="U68" t="n">
+        <v>76500000</v>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>Crane Sany 100 Ton untuk menggantikan Crane Tadano 70 Ton yang rusak</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr"/>
+      <c r="AD68" t="inlineStr"/>
+      <c r="AE68" t="inlineStr"/>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="inlineStr"/>
+      <c r="AH68" t="inlineStr"/>
+      <c r="AI68" t="inlineStr"/>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Penyediaan Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
+        </is>
+      </c>
+      <c r="O69" t="n">
+        <v>21</v>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>100</v>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>09 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T69" t="n">
+        <v>2750000</v>
+      </c>
+      <c r="U69" t="n">
+        <v>57750000</v>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>Vacuum Truck  5000 L DN 8806 CH untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr"/>
+      <c r="AD69" t="inlineStr"/>
+      <c r="AE69" t="inlineStr"/>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="inlineStr"/>
+      <c r="AH69" t="inlineStr"/>
+      <c r="AI69" t="inlineStr"/>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>028/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Aqua 600 ml</t>
+        </is>
+      </c>
+      <c r="O70" t="n">
+        <v>1800</v>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>100</v>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>08 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T70" t="n">
+        <v>7500</v>
+      </c>
+      <c r="U70" t="n">
+        <v>12150000</v>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>Penyediaan Estimated Sum Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr"/>
+      <c r="AD70" t="inlineStr"/>
+      <c r="AE70" t="inlineStr"/>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="inlineStr"/>
+      <c r="AH70" t="inlineStr"/>
+      <c r="AI70" t="inlineStr"/>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>028/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Aqua Galon Segel</t>
+        </is>
+      </c>
+      <c r="O71" t="n">
+        <v>18</v>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>100</v>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T71" t="n">
+        <v>53300</v>
+      </c>
+      <c r="U71" t="n">
+        <v>863460</v>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>Penyediaan Estimated Sum Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr"/>
+      <c r="AD71" t="inlineStr"/>
+      <c r="AE71" t="inlineStr"/>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="inlineStr"/>
+      <c r="AH71" t="inlineStr"/>
+      <c r="AI71" t="inlineStr"/>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+        </is>
+      </c>
+      <c r="O72" t="n">
+        <v>250</v>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Ltr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>100</v>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>08 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>08 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T72" t="n">
+        <v>25000</v>
+      </c>
+      <c r="U72" t="n">
+        <v>6250000</v>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 70 Ton</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr"/>
+      <c r="AD72" t="inlineStr"/>
+      <c r="AE72" t="inlineStr"/>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="inlineStr"/>
+      <c r="AH72" t="inlineStr"/>
+      <c r="AI72" t="inlineStr"/>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+        </is>
+      </c>
+      <c r="O73" t="n">
+        <v>200</v>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Ltr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>100</v>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>23 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>23 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T73" t="n">
+        <v>25000</v>
+      </c>
+      <c r="U73" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 100 Ton</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr"/>
+      <c r="AD73" t="inlineStr"/>
+      <c r="AE73" t="inlineStr"/>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="inlineStr"/>
+      <c r="AH73" t="inlineStr"/>
+      <c r="AI73" t="inlineStr"/>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+        </is>
+      </c>
+      <c r="O74" t="n">
+        <v>50</v>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Ltr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>100</v>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>08 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>08 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T74" t="n">
+        <v>25000</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1250000</v>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr"/>
+      <c r="AD74" t="inlineStr"/>
+      <c r="AE74" t="inlineStr"/>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="inlineStr"/>
+      <c r="AH74" t="inlineStr"/>
+      <c r="AI74" t="inlineStr"/>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+        </is>
+      </c>
+      <c r="O75" t="n">
+        <v>50</v>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Ltr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>100</v>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>08 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>08 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T75" t="n">
+        <v>25000</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1250000</v>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr"/>
+      <c r="AD75" t="inlineStr"/>
+      <c r="AE75" t="inlineStr"/>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="inlineStr"/>
+      <c r="AH75" t="inlineStr"/>
+      <c r="AI75" t="inlineStr"/>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+        </is>
+      </c>
+      <c r="O76" t="n">
+        <v>50</v>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>100</v>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>08 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>08 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T76" t="n">
+        <v>25000</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1250000</v>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 05</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr"/>
+      <c r="AD76" t="inlineStr"/>
+      <c r="AE76" t="inlineStr"/>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="inlineStr"/>
+      <c r="AH76" t="inlineStr"/>
+      <c r="AI76" t="inlineStr"/>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+        </is>
+      </c>
+      <c r="O77" t="n">
+        <v>50</v>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Ltr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>100</v>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>08 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>08 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T77" t="n">
+        <v>25000</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1250000</v>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 06</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr"/>
+      <c r="AD77" t="inlineStr"/>
+      <c r="AE77" t="inlineStr"/>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="inlineStr"/>
+      <c r="AH77" t="inlineStr"/>
+      <c r="AI77" t="inlineStr"/>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+        </is>
+      </c>
+      <c r="O78" t="n">
+        <v>115</v>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Ltr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>100</v>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>08 Aug 2026</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>23 Aug 2026</t>
+        </is>
+      </c>
+      <c r="T78" t="n">
+        <v>25000</v>
+      </c>
+      <c r="U78" t="n">
+        <v>2875000</v>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Vacuum Truck 5000 L</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr"/>
+      <c r="AD78" t="inlineStr"/>
+      <c r="AE78" t="inlineStr"/>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="inlineStr"/>
+      <c r="AH78" t="inlineStr"/>
+      <c r="AI78" t="inlineStr"/>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>004/BSS-JOB/WS/IV/2026</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>28 Apr 2026</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>4500011236</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Pengiriman OCTG (Casing 9 5/8" dan Tubing 4 1/2") Celegon-Senoro</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>18 Feb 2026</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Add Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="O79" t="n">
+        <v>1</v>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>100</v>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>28 Apr 2026</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>28 Apr 2026</t>
+        </is>
+      </c>
+      <c r="T79" t="n">
+        <v>773919900</v>
+      </c>
+      <c r="U79" t="n">
+        <v>890007884.9999999</v>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>Pengiriman OCTG (Casing 9 5/8" dan Tubing 4 1/2") Celegon-Senoro</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr"/>
+      <c r="AD79" t="inlineStr"/>
+      <c r="AE79" t="inlineStr"/>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="inlineStr"/>
+      <c r="AH79" t="inlineStr"/>
+      <c r="AI79" t="inlineStr"/>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>1000025165</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>003/BSS-JOB/WS/II/2026</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>4500011203</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Kayu Kaso/lata, 5x5x400 Kayu kelas 2</t>
+        </is>
+      </c>
+      <c r="O80" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>100</v>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="T80" t="n">
+        <v>3125000</v>
+      </c>
+      <c r="U80" t="n">
+        <v>1637500</v>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>Kayu Kaso/lata, 5x5x400 Kayu kelas 2  Material pembuatan grouting annulus SNR-19.</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr"/>
+      <c r="AD80" t="inlineStr"/>
+      <c r="AE80" t="inlineStr"/>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="inlineStr"/>
+      <c r="AH80" t="inlineStr"/>
+      <c r="AI80" t="inlineStr"/>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>1000025162</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>003/BSS-JOB/WS/II/2026</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>4500011203</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Paku Zeng</t>
+        </is>
+      </c>
+      <c r="O81" t="n">
+        <v>4</v>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>100</v>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="T81" t="n">
+        <v>50000</v>
+      </c>
+      <c r="U81" t="n">
+        <v>200000</v>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>Paku 10 cm pembuatan grouting annulus SNR-19.</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr"/>
+      <c r="AD81" t="inlineStr"/>
+      <c r="AE81" t="inlineStr"/>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="inlineStr"/>
+      <c r="AH81" t="inlineStr"/>
+      <c r="AI81" t="inlineStr"/>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>1000025162</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>003/BSS-JOB/WS/II/2026</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>4500011203</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Paku Zeng</t>
+        </is>
+      </c>
+      <c r="O82" t="n">
+        <v>2</v>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>100</v>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="T82" t="n">
+        <v>50000</v>
+      </c>
+      <c r="U82" t="n">
+        <v>100000</v>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>Paku 7 cm  pembuatan grouting annulus SNR-19.</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr"/>
+      <c r="AD82" t="inlineStr"/>
+      <c r="AE82" t="inlineStr"/>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="inlineStr"/>
+      <c r="AH82" t="inlineStr"/>
+      <c r="AI82" t="inlineStr"/>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>1000025162</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>003/BSS-JOB/WS/II/2026</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>4500011203</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Paku Zeng</t>
+        </is>
+      </c>
+      <c r="O83" t="n">
+        <v>2</v>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>100</v>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="T83" t="n">
+        <v>50000</v>
+      </c>
+      <c r="U83" t="n">
+        <v>100000</v>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>Paku 5 cm pembuatan grouting annulus SNR-19.</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr"/>
+      <c r="AD83" t="inlineStr"/>
+      <c r="AE83" t="inlineStr"/>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="inlineStr"/>
+      <c r="AH83" t="inlineStr"/>
+      <c r="AI83" t="inlineStr"/>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>1000025162</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>003/BSS-JOB/WS/II/2026</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>4500011203</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Pipa PVC AW 1/2" (4m)</t>
+        </is>
+      </c>
+      <c r="O84" t="n">
+        <v>1</v>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>100</v>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="T84" t="n">
+        <v>55500</v>
+      </c>
+      <c r="U84" t="n">
+        <v>55500</v>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>Pipa PVC AW 1/2" (4m)</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr"/>
+      <c r="AD84" t="inlineStr"/>
+      <c r="AE84" t="inlineStr"/>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="inlineStr"/>
+      <c r="AH84" t="inlineStr"/>
+      <c r="AI84" t="inlineStr"/>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>1000025162</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>003/BSS-JOB/WS/II/2026</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>4500011203</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>Lem pipa PVC</t>
+        </is>
+      </c>
+      <c r="O85" t="n">
+        <v>1</v>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>100</v>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>10 Sep 2026</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>10 Sep 2026</t>
+        </is>
+      </c>
+      <c r="T85" t="n">
+        <v>75000</v>
+      </c>
+      <c r="U85" t="n">
+        <v>75000</v>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>Lem pipa PVC</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr"/>
+      <c r="AD85" t="inlineStr"/>
+      <c r="AE85" t="inlineStr"/>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="inlineStr"/>
+      <c r="AH85" t="inlineStr"/>
+      <c r="AI85" t="inlineStr"/>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>1000025162</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>003/BSS-JOB/WS/II/2026</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>4500011203</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Pasir</t>
+        </is>
+      </c>
+      <c r="O86" t="n">
+        <v>1</v>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>100</v>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="T86" t="n">
+        <v>293750</v>
+      </c>
+      <c r="U86" t="n">
+        <v>293750</v>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>Pasir</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr"/>
+      <c r="AD86" t="inlineStr"/>
+      <c r="AE86" t="inlineStr"/>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="inlineStr"/>
+      <c r="AH86" t="inlineStr"/>
+      <c r="AI86" t="inlineStr"/>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>1000025162</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>003/BSS-JOB/WS/II/2026</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>4500011203</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>Batu Agregate A</t>
+        </is>
+      </c>
+      <c r="O87" t="n">
+        <v>1</v>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>100</v>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="T87" t="n">
+        <v>400000</v>
+      </c>
+      <c r="U87" t="n">
+        <v>400000</v>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>Batu Pecah 1-2</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr"/>
+      <c r="AD87" t="inlineStr"/>
+      <c r="AE87" t="inlineStr"/>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="inlineStr"/>
+      <c r="AH87" t="inlineStr"/>
+      <c r="AI87" t="inlineStr"/>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>1000025162</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>003/BSS-JOB/WS/II/2026</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>4500011203</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Semen PC 50 kg</t>
+        </is>
+      </c>
+      <c r="O88" t="n">
+        <v>12</v>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>100</v>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="T88" t="n">
+        <v>120000</v>
+      </c>
+      <c r="U88" t="n">
+        <v>1440000</v>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>Semen PC 50 kg</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr"/>
+      <c r="AD88" t="inlineStr"/>
+      <c r="AE88" t="inlineStr"/>
+      <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="inlineStr"/>
+      <c r="AH88" t="inlineStr"/>
+      <c r="AI88" t="inlineStr"/>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>1000025162</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>003/BSS-JOB/WS/II/2026</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>4500011203</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>Skop</t>
+        </is>
+      </c>
+      <c r="O89" t="n">
+        <v>2</v>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>100</v>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="T89" t="n">
+        <v>93750</v>
+      </c>
+      <c r="U89" t="n">
+        <v>187500</v>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>Skop</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr"/>
+      <c r="AD89" t="inlineStr"/>
+      <c r="AE89" t="inlineStr"/>
+      <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="inlineStr"/>
+      <c r="AH89" t="inlineStr"/>
+      <c r="AI89" t="inlineStr"/>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>1000025162</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>003/BSS-JOB/WS/II/2026</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>4500011203</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>Sendok adukan</t>
+        </is>
+      </c>
+      <c r="O90" t="n">
+        <v>2</v>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>100</v>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="T90" t="n">
+        <v>37500</v>
+      </c>
+      <c r="U90" t="n">
+        <v>75000</v>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>Sendok adukan</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr"/>
+      <c r="AD90" t="inlineStr"/>
+      <c r="AE90" t="inlineStr"/>
+      <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="inlineStr"/>
+      <c r="AH90" t="inlineStr"/>
+      <c r="AI90" t="inlineStr"/>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>1000025162</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>003/BSS-JOB/WS/II/2026</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>4500011203</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>Meteran @5m</t>
+        </is>
+      </c>
+      <c r="O91" t="n">
+        <v>1</v>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>100</v>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="T91" t="n">
+        <v>37500</v>
+      </c>
+      <c r="U91" t="n">
+        <v>37500</v>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>Meteran @5m</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr"/>
+      <c r="AD91" t="inlineStr"/>
+      <c r="AE91" t="inlineStr"/>
+      <c r="AF91" t="inlineStr"/>
+      <c r="AG91" t="inlineStr"/>
+      <c r="AH91" t="inlineStr"/>
+      <c r="AI91" t="inlineStr"/>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>1000025162</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>003/BSS-JOB/WS/II/2026</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>4500011203</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>Terpaulin A12</t>
+        </is>
+      </c>
+      <c r="O92" t="n">
+        <v>48</v>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>100</v>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="T92" t="n">
+        <v>31250</v>
+      </c>
+      <c r="U92" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>Terpaulin A12</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr"/>
+      <c r="AD92" t="inlineStr"/>
+      <c r="AE92" t="inlineStr"/>
+      <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="inlineStr"/>
+      <c r="AH92" t="inlineStr"/>
+      <c r="AI92" t="inlineStr"/>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>1000025162</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>003/BSS-JOB/WS/II/2026</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>4500011203</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>Terpaulin A12</t>
+        </is>
+      </c>
+      <c r="O93" t="n">
+        <v>20</v>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>100</v>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="T93" t="n">
+        <v>31250</v>
+      </c>
+      <c r="U93" t="n">
+        <v>625000</v>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>Terpaulin A12</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr"/>
+      <c r="AD93" t="inlineStr"/>
+      <c r="AE93" t="inlineStr"/>
+      <c r="AF93" t="inlineStr"/>
+      <c r="AG93" t="inlineStr"/>
+      <c r="AH93" t="inlineStr"/>
+      <c r="AI93" t="inlineStr"/>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>1000025162</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>003/BSS-JOB/WS/II/2026</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>4500011203</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>Kabel 2x1.5mm NYA/NYM @50m</t>
+        </is>
+      </c>
+      <c r="O94" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>100</v>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="T94" t="n">
+        <v>712500</v>
+      </c>
+      <c r="U94" t="n">
+        <v>142500</v>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>Kabel 2x1.5mm NYA/NYM @50m</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr"/>
+      <c r="AD94" t="inlineStr"/>
+      <c r="AE94" t="inlineStr"/>
+      <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="inlineStr"/>
+      <c r="AH94" t="inlineStr"/>
+      <c r="AI94" t="inlineStr"/>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>1000025162</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>003/BSS-JOB/WS/II/2026</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>4500011203</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>Paku Zeng</t>
+        </is>
+      </c>
+      <c r="O95" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>100</v>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="T95" t="n">
+        <v>50000</v>
+      </c>
+      <c r="U95" t="n">
+        <v>25000</v>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>Paku 12 cm</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr"/>
+      <c r="AD95" t="inlineStr"/>
+      <c r="AE95" t="inlineStr"/>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="inlineStr"/>
+      <c r="AH95" t="inlineStr"/>
+      <c r="AI95" t="inlineStr"/>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>1000025162</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>003/BSS-JOB/WS/II/2026</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>4500011203</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>Paku Zeng</t>
+        </is>
+      </c>
+      <c r="O96" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>100</v>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>10 Sep 2026</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>10 Sep 2026</t>
+        </is>
+      </c>
+      <c r="T96" t="n">
+        <v>50000</v>
+      </c>
+      <c r="U96" t="n">
+        <v>25000</v>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>Paku Beton 10 cm</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr"/>
+      <c r="AD96" t="inlineStr"/>
+      <c r="AE96" t="inlineStr"/>
+      <c r="AF96" t="inlineStr"/>
+      <c r="AG96" t="inlineStr"/>
+      <c r="AH96" t="inlineStr"/>
+      <c r="AI96" t="inlineStr"/>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>1000025162</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>006/BSS-JOB/WS/VI/2026</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>06 Jun 2026</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>4500011579</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Pengadaan Ban Spare part Genset Field Maintenance</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>04 Jun 2026</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>Add Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="O97" t="n">
+        <v>1</v>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>100</v>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>06 Jun 2026</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>06 Jun 2026</t>
+        </is>
+      </c>
+      <c r="T97" t="n">
+        <v>575000</v>
+      </c>
+      <c r="U97" t="n">
+        <v>661250</v>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>Pengadaan Ban Spare part Genset Field Maintenance</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr"/>
+      <c r="AD97" t="inlineStr"/>
+      <c r="AE97" t="inlineStr"/>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="inlineStr"/>
+      <c r="AH97" t="inlineStr"/>
+      <c r="AI97" t="inlineStr"/>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>1000025742</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>007/BSS-JOB/WS/VI/2026</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>06 Jun 2026</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>4500011580</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Transport Pengangkutan Material   Spare part Genset Field Maintenance</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>04 Jun 2026</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="O98" t="n">
+        <v>1</v>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>100</v>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>06 Jun 2026</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>06 Jun 2026</t>
+        </is>
+      </c>
+      <c r="T98" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="U98" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>Transport Pengangkutan Material   Spare part Genset Field Maintenance</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:18</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr"/>
+      <c r="AD98" t="inlineStr"/>
+      <c r="AE98" t="inlineStr"/>
+      <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="inlineStr"/>
+      <c r="AH98" t="inlineStr"/>
+      <c r="AI98" t="inlineStr"/>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>1000025743</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database_penyimpanan_aman/database_transaksi_rincian.xlsx
+++ b/database_penyimpanan_aman/database_transaksi_rincian.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK98"/>
+  <dimension ref="A1:AL114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -602,6 +602,11 @@
           <t>Nomor WAN / SA</t>
         </is>
       </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>Nomor WO</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -733,7 +738,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -749,6 +754,7 @@
         </is>
       </c>
       <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -880,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -896,6 +902,7 @@
         </is>
       </c>
       <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1027,7 +1034,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -1043,6 +1050,7 @@
         </is>
       </c>
       <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1174,7 +1182,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -1190,6 +1198,7 @@
         </is>
       </c>
       <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1321,7 +1330,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -1337,6 +1346,7 @@
         </is>
       </c>
       <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1468,7 +1478,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
@@ -1484,6 +1494,7 @@
         </is>
       </c>
       <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1615,7 +1626,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
@@ -1631,6 +1642,7 @@
         </is>
       </c>
       <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1762,7 +1774,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -1778,6 +1790,7 @@
         </is>
       </c>
       <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1909,7 +1922,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
@@ -1925,6 +1938,7 @@
         </is>
       </c>
       <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2056,7 +2070,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
@@ -2072,6 +2086,7 @@
         </is>
       </c>
       <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2203,7 +2218,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
@@ -2219,6 +2234,7 @@
         </is>
       </c>
       <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2350,7 +2366,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
@@ -2366,6 +2382,7 @@
         </is>
       </c>
       <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2497,7 +2514,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr"/>
@@ -2513,6 +2530,7 @@
         </is>
       </c>
       <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2644,7 +2662,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr"/>
@@ -2660,6 +2678,7 @@
         </is>
       </c>
       <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2791,7 +2810,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
@@ -2807,6 +2826,7 @@
         </is>
       </c>
       <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2938,7 +2958,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
@@ -2954,6 +2974,7 @@
         </is>
       </c>
       <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3085,7 +3106,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
@@ -3101,6 +3122,7 @@
         </is>
       </c>
       <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3232,7 +3254,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
@@ -3248,6 +3270,7 @@
         </is>
       </c>
       <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3379,7 +3402,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
@@ -3395,6 +3418,7 @@
         </is>
       </c>
       <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3526,7 +3550,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
@@ -3542,6 +3566,7 @@
         </is>
       </c>
       <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3673,7 +3698,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
@@ -3689,6 +3714,7 @@
         </is>
       </c>
       <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3820,7 +3846,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
@@ -3836,6 +3862,7 @@
         </is>
       </c>
       <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3967,7 +3994,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr"/>
@@ -3983,6 +4010,7 @@
         </is>
       </c>
       <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4114,7 +4142,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr"/>
@@ -4134,6 +4162,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4265,7 +4294,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr"/>
@@ -4285,6 +4314,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4416,7 +4446,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr"/>
@@ -4436,6 +4466,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4567,7 +4598,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr"/>
@@ -4587,6 +4618,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4718,7 +4750,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr"/>
@@ -4738,6 +4770,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4869,7 +4902,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr"/>
@@ -4889,6 +4922,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5020,7 +5054,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr"/>
@@ -5040,31 +5074,32 @@
           <t>1000025786</t>
         </is>
       </c>
+      <c r="AL31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>7207250142</t>
+          <t>7201250141</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>S250551FLD-R1</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>043/BSS-JOB/AB/VII/2026</t>
+          <t>017/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>25 Aug 2026</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -5079,22 +5114,22 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>24 Month</t>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>4500011425</t>
+          <t>4500011682</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift Untuk support Kegiatan Operation &amp; Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026, Refer CTR No. 7207250142-BSS-CTR-2026-020" (01 - 31 Juli 2026)</t>
+          <t>Penyediaan electric cable pendukung wellservice camp</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1 Jul 2026</t>
+          <t>24 Aug 2026</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -5109,7 +5144,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
+          <t>Add Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O32" t="n">
@@ -5125,19 +5160,19 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>16 Aug 2026</t>
+          <t>25 Aug 2026</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>16 Aug 2026</t>
+          <t>25 Aug 2026</t>
         </is>
       </c>
       <c r="T32" t="n">
-        <v>62818000</v>
+        <v>1160000</v>
       </c>
       <c r="U32" t="n">
-        <v>72240700</v>
+        <v>1334000</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -5166,12 +5201,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
+          <t>Penyediaan electric cable pendukung wellservice camp Ukuran 3x25 mm NYM</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr"/>
@@ -5183,7 +5218,7 @@
       <c r="AI32" t="inlineStr"/>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -5191,6 +5226,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5210,7 +5246,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>017/BSS-JOB/WS/VIII/2026</t>
+          <t>018/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -5235,12 +5271,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>4500011682</t>
+          <t>4500011683</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Penyediaan electric cable pendukung wellservice camp</t>
+          <t>Transport pengangkut electric cable pendukung wellservice camp</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -5255,12 +5291,12 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Add Cost + Fee 15%</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O33" t="n">
@@ -5268,7 +5304,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q33" t="n">
@@ -5285,10 +5321,10 @@
         </is>
       </c>
       <c r="T33" t="n">
-        <v>1160000</v>
+        <v>1600000</v>
       </c>
       <c r="U33" t="n">
-        <v>1334000</v>
+        <v>1600000</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -5317,12 +5353,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>Penyediaan electric cable pendukung wellservice camp Ukuran 3x25 mm NYM</t>
+          <t>Transport pengangkut electric cable pendukung wellservice camp</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr"/>
@@ -5334,7 +5370,7 @@
       <c r="AI33" t="inlineStr"/>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -5342,6 +5378,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5361,12 +5398,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>018/BSS-JOB/WS/VIII/2026</t>
+          <t>019/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>25 Aug 2026</t>
+          <t>26 Aug 2026</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -5386,12 +5423,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>4500011683</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Transport pengangkut electric cable pendukung wellservice camp</t>
+          <t>Pengiriman 4 ea Set Valve dari Senoro 2 ke SPM Batam</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -5406,16 +5443,16 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Batam - Luwuk/ Senoro atau sebaliknya</t>
         </is>
       </c>
       <c r="O34" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
@@ -5427,19 +5464,19 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>25 Aug 2026</t>
+          <t>24 Aug 2026</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>25 Aug 2026</t>
+          <t>26 Aug 2026</t>
         </is>
       </c>
       <c r="T34" t="n">
-        <v>1600000</v>
+        <v>150000</v>
       </c>
       <c r="U34" t="n">
-        <v>1600000</v>
+        <v>2250000</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -5468,12 +5505,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>Transport pengangkut electric cable pendukung wellservice camp</t>
+          <t>Cargo Manifest Barang Seat Valve No GS08/01 Tgl 24 Agustus 2026</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr"/>
@@ -5493,6 +5530,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5562,15 +5600,15 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Batam - Luwuk/ Senoro atau sebaliknya</t>
+          <t>Balikpapan - Batam atau sebaliknya</t>
         </is>
       </c>
       <c r="O35" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Pallet</t>
         </is>
       </c>
       <c r="Q35" t="n">
@@ -5583,14 +5621,14 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>26 Aug 2026</t>
+          <t>24 Aug 2026</t>
         </is>
       </c>
       <c r="T35" t="n">
-        <v>150000</v>
+        <v>200000</v>
       </c>
       <c r="U35" t="n">
-        <v>2250000</v>
+        <v>200000</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -5619,12 +5657,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>Cargo Manifest Barang Seat Valve No GS08/01 Tgl 24 Agustus 2026</t>
+          <t>Pembuatan Wooden Pallet Box</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr"/>
@@ -5644,6 +5682,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5708,12 +5747,12 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>MOVING AIR FREIGHT TRANSPORT</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Balikpapan - Batam atau sebaliknya</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O36" t="n">
@@ -5721,7 +5760,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Pallet</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q36" t="n">
@@ -5738,10 +5777,10 @@
         </is>
       </c>
       <c r="T36" t="n">
-        <v>200000</v>
+        <v>1600000</v>
       </c>
       <c r="U36" t="n">
-        <v>200000</v>
+        <v>1600000</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -5770,12 +5809,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>Pembuatan Wooden Pallet Box</t>
+          <t>Kendaraan Untuk Pengiriman dari Luwuk ke Bandara Luwuk</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr"/>
@@ -5795,6 +5834,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5814,12 +5854,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>019/BSS-JOB/WS/VIII/2026</t>
+          <t>020/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>26 Aug 2026</t>
+          <t>04 Sep 2026</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -5839,17 +5879,17 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Pengiriman 4 ea Set Valve dari Senoro 2 ke SPM Batam</t>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 04/09/2026</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>24 Aug 2026</t>
+          <t>03 Sep 2026</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -5859,12 +5899,12 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Add Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O37" t="n">
@@ -5872,7 +5912,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q37" t="n">
@@ -5880,19 +5920,19 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>24 Aug 2026</t>
+          <t>04 Sep 2026</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>24 Aug 2026</t>
+          <t>04 Sep 2026</t>
         </is>
       </c>
       <c r="T37" t="n">
-        <v>1600000</v>
+        <v>5054500</v>
       </c>
       <c r="U37" t="n">
-        <v>1600000</v>
+        <v>5812675</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -5921,12 +5961,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>Kendaraan Untuk Pengiriman dari Luwuk ke Bandara Luwuk</t>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 04/09/2026</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr"/>
@@ -5938,7 +5978,7 @@
       <c r="AI37" t="inlineStr"/>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -5946,6 +5986,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5965,7 +6006,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>020/BSS-JOB/WS/IX/2026</t>
+          <t>021/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -5995,7 +6036,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 04/09/2026</t>
+          <t>(Provsum)  Penyediaan kontainer box untuk penyimpanan APD dan Dokumen</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -6019,11 +6060,11 @@
         </is>
       </c>
       <c r="O38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q38" t="n">
@@ -6040,10 +6081,10 @@
         </is>
       </c>
       <c r="T38" t="n">
-        <v>5054500</v>
+        <v>175000</v>
       </c>
       <c r="U38" t="n">
-        <v>5812675</v>
+        <v>517499.9999999999</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
@@ -6072,12 +6113,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 04/09/2026</t>
+          <t>Kontainer box ukuran 95 untuk Penyimpanan APD dan Dokument</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr"/>
@@ -6097,6 +6138,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6170,7 +6212,7 @@
         </is>
       </c>
       <c r="O39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
@@ -6191,10 +6233,10 @@
         </is>
       </c>
       <c r="T39" t="n">
-        <v>175000</v>
+        <v>100000</v>
       </c>
       <c r="U39" t="n">
-        <v>517499.9999999999</v>
+        <v>0</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
@@ -6223,12 +6265,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>Kontainer box ukuran 95 untuk Penyimpanan APD dan Dokument</t>
+          <t>Kontainer box ukuran 52 untuk Penyimpanan APD dan Dokument</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr"/>
@@ -6248,6 +6290,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6267,7 +6310,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>021/BSS-JOB/WS/IX/2026</t>
+          <t>022/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -6297,7 +6340,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>(Provsum)  Penyediaan kontainer box untuk penyimpanan APD dan Dokumen</t>
+          <t>Civil Enginner melakukan Survey untuk pengukuran dudukan X-Mas Tree di Sumur Senoro 16</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -6312,12 +6355,12 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Add Cost + Fee 15%</t>
+          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
         </is>
       </c>
       <c r="O40" t="n">
@@ -6325,7 +6368,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q40" t="n">
@@ -6342,10 +6385,10 @@
         </is>
       </c>
       <c r="T40" t="n">
-        <v>100000</v>
+        <v>750000</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>750000</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -6374,12 +6417,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>Kontainer box ukuran 52 untuk Penyimpanan APD dan Dokument</t>
+          <t>Tenaga Civil Engineer melakukan survey di Lokasi Sumur Senoro 16</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr"/>
@@ -6391,7 +6434,7 @@
       <c r="AI40" t="inlineStr"/>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -6399,6 +6442,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6463,12 +6507,12 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O41" t="n">
@@ -6493,10 +6537,10 @@
         </is>
       </c>
       <c r="T41" t="n">
-        <v>750000</v>
+        <v>1600000</v>
       </c>
       <c r="U41" t="n">
-        <v>750000</v>
+        <v>1600000</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -6525,12 +6569,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>Tenaga Civil Engineer melakukan survey di Lokasi Sumur Senoro 16</t>
+          <t>Kendaraan Operasional Double Cabin DN 8890 RG untuk transportasi Survey ke Lokasi</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr"/>
@@ -6550,6 +6594,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6569,12 +6614,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>022/BSS-JOB/WS/IX/2026</t>
+          <t>023/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>04 Sep 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -6599,12 +6644,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Civil Enginner melakukan Survey untuk pengukuran dudukan X-Mas Tree di Sumur Senoro 16</t>
+          <t>Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>03 Sep 2026</t>
+          <t>07 Aug 2026</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -6614,20 +6659,20 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
         </is>
       </c>
       <c r="O42" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="Q42" t="n">
@@ -6635,19 +6680,19 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>04 Sep 2026</t>
+          <t>08 Aug 2026</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>04 Sep 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="T42" t="n">
-        <v>1600000</v>
+        <v>750000</v>
       </c>
       <c r="U42" t="n">
-        <v>1600000</v>
+        <v>16500000</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -6676,12 +6721,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>Kendaraan Operasional Double Cabin DN 8890 RG untuk transportasi Survey ke Lokasi</t>
+          <t>Personel GS - Koordinator Lapangan atas Nama Nur Afiata</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr"/>
@@ -6701,6 +6746,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6774,7 +6820,7 @@
         </is>
       </c>
       <c r="O43" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
@@ -6798,7 +6844,7 @@
         <v>750000</v>
       </c>
       <c r="U43" t="n">
-        <v>16500000</v>
+        <v>18000000</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -6827,12 +6873,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>Personel GS - Koordinator Lapangan atas Nama Nur Afiata</t>
+          <t>Personel GS -HSE Officer  Lapangan atas I Gusti Ngurah Dwipayana</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr"/>
@@ -6852,6 +6898,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6921,7 +6968,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
+          <t>Welder (GTAW)</t>
         </is>
       </c>
       <c r="O44" t="n">
@@ -6946,10 +6993,10 @@
         </is>
       </c>
       <c r="T44" t="n">
-        <v>750000</v>
+        <v>500000</v>
       </c>
       <c r="U44" t="n">
-        <v>18000000</v>
+        <v>12000000</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
@@ -6978,12 +7025,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>Personel GS -HSE Officer  Lapangan atas I Gusti Ngurah Dwipayana</t>
+          <t>Welder = Tenaga Paramedic atas Nama Meilita Bella di Lokasi Senoro</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr"/>
@@ -7003,6 +7050,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -7129,12 +7177,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>Welder = Tenaga Paramedic atas Nama Meilita Bella di Lokasi Senoro</t>
+          <t>Welder = Tenaga Paramedic atas Nama Widiya Satuwo di Lokasi Senoro</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr"/>
@@ -7154,6 +7202,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -7173,7 +7222,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>023/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -7223,11 +7272,11 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Welder (GTAW)</t>
+          <t>Operator Crane</t>
         </is>
       </c>
       <c r="O46" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
@@ -7244,14 +7293,14 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>31 Aug 2026</t>
+          <t>20 Aug 2026</t>
         </is>
       </c>
       <c r="T46" t="n">
-        <v>500000</v>
+        <v>750000</v>
       </c>
       <c r="U46" t="n">
-        <v>12000000</v>
+        <v>9750000</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
@@ -7280,12 +7329,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>Welder = Tenaga Paramedic atas Nama Widiya Satuwo di Lokasi Senoro</t>
+          <t>Operator Crane Shift Siang atas nama Rasid A Laugi</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr"/>
@@ -7305,6 +7354,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -7378,7 +7428,7 @@
         </is>
       </c>
       <c r="O47" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
@@ -7390,19 +7440,19 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>08 Aug 2026</t>
+          <t>23 Aug 2026</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>20 Aug 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="T47" t="n">
         <v>750000</v>
       </c>
       <c r="U47" t="n">
-        <v>9750000</v>
+        <v>6750000</v>
       </c>
       <c r="V47" t="inlineStr">
         <is>
@@ -7431,12 +7481,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>Operator Crane Shift Siang atas nama Rasid A Laugi</t>
+          <t>Operator Crane Shift Siang atas nama Wanhar</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr"/>
@@ -7456,6 +7506,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -7529,7 +7580,7 @@
         </is>
       </c>
       <c r="O48" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
@@ -7541,7 +7592,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>23 Aug 2026</t>
+          <t>08 Aug 2026</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -7553,7 +7604,7 @@
         <v>750000</v>
       </c>
       <c r="U48" t="n">
-        <v>6750000</v>
+        <v>12750000</v>
       </c>
       <c r="V48" t="inlineStr">
         <is>
@@ -7582,12 +7633,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>Operator Crane Shift Siang atas nama Wanhar</t>
+          <t>Operator Crane Shift Malam  atas nama Ilsan Adjedar</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr"/>
@@ -7607,6 +7658,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -7676,11 +7728,11 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Operator Crane</t>
+          <t>Rigger</t>
         </is>
       </c>
       <c r="O49" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
@@ -7701,10 +7753,10 @@
         </is>
       </c>
       <c r="T49" t="n">
-        <v>750000</v>
+        <v>650000</v>
       </c>
       <c r="U49" t="n">
-        <v>12750000</v>
+        <v>14300000</v>
       </c>
       <c r="V49" t="inlineStr">
         <is>
@@ -7733,12 +7785,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>Operator Crane Shift Malam  atas nama Ilsan Adjedar</t>
+          <t>Rigger  Crane Shift Siang  atas nama Tison</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr"/>
@@ -7758,6 +7810,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -7831,7 +7884,7 @@
         </is>
       </c>
       <c r="O50" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
@@ -7855,7 +7908,7 @@
         <v>650000</v>
       </c>
       <c r="U50" t="n">
-        <v>14300000</v>
+        <v>13650000</v>
       </c>
       <c r="V50" t="inlineStr">
         <is>
@@ -7884,12 +7937,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>Rigger  Crane Shift Siang  atas nama Tison</t>
+          <t>Rigger  Crane Shift Malam  atas nama Agus Dg Mangata</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr"/>
@@ -7909,6 +7962,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -7978,7 +8032,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Rigger</t>
+          <t>Operator Heavy Equipment (Vacuum Truck)</t>
         </is>
       </c>
       <c r="O51" t="n">
@@ -7994,7 +8048,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>08 Aug 2026</t>
+          <t>09 Aug 2026</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -8003,10 +8057,10 @@
         </is>
       </c>
       <c r="T51" t="n">
-        <v>650000</v>
+        <v>500000</v>
       </c>
       <c r="U51" t="n">
-        <v>13650000</v>
+        <v>10500000</v>
       </c>
       <c r="V51" t="inlineStr">
         <is>
@@ -8035,12 +8089,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>Rigger  Crane Shift Malam  atas nama Agus Dg Mangata</t>
+          <t>Operator Heavy Equipment (Vacuum Truck) atas nama Wijayanto Sucipto</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr"/>
@@ -8060,6 +8114,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -8129,11 +8184,11 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Operator Heavy Equipment (Vacuum Truck)</t>
+          <t>Mechanic/ Electrician</t>
         </is>
       </c>
       <c r="O52" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
@@ -8154,10 +8209,10 @@
         </is>
       </c>
       <c r="T52" t="n">
-        <v>500000</v>
+        <v>600000</v>
       </c>
       <c r="U52" t="n">
-        <v>10500000</v>
+        <v>13800000</v>
       </c>
       <c r="V52" t="inlineStr">
         <is>
@@ -8186,12 +8241,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>Operator Heavy Equipment (Vacuum Truck) atas nama Wijayanto Sucipto</t>
+          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Sugeng</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr"/>
@@ -8211,6 +8266,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -8337,12 +8393,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Sugeng</t>
+          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Ahmad Dhani</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr"/>
@@ -8362,6 +8418,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -8381,7 +8438,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -8411,7 +8468,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026</t>
+          <t>Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -8426,20 +8483,20 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
         </is>
       </c>
       <c r="O54" t="n">
-        <v>23</v>
+        <v>0.48</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q54" t="n">
@@ -8456,10 +8513,10 @@
         </is>
       </c>
       <c r="T54" t="n">
-        <v>600000</v>
+        <v>25000000</v>
       </c>
       <c r="U54" t="n">
-        <v>13800000</v>
+        <v>12000000</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
@@ -8488,12 +8545,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Ahmad Dhani</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr"/>
@@ -8513,6 +8570,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -8582,7 +8640,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
+          <t>Portacamp - Living camp,ukuran 40FT (8 sleepers)</t>
         </is>
       </c>
       <c r="O55" t="n">
@@ -8607,10 +8665,10 @@
         </is>
       </c>
       <c r="T55" t="n">
-        <v>25000000</v>
+        <v>20000000</v>
       </c>
       <c r="U55" t="n">
-        <v>12000000</v>
+        <v>9600000</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
@@ -8639,12 +8697,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Portacamp - Living camp,ukuran 40FT (8 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr"/>
@@ -8664,6 +8722,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -8728,16 +8787,16 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (8 sleepers)</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="O56" t="n">
-        <v>0.48</v>
+        <v>0.74</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
@@ -8758,10 +8817,10 @@
         </is>
       </c>
       <c r="T56" t="n">
-        <v>20000000</v>
+        <v>60000000</v>
       </c>
       <c r="U56" t="n">
-        <v>9600000</v>
+        <v>44400000</v>
       </c>
       <c r="V56" t="inlineStr">
         <is>
@@ -8790,12 +8849,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (8 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr"/>
@@ -8815,6 +8874,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -8941,12 +9001,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr"/>
@@ -8966,6 +9026,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -9035,7 +9096,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="O58" t="n">
@@ -9060,10 +9121,10 @@
         </is>
       </c>
       <c r="T58" t="n">
-        <v>60000000</v>
+        <v>15000000</v>
       </c>
       <c r="U58" t="n">
-        <v>44400000</v>
+        <v>11100000</v>
       </c>
       <c r="V58" t="inlineStr">
         <is>
@@ -9092,12 +9153,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr"/>
@@ -9117,6 +9178,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -9248,7 +9310,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr"/>
@@ -9268,6 +9330,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -9287,7 +9350,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -9317,12 +9380,12 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Penyediaan Car &amp; Tansportation Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>07 Aug 2026</t>
+          <t>06 Aug 2026</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -9332,20 +9395,20 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O60" t="n">
-        <v>0.74</v>
+        <v>25</v>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q60" t="n">
@@ -9353,7 +9416,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>09 Aug 2026</t>
+          <t>07 Aug 2026</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -9362,10 +9425,10 @@
         </is>
       </c>
       <c r="T60" t="n">
-        <v>15000000</v>
+        <v>1600000</v>
       </c>
       <c r="U60" t="n">
-        <v>11100000</v>
+        <v>40000000</v>
       </c>
       <c r="V60" t="inlineStr">
         <is>
@@ -9394,12 +9457,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
+          <t>Kendaraan Innova DN 1259 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr"/>
@@ -9419,6 +9482,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -9492,7 +9556,7 @@
         </is>
       </c>
       <c r="O61" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="P61" t="inlineStr">
         <is>
@@ -9509,14 +9573,14 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>31 Aug 2026</t>
+          <t>21 Aug 2026</t>
         </is>
       </c>
       <c r="T61" t="n">
         <v>1600000</v>
       </c>
       <c r="U61" t="n">
-        <v>40000000</v>
+        <v>24000000</v>
       </c>
       <c r="V61" t="inlineStr">
         <is>
@@ -9545,12 +9609,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1259 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Kendaraan Innova DN 1258 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr"/>
@@ -9570,6 +9634,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -9643,7 +9708,7 @@
         </is>
       </c>
       <c r="O62" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
@@ -9660,14 +9725,14 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>21 Aug 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="T62" t="n">
         <v>1600000</v>
       </c>
       <c r="U62" t="n">
-        <v>24000000</v>
+        <v>40000000</v>
       </c>
       <c r="V62" t="inlineStr">
         <is>
@@ -9696,12 +9761,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1258 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Kendaraan Innova DN 1257 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr"/>
@@ -9721,6 +9786,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -9794,7 +9860,7 @@
         </is>
       </c>
       <c r="O63" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
@@ -9806,19 +9872,19 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>07 Aug 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>31 Aug 2026</t>
+          <t>14 Aug 2026</t>
         </is>
       </c>
       <c r="T63" t="n">
         <v>1600000</v>
       </c>
       <c r="U63" t="n">
-        <v>40000000</v>
+        <v>6400000</v>
       </c>
       <c r="V63" t="inlineStr">
         <is>
@@ -9847,12 +9913,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1257 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Kendaraan Pajero DN 1904 RA Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr"/>
@@ -9872,6 +9938,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -9941,11 +10008,11 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O64" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="P64" t="inlineStr">
         <is>
@@ -9957,19 +10024,19 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>11 Aug 2026</t>
+          <t>07 Aug 2026</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>14 Aug 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="T64" t="n">
         <v>1600000</v>
       </c>
       <c r="U64" t="n">
-        <v>6400000</v>
+        <v>40000000</v>
       </c>
       <c r="V64" t="inlineStr">
         <is>
@@ -9998,12 +10065,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>Kendaraan Pajero DN 1904 RA Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Kendaraan Hilux DN 1916 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr"/>
@@ -10023,6 +10090,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -10096,7 +10164,7 @@
         </is>
       </c>
       <c r="O65" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
@@ -10108,7 +10176,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>07 Aug 2026</t>
+          <t>08 Aug 2026</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -10120,7 +10188,7 @@
         <v>1600000</v>
       </c>
       <c r="U65" t="n">
-        <v>40000000</v>
+        <v>35200000</v>
       </c>
       <c r="V65" t="inlineStr">
         <is>
@@ -10149,12 +10217,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>Kendaraan Hilux DN 1916 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Kendaraan Hilux DN 1917 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr"/>
@@ -10174,6 +10242,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -10193,7 +10262,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -10223,12 +10292,12 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Penyediaan Car &amp; Tansportation Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Penyediaan Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>06 Aug 2026</t>
+          <t>07 Aug 2026</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -10238,16 +10307,16 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="O66" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="P66" t="inlineStr">
         <is>
@@ -10264,14 +10333,14 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>31 Aug 2026</t>
+          <t>14 Aug 2026</t>
         </is>
       </c>
       <c r="T66" t="n">
-        <v>1600000</v>
+        <v>8500000</v>
       </c>
       <c r="U66" t="n">
-        <v>35200000</v>
+        <v>59500000</v>
       </c>
       <c r="V66" t="inlineStr">
         <is>
@@ -10300,12 +10369,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>Kendaraan Hilux DN 1917 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Crane Tadano 70 ton Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr"/>
@@ -10325,6 +10394,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -10398,7 +10468,7 @@
         </is>
       </c>
       <c r="O67" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P67" t="inlineStr">
         <is>
@@ -10410,19 +10480,19 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>08 Aug 2026</t>
+          <t>23 Aug 2026</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>14 Aug 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="T67" t="n">
         <v>8500000</v>
       </c>
       <c r="U67" t="n">
-        <v>59500000</v>
+        <v>76500000</v>
       </c>
       <c r="V67" t="inlineStr">
         <is>
@@ -10451,12 +10521,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>Crane Tadano 70 ton Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Crane Sany 100 Ton untuk menggantikan Crane Tadano 70 Ton yang rusak</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr"/>
@@ -10476,6 +10546,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -10545,11 +10616,11 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>crane min 70 ton, call out, (hanya unit)</t>
+          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="O68" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
@@ -10561,7 +10632,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>23 Aug 2026</t>
+          <t>09 Aug 2026</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -10570,10 +10641,10 @@
         </is>
       </c>
       <c r="T68" t="n">
-        <v>8500000</v>
+        <v>2750000</v>
       </c>
       <c r="U68" t="n">
-        <v>76500000</v>
+        <v>57750000</v>
       </c>
       <c r="V68" t="inlineStr">
         <is>
@@ -10602,12 +10673,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>Crane Sany 100 Ton untuk menggantikan Crane Tadano 70 Ton yang rusak</t>
+          <t>Vacuum Truck  5000 L DN 8806 CH untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr"/>
@@ -10627,6 +10698,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -10646,7 +10718,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>028/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -10676,7 +10748,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Penyediaan Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -10691,20 +10763,20 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
+          <t>Aqua 600 ml</t>
         </is>
       </c>
       <c r="O69" t="n">
-        <v>21</v>
+        <v>1800</v>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q69" t="n">
@@ -10712,7 +10784,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>09 Aug 2026</t>
+          <t>08 Aug 2026</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -10721,10 +10793,10 @@
         </is>
       </c>
       <c r="T69" t="n">
-        <v>2750000</v>
+        <v>7500</v>
       </c>
       <c r="U69" t="n">
-        <v>57750000</v>
+        <v>12150000</v>
       </c>
       <c r="V69" t="inlineStr">
         <is>
@@ -10753,12 +10825,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>Vacuum Truck  5000 L DN 8806 CH untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Penyediaan Estimated Sum Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr"/>
@@ -10770,7 +10842,7 @@
       <c r="AI69" t="inlineStr"/>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -10778,6 +10850,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -10847,11 +10920,11 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>Aqua 600 ml</t>
+          <t>Aqua Galon Segel</t>
         </is>
       </c>
       <c r="O70" t="n">
-        <v>1800</v>
+        <v>18</v>
       </c>
       <c r="P70" t="inlineStr">
         <is>
@@ -10863,7 +10936,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>08 Aug 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -10872,10 +10945,10 @@
         </is>
       </c>
       <c r="T70" t="n">
-        <v>7500</v>
+        <v>53300</v>
       </c>
       <c r="U70" t="n">
-        <v>12150000</v>
+        <v>863460</v>
       </c>
       <c r="V70" t="inlineStr">
         <is>
@@ -10904,12 +10977,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>Penyediaan Estimated Sum Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Penyediaan Estimated Sum Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr"/>
@@ -10929,6 +11002,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -10948,7 +11022,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>028/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -10978,7 +11052,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -10993,20 +11067,20 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>Aqua Galon Segel</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="O71" t="n">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="Q71" t="n">
@@ -11014,19 +11088,19 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>08 Aug 2026</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>31 Aug 2026</t>
+          <t>08 Aug 2026</t>
         </is>
       </c>
       <c r="T71" t="n">
-        <v>53300</v>
+        <v>25000</v>
       </c>
       <c r="U71" t="n">
-        <v>863460</v>
+        <v>6250000</v>
       </c>
       <c r="V71" t="inlineStr">
         <is>
@@ -11055,12 +11129,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>Penyediaan Estimated Sum Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 70 Ton</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr"/>
@@ -11080,6 +11154,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -11153,7 +11228,7 @@
         </is>
       </c>
       <c r="O72" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="P72" t="inlineStr">
         <is>
@@ -11165,19 +11240,19 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>08 Aug 2026</t>
+          <t>23 Aug 2026</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>08 Aug 2026</t>
+          <t>23 Aug 2026</t>
         </is>
       </c>
       <c r="T72" t="n">
         <v>25000</v>
       </c>
       <c r="U72" t="n">
-        <v>6250000</v>
+        <v>5000000</v>
       </c>
       <c r="V72" t="inlineStr">
         <is>
@@ -11206,12 +11281,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 70 Ton</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 100 Ton</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr"/>
@@ -11231,6 +11306,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -11304,7 +11380,7 @@
         </is>
       </c>
       <c r="O73" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="P73" t="inlineStr">
         <is>
@@ -11316,19 +11392,19 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>23 Aug 2026</t>
+          <t>08 Aug 2026</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>23 Aug 2026</t>
+          <t>08 Aug 2026</t>
         </is>
       </c>
       <c r="T73" t="n">
         <v>25000</v>
       </c>
       <c r="U73" t="n">
-        <v>5000000</v>
+        <v>1250000</v>
       </c>
       <c r="V73" t="inlineStr">
         <is>
@@ -11357,12 +11433,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 100 Ton</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr"/>
@@ -11382,6 +11458,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -11513,7 +11590,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr"/>
@@ -11533,6 +11610,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -11610,7 +11688,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q75" t="n">
@@ -11659,12 +11737,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 05</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr"/>
@@ -11684,6 +11762,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -11761,7 +11840,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="Q76" t="n">
@@ -11810,12 +11889,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 05</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 06</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr"/>
@@ -11835,6 +11914,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -11908,7 +11988,7 @@
         </is>
       </c>
       <c r="O77" t="n">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="P77" t="inlineStr">
         <is>
@@ -11925,14 +12005,14 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>08 Aug 2026</t>
+          <t>23 Aug 2026</t>
         </is>
       </c>
       <c r="T77" t="n">
         <v>25000</v>
       </c>
       <c r="U77" t="n">
-        <v>1250000</v>
+        <v>2875000</v>
       </c>
       <c r="V77" t="inlineStr">
         <is>
@@ -11961,12 +12041,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 06</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Vacuum Truck 5000 L</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr"/>
@@ -11986,6 +12066,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AL77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -12005,12 +12086,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>004/BSS-JOB/WS/IV/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>31 Aug 2026</t>
+          <t>28 Apr 2026</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -12030,17 +12111,17 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011236</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengiriman OCTG (Casing 9 5/8" dan Tubing 4 1/2") Celegon-Senoro</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>07 Aug 2026</t>
+          <t>18 Feb 2026</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -12050,20 +12131,20 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Add Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O78" t="n">
-        <v>115</v>
+        <v>1</v>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q78" t="n">
@@ -12071,19 +12152,19 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>08 Aug 2026</t>
+          <t>28 Apr 2026</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>23 Aug 2026</t>
+          <t>28 Apr 2026</t>
         </is>
       </c>
       <c r="T78" t="n">
-        <v>25000</v>
+        <v>773919900</v>
       </c>
       <c r="U78" t="n">
-        <v>2875000</v>
+        <v>890007884.9999999</v>
       </c>
       <c r="V78" t="inlineStr">
         <is>
@@ -12112,12 +12193,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Vacuum Truck 5000 L</t>
+          <t>Pengiriman OCTG (Casing 9 5/8" dan Tubing 4 1/2") Celegon-Senoro</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr"/>
@@ -12129,14 +12210,15 @@
       <c r="AI78" t="inlineStr"/>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>1000025165</t>
+        </is>
+      </c>
+      <c r="AL78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -12156,12 +12238,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>004/BSS-JOB/WS/IV/2026</t>
+          <t>003/BSS-JOB/WS/II/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>28 Apr 2026</t>
+          <t>19 Feb 2026</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -12181,17 +12263,17 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>4500011236</t>
+          <t>4500011203</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Pengiriman OCTG (Casing 9 5/8" dan Tubing 4 1/2") Celegon-Senoro</t>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>18 Feb 2026</t>
+          <t>19 Feb 2026</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -12201,20 +12283,20 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>Add Cost + Fee 15%</t>
+          <t>Kayu Kaso/lata, 5x5x400 Kayu kelas 2</t>
         </is>
       </c>
       <c r="O79" t="n">
-        <v>1</v>
+        <v>0.524</v>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="Q79" t="n">
@@ -12222,19 +12304,19 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>28 Apr 2026</t>
+          <t>19 Feb 2026</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>28 Apr 2026</t>
+          <t>19 Feb 2026</t>
         </is>
       </c>
       <c r="T79" t="n">
-        <v>773919900</v>
+        <v>3125000</v>
       </c>
       <c r="U79" t="n">
-        <v>890007884.9999999</v>
+        <v>1637500</v>
       </c>
       <c r="V79" t="inlineStr">
         <is>
@@ -12263,12 +12345,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>Pengiriman OCTG (Casing 9 5/8" dan Tubing 4 1/2") Celegon-Senoro</t>
+          <t>Kayu Kaso/lata, 5x5x400 Kayu kelas 2  Material pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr"/>
@@ -12280,14 +12362,15 @@
       <c r="AI79" t="inlineStr"/>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>1000025165</t>
-        </is>
-      </c>
+          <t>1000025162</t>
+        </is>
+      </c>
+      <c r="AL79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -12357,15 +12440,15 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>Kayu Kaso/lata, 5x5x400 Kayu kelas 2</t>
+          <t>Paku Zeng</t>
         </is>
       </c>
       <c r="O80" t="n">
-        <v>0.524</v>
+        <v>4</v>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q80" t="n">
@@ -12382,10 +12465,10 @@
         </is>
       </c>
       <c r="T80" t="n">
-        <v>3125000</v>
+        <v>50000</v>
       </c>
       <c r="U80" t="n">
-        <v>1637500</v>
+        <v>200000</v>
       </c>
       <c r="V80" t="inlineStr">
         <is>
@@ -12414,12 +12497,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>Kayu Kaso/lata, 5x5x400 Kayu kelas 2  Material pembuatan grouting annulus SNR-19.</t>
+          <t>Paku 10 cm pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr"/>
@@ -12439,6 +12522,7 @@
           <t>1000025162</t>
         </is>
       </c>
+      <c r="AL80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -12512,7 +12596,7 @@
         </is>
       </c>
       <c r="O81" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P81" t="inlineStr">
         <is>
@@ -12536,7 +12620,7 @@
         <v>50000</v>
       </c>
       <c r="U81" t="n">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="V81" t="inlineStr">
         <is>
@@ -12565,12 +12649,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>Paku 10 cm pembuatan grouting annulus SNR-19.</t>
+          <t>Paku 7 cm  pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr"/>
@@ -12590,6 +12674,7 @@
           <t>1000025162</t>
         </is>
       </c>
+      <c r="AL81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -12716,12 +12801,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>Paku 7 cm  pembuatan grouting annulus SNR-19.</t>
+          <t>Paku 5 cm pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr"/>
@@ -12741,6 +12826,7 @@
           <t>1000025162</t>
         </is>
       </c>
+      <c r="AL82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -12810,15 +12896,15 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>Paku Zeng</t>
+          <t>Pipa PVC AW 1/2" (4m)</t>
         </is>
       </c>
       <c r="O83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q83" t="n">
@@ -12835,10 +12921,10 @@
         </is>
       </c>
       <c r="T83" t="n">
-        <v>50000</v>
+        <v>55500</v>
       </c>
       <c r="U83" t="n">
-        <v>100000</v>
+        <v>55500</v>
       </c>
       <c r="V83" t="inlineStr">
         <is>
@@ -12867,12 +12953,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>Paku 5 cm pembuatan grouting annulus SNR-19.</t>
+          <t>Pipa PVC AW 1/2" (4m)</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr"/>
@@ -12892,6 +12978,7 @@
           <t>1000025162</t>
         </is>
       </c>
+      <c r="AL83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -12961,7 +13048,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>Pipa PVC AW 1/2" (4m)</t>
+          <t>Lem pipa PVC</t>
         </is>
       </c>
       <c r="O84" t="n">
@@ -12977,19 +13064,19 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>19 Feb 2026</t>
+          <t>10 Sep 2026</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>19 Feb 2026</t>
+          <t>10 Sep 2026</t>
         </is>
       </c>
       <c r="T84" t="n">
-        <v>55500</v>
+        <v>75000</v>
       </c>
       <c r="U84" t="n">
-        <v>55500</v>
+        <v>75000</v>
       </c>
       <c r="V84" t="inlineStr">
         <is>
@@ -13018,12 +13105,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>Pipa PVC AW 1/2" (4m)</t>
+          <t>Lem pipa PVC</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr"/>
@@ -13043,6 +13130,7 @@
           <t>1000025162</t>
         </is>
       </c>
+      <c r="AL84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -13112,7 +13200,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>Lem pipa PVC</t>
+          <t>Pasir</t>
         </is>
       </c>
       <c r="O85" t="n">
@@ -13120,7 +13208,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="Q85" t="n">
@@ -13128,19 +13216,19 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>10 Sep 2026</t>
+          <t>19 Feb 2026</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>10 Sep 2026</t>
+          <t>19 Feb 2026</t>
         </is>
       </c>
       <c r="T85" t="n">
-        <v>75000</v>
+        <v>293750</v>
       </c>
       <c r="U85" t="n">
-        <v>75000</v>
+        <v>293750</v>
       </c>
       <c r="V85" t="inlineStr">
         <is>
@@ -13169,12 +13257,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>Lem pipa PVC</t>
+          <t>Pasir</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr"/>
@@ -13194,6 +13282,7 @@
           <t>1000025162</t>
         </is>
       </c>
+      <c r="AL85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -13263,7 +13352,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>Pasir</t>
+          <t>Batu Agregate A</t>
         </is>
       </c>
       <c r="O86" t="n">
@@ -13288,10 +13377,10 @@
         </is>
       </c>
       <c r="T86" t="n">
-        <v>293750</v>
+        <v>400000</v>
       </c>
       <c r="U86" t="n">
-        <v>293750</v>
+        <v>400000</v>
       </c>
       <c r="V86" t="inlineStr">
         <is>
@@ -13320,12 +13409,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>Pasir</t>
+          <t>Batu Pecah 1-2</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr"/>
@@ -13345,6 +13434,7 @@
           <t>1000025162</t>
         </is>
       </c>
+      <c r="AL86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -13414,15 +13504,15 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>Batu Agregate A</t>
+          <t>Semen PC 50 kg</t>
         </is>
       </c>
       <c r="O87" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q87" t="n">
@@ -13439,10 +13529,10 @@
         </is>
       </c>
       <c r="T87" t="n">
-        <v>400000</v>
+        <v>120000</v>
       </c>
       <c r="U87" t="n">
-        <v>400000</v>
+        <v>1440000</v>
       </c>
       <c r="V87" t="inlineStr">
         <is>
@@ -13471,12 +13561,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>Batu Pecah 1-2</t>
+          <t>Semen PC 50 kg</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr"/>
@@ -13496,6 +13586,7 @@
           <t>1000025162</t>
         </is>
       </c>
+      <c r="AL87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -13565,11 +13656,11 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>Semen PC 50 kg</t>
+          <t>Skop</t>
         </is>
       </c>
       <c r="O88" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="P88" t="inlineStr">
         <is>
@@ -13590,10 +13681,10 @@
         </is>
       </c>
       <c r="T88" t="n">
-        <v>120000</v>
+        <v>93750</v>
       </c>
       <c r="U88" t="n">
-        <v>1440000</v>
+        <v>187500</v>
       </c>
       <c r="V88" t="inlineStr">
         <is>
@@ -13622,12 +13713,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>Semen PC 50 kg</t>
+          <t>Skop</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr"/>
@@ -13647,6 +13738,7 @@
           <t>1000025162</t>
         </is>
       </c>
+      <c r="AL88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -13716,7 +13808,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>Skop</t>
+          <t>Sendok adukan</t>
         </is>
       </c>
       <c r="O89" t="n">
@@ -13741,10 +13833,10 @@
         </is>
       </c>
       <c r="T89" t="n">
-        <v>93750</v>
+        <v>37500</v>
       </c>
       <c r="U89" t="n">
-        <v>187500</v>
+        <v>75000</v>
       </c>
       <c r="V89" t="inlineStr">
         <is>
@@ -13773,12 +13865,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>Skop</t>
+          <t>Sendok adukan</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr"/>
@@ -13798,6 +13890,7 @@
           <t>1000025162</t>
         </is>
       </c>
+      <c r="AL89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -13867,11 +13960,11 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>Sendok adukan</t>
+          <t>Meteran @5m</t>
         </is>
       </c>
       <c r="O90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P90" t="inlineStr">
         <is>
@@ -13895,7 +13988,7 @@
         <v>37500</v>
       </c>
       <c r="U90" t="n">
-        <v>75000</v>
+        <v>37500</v>
       </c>
       <c r="V90" t="inlineStr">
         <is>
@@ -13924,12 +14017,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>Sendok adukan</t>
+          <t>Meteran @5m</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr"/>
@@ -13949,6 +14042,7 @@
           <t>1000025162</t>
         </is>
       </c>
+      <c r="AL90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -14018,15 +14112,15 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>Meteran @5m</t>
+          <t>Terpaulin A12</t>
         </is>
       </c>
       <c r="O91" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>m</t>
         </is>
       </c>
       <c r="Q91" t="n">
@@ -14043,10 +14137,10 @@
         </is>
       </c>
       <c r="T91" t="n">
-        <v>37500</v>
+        <v>31250</v>
       </c>
       <c r="U91" t="n">
-        <v>37500</v>
+        <v>1500000</v>
       </c>
       <c r="V91" t="inlineStr">
         <is>
@@ -14075,12 +14169,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>Meteran @5m</t>
+          <t>Terpaulin A12</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr"/>
@@ -14100,6 +14194,7 @@
           <t>1000025162</t>
         </is>
       </c>
+      <c r="AL91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -14173,7 +14268,7 @@
         </is>
       </c>
       <c r="O92" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="P92" t="inlineStr">
         <is>
@@ -14197,7 +14292,7 @@
         <v>31250</v>
       </c>
       <c r="U92" t="n">
-        <v>1500000</v>
+        <v>625000</v>
       </c>
       <c r="V92" t="inlineStr">
         <is>
@@ -14231,7 +14326,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr"/>
@@ -14251,6 +14346,7 @@
           <t>1000025162</t>
         </is>
       </c>
+      <c r="AL92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -14320,15 +14416,15 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>Terpaulin A12</t>
+          <t>Kabel 2x1.5mm NYA/NYM @50m</t>
         </is>
       </c>
       <c r="O93" t="n">
-        <v>20</v>
+        <v>0.2</v>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>Roll</t>
         </is>
       </c>
       <c r="Q93" t="n">
@@ -14345,10 +14441,10 @@
         </is>
       </c>
       <c r="T93" t="n">
-        <v>31250</v>
+        <v>712500</v>
       </c>
       <c r="U93" t="n">
-        <v>625000</v>
+        <v>142500</v>
       </c>
       <c r="V93" t="inlineStr">
         <is>
@@ -14377,12 +14473,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>Terpaulin A12</t>
+          <t>Kabel 2x1.5mm NYA/NYM @50m</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr"/>
@@ -14402,6 +14498,7 @@
           <t>1000025162</t>
         </is>
       </c>
+      <c r="AL93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -14471,15 +14568,15 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>Kabel 2x1.5mm NYA/NYM @50m</t>
+          <t>Paku Zeng</t>
         </is>
       </c>
       <c r="O94" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Roll</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q94" t="n">
@@ -14496,10 +14593,10 @@
         </is>
       </c>
       <c r="T94" t="n">
-        <v>712500</v>
+        <v>50000</v>
       </c>
       <c r="U94" t="n">
-        <v>142500</v>
+        <v>25000</v>
       </c>
       <c r="V94" t="inlineStr">
         <is>
@@ -14528,12 +14625,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>Kabel 2x1.5mm NYA/NYM @50m</t>
+          <t>Paku 12 cm</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr"/>
@@ -14553,6 +14650,7 @@
           <t>1000025162</t>
         </is>
       </c>
+      <c r="AL94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -14638,12 +14736,12 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>19 Feb 2026</t>
+          <t>10 Sep 2026</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>19 Feb 2026</t>
+          <t>10 Sep 2026</t>
         </is>
       </c>
       <c r="T95" t="n">
@@ -14679,12 +14777,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>Paku 12 cm</t>
+          <t>Paku Beton 10 cm</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr"/>
@@ -14704,6 +14802,7 @@
           <t>1000025162</t>
         </is>
       </c>
+      <c r="AL95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -14723,12 +14822,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>003/BSS-JOB/WS/II/2026</t>
+          <t>006/BSS-JOB/WS/VI/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>19 Feb 2026</t>
+          <t>06 Jun 2026</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -14743,22 +14842,22 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>4500011203</t>
+          <t>4500011579</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Material pembuatan grouting annulus SNR-19.</t>
+          <t>Pengadaan Ban Spare part Genset Field Maintenance</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>19 Feb 2026</t>
+          <t>04 Jun 2026</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -14768,20 +14867,20 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>Paku Zeng</t>
+          <t>Add Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O96" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q96" t="n">
@@ -14789,19 +14888,19 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>10 Sep 2026</t>
+          <t>06 Jun 2026</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>10 Sep 2026</t>
+          <t>06 Jun 2026</t>
         </is>
       </c>
       <c r="T96" t="n">
-        <v>50000</v>
+        <v>575000</v>
       </c>
       <c r="U96" t="n">
-        <v>25000</v>
+        <v>661250</v>
       </c>
       <c r="V96" t="inlineStr">
         <is>
@@ -14830,12 +14929,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>Paku Beton 10 cm</t>
+          <t>Pengadaan Ban Spare part Genset Field Maintenance</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr"/>
@@ -14852,9 +14951,10 @@
       </c>
       <c r="AK96" t="inlineStr">
         <is>
-          <t>1000025162</t>
-        </is>
-      </c>
+          <t>1000025742</t>
+        </is>
+      </c>
+      <c r="AL96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -14874,7 +14974,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>006/BSS-JOB/WS/VI/2026</t>
+          <t>007/BSS-JOB/WS/VI/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -14899,12 +14999,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>4500011579</t>
+          <t>4500011580</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Pengadaan Ban Spare part Genset Field Maintenance</t>
+          <t>Transport Pengangkutan Material   Spare part Genset Field Maintenance</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -14919,12 +15019,12 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>Add Cost + Fee 15%</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O97" t="n">
@@ -14932,7 +15032,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q97" t="n">
@@ -14949,10 +15049,10 @@
         </is>
       </c>
       <c r="T97" t="n">
-        <v>575000</v>
+        <v>1600000</v>
       </c>
       <c r="U97" t="n">
-        <v>661250</v>
+        <v>1600000</v>
       </c>
       <c r="V97" t="inlineStr">
         <is>
@@ -14981,12 +15081,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>Pengadaan Ban Spare part Genset Field Maintenance</t>
+          <t>Transport Pengangkutan Material   Spare part Genset Field Maintenance</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr"/>
@@ -14998,39 +15098,40 @@
       <c r="AI97" t="inlineStr"/>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
         <is>
-          <t>1000025742</t>
-        </is>
-      </c>
+          <t>1000025743</t>
+        </is>
+      </c>
+      <c r="AL97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>7201250141</t>
+          <t>7207250142</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>S25048TPD</t>
+          <t>S250551FLD-R1</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>007/BSS-JOB/WS/VI/2026</t>
+          <t>001/BSS-JOB/FLD/XII/2025</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>06 Jun 2026</t>
+          <t>31 Dec 2025</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -15045,22 +15146,22 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+          <t>24 Month</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>4500011580</t>
+          <t>4599910747</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Transport Pengangkutan Material   Spare part Genset Field Maintenance</t>
+          <t>Jasa Mobilisasi Alat Berat Monthly Basis</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>04 Jun 2026</t>
+          <t>20 Dec 2025</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -15070,12 +15171,12 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>JASA MOBILISASI</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Jasa Mob - Demob (Per Unit), Mobilisasi Semua Alat Berat Dari Luar Luwuk ke Luwuk (Monthly Basis)</t>
         </is>
       </c>
       <c r="O98" t="n">
@@ -15083,7 +15184,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q98" t="n">
@@ -15091,19 +15192,19 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>06 Jun 2026</t>
+          <t>20 Dec 2025</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>06 Jun 2026</t>
+          <t>31 Dec 2025</t>
         </is>
       </c>
       <c r="T98" t="n">
-        <v>1600000</v>
+        <v>400000000</v>
       </c>
       <c r="U98" t="n">
-        <v>1600000</v>
+        <v>400000000</v>
       </c>
       <c r="V98" t="inlineStr">
         <is>
@@ -15132,12 +15233,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>Transport Pengangkutan Material   Spare part Genset Field Maintenance</t>
+          <t>Jasa Mob - Demob (Per Unit), Mobilisasi Semua Alat Berat Dari Luar Luwuk ke Luwuk (Monthly Basis) 5 unit Alat Berat Monthly Basis</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-09-10 13:42:18</t>
+          <t>2026-09-10 19:10:55</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr"/>
@@ -15154,7 +15255,2508 @@
       </c>
       <c r="AK98" t="inlineStr">
         <is>
-          <t>1000025743</t>
+          <t>1000024733</t>
+        </is>
+      </c>
+      <c r="AL98" t="inlineStr">
+        <is>
+          <t>7207250142-BSS-WO-2026-020</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>S250551FLD-R1</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>002/BSS-JOB/FLD/XII/2025</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>31 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>24 Month</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>4500010748</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>20 Dec 2025</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>MONTHLY BASIS</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP</t>
+        </is>
+      </c>
+      <c r="O99" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>100</v>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>20 Dec 2025</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>31 Dec 2025</t>
+        </is>
+      </c>
+      <c r="T99" t="n">
+        <v>75538000</v>
+      </c>
+      <c r="U99" t="n">
+        <v>29459820</v>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (20 - 31 Desember 2025)</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:10:55</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr"/>
+      <c r="AD99" t="inlineStr"/>
+      <c r="AE99" t="inlineStr"/>
+      <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="inlineStr"/>
+      <c r="AH99" t="inlineStr"/>
+      <c r="AI99" t="inlineStr"/>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>1000024201</t>
+        </is>
+      </c>
+      <c r="AL99" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>S250551FLD-R1</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>003/BSS-JOB/FLD/XII/2025</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>31 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>24 Month</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>4500010749</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>20 Dec 2025</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>MONTHLY BASIS</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
+        </is>
+      </c>
+      <c r="O100" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>100</v>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>20 Dec 2025</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>31 Dec 2025</t>
+        </is>
+      </c>
+      <c r="T100" t="n">
+        <v>62818000</v>
+      </c>
+      <c r="U100" t="n">
+        <v>24499020</v>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (20 - 31 Desember 2025)</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:10:55</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr"/>
+      <c r="AD100" t="inlineStr"/>
+      <c r="AE100" t="inlineStr"/>
+      <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="inlineStr"/>
+      <c r="AH100" t="inlineStr"/>
+      <c r="AI100" t="inlineStr"/>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>1000024205</t>
+        </is>
+      </c>
+      <c r="AL100" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-003</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>S250551FLD-R1</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>004/BSS-JOB/FLD/XII/2025</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>31 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>24 Month</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>4500010750</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>20 Dec 2025</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>MONTHLY BASIS</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Vacuum Truck 10.000 L</t>
+        </is>
+      </c>
+      <c r="O101" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>100</v>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>20 Dec 2025</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>31 Dec 2025</t>
+        </is>
+      </c>
+      <c r="T101" t="n">
+        <v>78225000</v>
+      </c>
+      <c r="U101" t="n">
+        <v>30507750</v>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (20 - 31 Desember 2025)</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:10:55</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr"/>
+      <c r="AD101" t="inlineStr"/>
+      <c r="AE101" t="inlineStr"/>
+      <c r="AF101" t="inlineStr"/>
+      <c r="AG101" t="inlineStr"/>
+      <c r="AH101" t="inlineStr"/>
+      <c r="AI101" t="inlineStr"/>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>1000024200</t>
+        </is>
+      </c>
+      <c r="AL101" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>S250551FLD-R1</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>005/BSS-JOB/FLD/XII/2025</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>31 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>24 Month</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>4500010746</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20-31 Desember 2025)</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>20 Dec 2025</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>MONTHLY BASIS</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Mobile Crane Capacity 80 T</t>
+        </is>
+      </c>
+      <c r="O102" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>100</v>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>20 Dec 2025</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>31 Dec 2025</t>
+        </is>
+      </c>
+      <c r="T102" t="n">
+        <v>189241000</v>
+      </c>
+      <c r="U102" t="n">
+        <v>73803990</v>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (20-31 Desember 2025)</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:10:55</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr"/>
+      <c r="AD102" t="inlineStr"/>
+      <c r="AE102" t="inlineStr"/>
+      <c r="AF102" t="inlineStr"/>
+      <c r="AG102" t="inlineStr"/>
+      <c r="AH102" t="inlineStr"/>
+      <c r="AI102" t="inlineStr"/>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>1000024199</t>
+        </is>
+      </c>
+      <c r="AL102" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-005</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>S250551FLD-R1</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>006/BSS-JOB/FLD/XII/2025</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>31 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>24 Month</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>4500010745</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>20 Dec 2025</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>MONTHLY BASIS</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Truck Mounted Crane (TMC) Capacity 8 T</t>
+        </is>
+      </c>
+      <c r="O103" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>100</v>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>20 Dec 2025</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>31 Dec 2025</t>
+        </is>
+      </c>
+      <c r="T103" t="n">
+        <v>131224000</v>
+      </c>
+      <c r="U103" t="n">
+        <v>51177360</v>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (20 - 31 Desember 2025)</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:10:55</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr"/>
+      <c r="AD103" t="inlineStr"/>
+      <c r="AE103" t="inlineStr"/>
+      <c r="AF103" t="inlineStr"/>
+      <c r="AG103" t="inlineStr"/>
+      <c r="AH103" t="inlineStr"/>
+      <c r="AI103" t="inlineStr"/>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>1000024198</t>
+        </is>
+      </c>
+      <c r="AL103" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-006</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>S250551FLD-R1</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>007/BSS-JOB/FLD/I/2026</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>31 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>24 Month</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>4500010745</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 s/d 31 Januari 2026)</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>20 Dec 2025</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>MONTHLY BASIS</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Truck Mounted Crane (TMC) Capacity 8 T</t>
+        </is>
+      </c>
+      <c r="O104" t="n">
+        <v>1</v>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>100</v>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>01 Jan 2026</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>31 Jan 2026</t>
+        </is>
+      </c>
+      <c r="T104" t="n">
+        <v>131224000</v>
+      </c>
+      <c r="U104" t="n">
+        <v>131224000</v>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 s/d 31 Januari 2026)</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:10:55</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr"/>
+      <c r="AD104" t="inlineStr"/>
+      <c r="AE104" t="inlineStr"/>
+      <c r="AF104" t="inlineStr"/>
+      <c r="AG104" t="inlineStr"/>
+      <c r="AH104" t="inlineStr"/>
+      <c r="AI104" t="inlineStr"/>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>1000024508</t>
+        </is>
+      </c>
+      <c r="AL104" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-006</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>S250551FLD-R1</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>008/BSS-JOB/FLD/I/2026</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>31 Jan 2026</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>24 Month</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>4500010749</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>20 Dec 2025</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>MONTHLY BASIS</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
+        </is>
+      </c>
+      <c r="O105" t="n">
+        <v>1</v>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>100</v>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>01 Jan 2026</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>31 Jan 2026</t>
+        </is>
+      </c>
+      <c r="T105" t="n">
+        <v>62818000</v>
+      </c>
+      <c r="U105" t="n">
+        <v>62818000</v>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 SD 31 JANUARI 2026)</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:10:55</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr"/>
+      <c r="AD105" t="inlineStr"/>
+      <c r="AE105" t="inlineStr"/>
+      <c r="AF105" t="inlineStr"/>
+      <c r="AG105" t="inlineStr"/>
+      <c r="AH105" t="inlineStr"/>
+      <c r="AI105" t="inlineStr"/>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>1000024511</t>
+        </is>
+      </c>
+      <c r="AL105" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-003</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>S250551FLD-R1</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>009/BSS-JOB/FLD/I/2026</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>31 Jan 2026</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>24 Month</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>4500010746</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>20 Dec 2025</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>MONTHLY BASIS</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Mobile Crane Capacity 80 T</t>
+        </is>
+      </c>
+      <c r="O106" t="n">
+        <v>1</v>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>100</v>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>01 Jan 2026</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>31 Jan 2026</t>
+        </is>
+      </c>
+      <c r="T106" t="n">
+        <v>189241000</v>
+      </c>
+      <c r="U106" t="n">
+        <v>189241000</v>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 SD 31 JANUARI 2026)</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:10:55</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr"/>
+      <c r="AD106" t="inlineStr"/>
+      <c r="AE106" t="inlineStr"/>
+      <c r="AF106" t="inlineStr"/>
+      <c r="AG106" t="inlineStr"/>
+      <c r="AH106" t="inlineStr"/>
+      <c r="AI106" t="inlineStr"/>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>1000024510</t>
+        </is>
+      </c>
+      <c r="AL106" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-005</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>S250551FLD-R1</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>010/BSS-JOB/FLD/I/2026</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>31 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>24 Month</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>4500010748</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>20 Dec 2025</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>MONTHLY BASIS</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP</t>
+        </is>
+      </c>
+      <c r="O107" t="n">
+        <v>1</v>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>100</v>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>01 Jan 2026</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>31 Jan 2026</t>
+        </is>
+      </c>
+      <c r="T107" t="n">
+        <v>75538000</v>
+      </c>
+      <c r="U107" t="n">
+        <v>75538000</v>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 SD 31 JANUARI 2026)</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:10:55</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr"/>
+      <c r="AD107" t="inlineStr"/>
+      <c r="AE107" t="inlineStr"/>
+      <c r="AF107" t="inlineStr"/>
+      <c r="AG107" t="inlineStr"/>
+      <c r="AH107" t="inlineStr"/>
+      <c r="AI107" t="inlineStr"/>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>1000024516</t>
+        </is>
+      </c>
+      <c r="AL107" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>S250551FLD-R1</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>011/BSS-JOB/FLD/I/2026</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>31 Jan 2026</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>24 Month</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>4500010750</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>20 Dec 2025</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>MONTHLY BASIS</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Vacuum Truck 10.000 L</t>
+        </is>
+      </c>
+      <c r="O108" t="n">
+        <v>1</v>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>100</v>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>01 Jan 2026</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>31 Jan 2026</t>
+        </is>
+      </c>
+      <c r="T108" t="n">
+        <v>78225000</v>
+      </c>
+      <c r="U108" t="n">
+        <v>78225000</v>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 SD 31 JANUARI 2026)</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:10:55</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr"/>
+      <c r="AD108" t="inlineStr"/>
+      <c r="AE108" t="inlineStr"/>
+      <c r="AF108" t="inlineStr"/>
+      <c r="AG108" t="inlineStr"/>
+      <c r="AH108" t="inlineStr"/>
+      <c r="AI108" t="inlineStr"/>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>1000024509</t>
+        </is>
+      </c>
+      <c r="AL108" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>S250551FLD-R1</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>012/BSS-JOB/FLD/I/2026</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>10 Feb 2026</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>24 Month</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>4500010980</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Oncall Basis Dump Truck Untuk Pengangkutan Material Sirtu dari Area Red Zona ke Area Green Zona CPP Senoro</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>03 Feb 2026</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>ON-CALL BASIS</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat On Call Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Dump Truck 4 Ton min 120PS</t>
+        </is>
+      </c>
+      <c r="O109" t="n">
+        <v>7</v>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>100</v>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>03 Feb 2026</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>09 Feb 2026</t>
+        </is>
+      </c>
+      <c r="T109" t="n">
+        <v>1936000</v>
+      </c>
+      <c r="U109" t="n">
+        <v>13552000</v>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Oncall Basis Dump Truck Untuk Pengangkutan Material Sirtu dari Area Red Zona ke Area Green Zona CPP Senoro</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:10:55</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr"/>
+      <c r="AD109" t="inlineStr"/>
+      <c r="AE109" t="inlineStr"/>
+      <c r="AF109" t="inlineStr"/>
+      <c r="AG109" t="inlineStr"/>
+      <c r="AH109" t="inlineStr"/>
+      <c r="AI109" t="inlineStr"/>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>1000024507</t>
+        </is>
+      </c>
+      <c r="AL109" t="inlineStr">
+        <is>
+          <t>7207250142-BSS-WO-2025-008</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>S250551FLD-R1</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>014/BSS-JOB/FLD/II/2026</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>28 Feb 2026</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>24 Month</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>4500010749</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>20 Dec 2025</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>MONTHLY BASIS</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
+        </is>
+      </c>
+      <c r="O110" t="n">
+        <v>1</v>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>100</v>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>01 Feb 2026</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>28 Feb 2026</t>
+        </is>
+      </c>
+      <c r="T110" t="n">
+        <v>62818000</v>
+      </c>
+      <c r="U110" t="n">
+        <v>62818000</v>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 - 28 Februari 2026)</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:10:55</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr"/>
+      <c r="AD110" t="inlineStr"/>
+      <c r="AE110" t="inlineStr"/>
+      <c r="AF110" t="inlineStr"/>
+      <c r="AG110" t="inlineStr"/>
+      <c r="AH110" t="inlineStr"/>
+      <c r="AI110" t="inlineStr"/>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>1000024711</t>
+        </is>
+      </c>
+      <c r="AL110" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-003</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>S250551FLD-R1</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/FLD/II/2026</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>28 Feb 2026</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>24 Month</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>4500010748</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>20 Dec 2025</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>MONTHLY BASIS</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP</t>
+        </is>
+      </c>
+      <c r="O111" t="n">
+        <v>1</v>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>100</v>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>01 Feb 2026</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>28 Feb 2026</t>
+        </is>
+      </c>
+      <c r="T111" t="n">
+        <v>75538000</v>
+      </c>
+      <c r="U111" t="n">
+        <v>75538000</v>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 - 28 Februari 2026)</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:10:55</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr"/>
+      <c r="AD111" t="inlineStr"/>
+      <c r="AE111" t="inlineStr"/>
+      <c r="AF111" t="inlineStr"/>
+      <c r="AG111" t="inlineStr"/>
+      <c r="AH111" t="inlineStr"/>
+      <c r="AI111" t="inlineStr"/>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>1000024712</t>
+        </is>
+      </c>
+      <c r="AL111" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>S250551FLD-R1</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>015/BSS-JOB/FLD/II/2026</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>28 Feb 2026</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>24 Month</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>4500010750</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>20 Dec 2025</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>MONTHLY BASIS</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Vacuum Truck 10.000 L</t>
+        </is>
+      </c>
+      <c r="O112" t="n">
+        <v>1</v>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>100</v>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>01 Feb 2026</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>28 Feb 2026</t>
+        </is>
+      </c>
+      <c r="T112" t="n">
+        <v>78225000</v>
+      </c>
+      <c r="U112" t="n">
+        <v>78225000</v>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 - 28 Februari 2026)</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:10:55</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr"/>
+      <c r="AD112" t="inlineStr"/>
+      <c r="AE112" t="inlineStr"/>
+      <c r="AF112" t="inlineStr"/>
+      <c r="AG112" t="inlineStr"/>
+      <c r="AH112" t="inlineStr"/>
+      <c r="AI112" t="inlineStr"/>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>1000024709</t>
+        </is>
+      </c>
+      <c r="AL112" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>S250551FLD-R1</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>016/BSS-JOB/FLD/II/2026</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>28 Feb 2026</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>24 Month</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>4500010746</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>20 Dec 2025</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>MONTHLY BASIS</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Mobile Crane Capacity 80 T</t>
+        </is>
+      </c>
+      <c r="O113" t="n">
+        <v>1</v>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>100</v>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>01 Feb 2026</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>28 Feb 2026</t>
+        </is>
+      </c>
+      <c r="T113" t="n">
+        <v>189241000</v>
+      </c>
+      <c r="U113" t="n">
+        <v>189241000</v>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 - 28 Februari 2026)</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:10:55</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr"/>
+      <c r="AD113" t="inlineStr"/>
+      <c r="AE113" t="inlineStr"/>
+      <c r="AF113" t="inlineStr"/>
+      <c r="AG113" t="inlineStr"/>
+      <c r="AH113" t="inlineStr"/>
+      <c r="AI113" t="inlineStr"/>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>1000024708</t>
+        </is>
+      </c>
+      <c r="AL113" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-005</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>S250551FLD-R1</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>017/BSS-JOB/FLD/II/2026</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>28 Feb 2026</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>24 Month</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>4500010745</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>20 Dec 2025</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>MONTHLY BASIS</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Truck Mounted Crane (TMC) Capacity 8 T</t>
+        </is>
+      </c>
+      <c r="O114" t="n">
+        <v>1</v>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>100</v>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>01 Feb 2026</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>28 Feb 2026</t>
+        </is>
+      </c>
+      <c r="T114" t="n">
+        <v>131224000</v>
+      </c>
+      <c r="U114" t="n">
+        <v>131224000</v>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 - 28 Februari 2026)</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:10:55</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr"/>
+      <c r="AD114" t="inlineStr"/>
+      <c r="AE114" t="inlineStr"/>
+      <c r="AF114" t="inlineStr"/>
+      <c r="AG114" t="inlineStr"/>
+      <c r="AH114" t="inlineStr"/>
+      <c r="AI114" t="inlineStr"/>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>1000024727</t>
+        </is>
+      </c>
+      <c r="AL114" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-006</t>
         </is>
       </c>
     </row>
